--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47483A04-1FAE-48B7-8D81-F9D3B40C6A8A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6573FF71-1ACB-487C-9D8B-8B49D3C64D6D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="30,12,25" sheetId="101" r:id="rId1"/>
+    <sheet name="06,01,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,24 +31,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="6">
-  <si>
-    <t>ЗПФ</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="3">
   <si>
     <t>КИ</t>
   </si>
   <si>
-    <t>КСК</t>
+    <t>ЛП</t>
   </si>
   <si>
-    <t>04,01,26</t>
-  </si>
-  <si>
-    <t>05,01,26</t>
-  </si>
-  <si>
-    <t>ЛП</t>
+    <t>08,01,26</t>
   </si>
 </sst>
 </file>
@@ -89,7 +80,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -224,11 +215,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -264,6 +292,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -651,130 +688,128 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="11">
+    <row r="1" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4">
         <v>1</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="7">
-        <v>15482.119999999999</v>
-      </c>
-      <c r="F1" s="8">
-        <v>0.39583333333333331</v>
+      <c r="E1" s="5">
+        <v>18168.139999999996</v>
+      </c>
+      <c r="F1" s="6">
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12"/>
-      <c r="B2" s="9" t="s">
+      <c r="A2" s="1">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="9">
-        <v>2253.1</v>
-      </c>
-      <c r="F2" s="10">
-        <v>0.39583333333333331</v>
+      <c r="E2" s="2">
+        <v>18299.759999999995</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0.45833333333333331</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
+        <v>3</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>5</v>
-      </c>
       <c r="E3" s="5">
-        <v>17997.919999999998</v>
+        <v>18175.439999999999</v>
       </c>
       <c r="F3" s="6">
-        <v>0.45833333333333331</v>
+        <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
+    <row r="4" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="11">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="2">
-        <v>18154.95</v>
-      </c>
-      <c r="F4" s="3">
-        <v>0.5</v>
+      <c r="E4" s="7">
+        <v>9287.3200000000015</v>
+      </c>
+      <c r="F4" s="8">
+        <v>0.54166666666666663</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
+    <row r="5" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="13"/>
+      <c r="B5" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E5" s="5">
-        <v>17758.97</v>
-      </c>
-      <c r="F5" s="6">
-        <v>0.375</v>
+      <c r="E5" s="14">
+        <v>4605.9600000000019</v>
+      </c>
+      <c r="F5" s="15">
+        <v>0.54166666666666663</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="A6" s="12"/>
+      <c r="B6" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="2">
-        <v>12000.76</v>
-      </c>
-      <c r="F6" s="3">
-        <v>0.375</v>
+      <c r="D6" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="9">
+        <v>3015</v>
+      </c>
+      <c r="F6" s="10">
+        <v>0.54166666666666663</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A4:A6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6573FF71-1ACB-487C-9D8B-8B49D3C64D6D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABF1048E-702E-4457-A5C9-99B30EC16026}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="06,01,26" sheetId="101" r:id="rId1"/>
+    <sheet name="07,01,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="7">
   <si>
     <t>КИ</t>
   </si>
@@ -39,7 +39,19 @@
     <t>ЛП</t>
   </si>
   <si>
-    <t>08,01,26</t>
+    <t>09,01,26</t>
+  </si>
+  <si>
+    <t>КСК</t>
+  </si>
+  <si>
+    <t>ЗПФ</t>
+  </si>
+  <si>
+    <t>10,01,26</t>
+  </si>
+  <si>
+    <t>НВ</t>
   </si>
 </sst>
 </file>
@@ -256,7 +268,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -288,19 +300,46 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -685,131 +724,360 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4">
+    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="16">
         <v>1</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="17">
+        <v>15395.74</v>
+      </c>
+      <c r="F1" s="18">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="19"/>
+      <c r="B2" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="20">
+        <v>2072.6999999999998</v>
+      </c>
+      <c r="F2" s="21">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="5">
-        <v>18168.139999999996</v>
-      </c>
-      <c r="F1" s="6">
+      <c r="E3" s="2">
+        <v>12250.32</v>
+      </c>
+      <c r="F3" s="3">
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+    <row r="4" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="16">
+        <v>3</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="17">
+        <v>17206.269999999997</v>
+      </c>
+      <c r="F4" s="18">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="19"/>
+      <c r="B5" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="20">
+        <v>444.00000000000006</v>
+      </c>
+      <c r="F5" s="21">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="13">
+        <v>4</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="7">
+        <v>8556.4000000000015</v>
+      </c>
+      <c r="F6" s="8">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="14"/>
+      <c r="B7" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="11">
+        <v>1312.8</v>
+      </c>
+      <c r="F7" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15"/>
+      <c r="B8" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="9">
+        <v>7342.8</v>
+      </c>
+      <c r="F8" s="10">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>5</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="D9" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="5">
+        <v>12544.32</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="13">
+        <v>6</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="2">
-        <v>18299.759999999995</v>
-      </c>
-      <c r="F2" s="3">
+      <c r="E10" s="7">
+        <v>3627.5400000000004</v>
+      </c>
+      <c r="F10" s="8">
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>3</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="5">
-        <v>18175.439999999999</v>
-      </c>
-      <c r="F3" s="6">
+    <row r="11" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="14"/>
+      <c r="B11" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="11">
+        <v>1229.58</v>
+      </c>
+      <c r="F11" s="12">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="15"/>
+      <c r="B12" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="9">
+        <v>12532.46</v>
+      </c>
+      <c r="F12" s="10">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="16">
+        <v>7</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="17">
+        <v>2025</v>
+      </c>
+      <c r="F13" s="18">
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="11">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="7">
-        <v>9287.3200000000015</v>
-      </c>
-      <c r="F4" s="8">
+    <row r="14" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A14" s="22"/>
+      <c r="B14" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="23">
+        <v>14188.970000000001</v>
+      </c>
+      <c r="F14" s="24">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="19"/>
+      <c r="B15" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="20">
+        <v>1197.04</v>
+      </c>
+      <c r="F15" s="21">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A16" s="13">
+        <v>8</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" s="7">
+        <v>4882.13</v>
+      </c>
+      <c r="F16" s="8">
         <v>0.54166666666666663</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="13"/>
-      <c r="B5" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="14">
-        <v>4605.9600000000019</v>
-      </c>
-      <c r="F5" s="15">
+    <row r="17" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A17" s="14"/>
+      <c r="B17" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="11">
+        <v>6505.7999999999993</v>
+      </c>
+      <c r="F17" s="12">
         <v>0.54166666666666663</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="B6" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="9">
-        <v>3015</v>
-      </c>
-      <c r="F6" s="10">
+    <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="15"/>
+      <c r="B18" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" s="9">
+        <v>5985.72</v>
+      </c>
+      <c r="F18" s="10">
         <v>0.54166666666666663</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A4:A6"/>
+  <mergeCells count="6">
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="A10:A12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABF1048E-702E-4457-A5C9-99B30EC16026}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA3BC8AB-114F-492E-8014-D07C2F8C3B98}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="07,01,26" sheetId="101" r:id="rId1"/>
+    <sheet name="08,01,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
   <si>
     <t>КИ</t>
   </si>
@@ -39,19 +39,10 @@
     <t>ЛП</t>
   </si>
   <si>
-    <t>09,01,26</t>
-  </si>
-  <si>
     <t>КСК</t>
   </si>
   <si>
-    <t>ЗПФ</t>
-  </si>
-  <si>
-    <t>10,01,26</t>
-  </si>
-  <si>
-    <t>НВ</t>
+    <t>11,01,26</t>
   </si>
 </sst>
 </file>
@@ -72,7 +63,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -81,68 +72,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="7">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -227,65 +167,16 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -294,52 +185,10 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -724,360 +573,53 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="13.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="16">
+      <c r="A1" s="5">
         <v>1</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="17">
-        <v>15395.74</v>
-      </c>
-      <c r="F1" s="18">
+      <c r="E1" s="1">
+        <v>15389.899999999998</v>
+      </c>
+      <c r="F1" s="2">
         <v>0.375</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19"/>
-      <c r="B2" s="20" t="s">
+      <c r="A2" s="6"/>
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="20" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="20">
-        <v>2072.6999999999998</v>
-      </c>
-      <c r="F2" s="21">
+      <c r="D2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3">
+        <v>1975.4999999999998</v>
+      </c>
+      <c r="F2" s="4">
         <v>0.375</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="2">
-        <v>12250.32</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="16">
-        <v>3</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="17">
-        <v>17206.269999999997</v>
-      </c>
-      <c r="F4" s="18">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="19"/>
-      <c r="B5" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="20">
-        <v>444.00000000000006</v>
-      </c>
-      <c r="F5" s="21">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="13">
-        <v>4</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="7">
-        <v>8556.4000000000015</v>
-      </c>
-      <c r="F6" s="8">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="14"/>
-      <c r="B7" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="11">
-        <v>1312.8</v>
-      </c>
-      <c r="F7" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15"/>
-      <c r="B8" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="9">
-        <v>7342.8</v>
-      </c>
-      <c r="F8" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
-        <v>5</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="5">
-        <v>12544.32</v>
-      </c>
-      <c r="F9" s="6">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="13">
-        <v>6</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="7">
-        <v>3627.5400000000004</v>
-      </c>
-      <c r="F10" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="14"/>
-      <c r="B11" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="11">
-        <v>1229.58</v>
-      </c>
-      <c r="F11" s="12">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="15"/>
-      <c r="B12" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" s="9">
-        <v>12532.46</v>
-      </c>
-      <c r="F12" s="10">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="16">
-        <v>7</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13" s="17">
-        <v>2025</v>
-      </c>
-      <c r="F13" s="18">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A14" s="22"/>
-      <c r="B14" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="C14" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="D14" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14" s="23">
-        <v>14188.970000000001</v>
-      </c>
-      <c r="F14" s="24">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="19"/>
-      <c r="B15" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="C15" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15" s="20">
-        <v>1197.04</v>
-      </c>
-      <c r="F15" s="21">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A16" s="13">
-        <v>8</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16" s="7">
-        <v>4882.13</v>
-      </c>
-      <c r="F16" s="8">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A17" s="14"/>
-      <c r="B17" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17" s="11">
-        <v>6505.7999999999993</v>
-      </c>
-      <c r="F17" s="12">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="15"/>
-      <c r="B18" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E18" s="9">
-        <v>5985.72</v>
-      </c>
-      <c r="F18" s="10">
-        <v>0.54166666666666663</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="A16:A18"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="A10:A12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA3BC8AB-114F-492E-8014-D07C2F8C3B98}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{516A8E92-8009-4D87-96E3-D30ACDBD695F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="08,01,26" sheetId="101" r:id="rId1"/>
+    <sheet name="09,01,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="7">
   <si>
     <t>КИ</t>
   </si>
@@ -43,6 +43,15 @@
   </si>
   <si>
     <t>11,01,26</t>
+  </si>
+  <si>
+    <t>ЗПФ</t>
+  </si>
+  <si>
+    <t>НВ</t>
+  </si>
+  <si>
+    <t>12,01,26</t>
   </si>
 </sst>
 </file>
@@ -63,7 +72,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -76,8 +85,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -167,11 +182,93 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -189,6 +286,51 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -573,53 +715,327 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="5">
+    <row r="1" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="8">
+        <v>11061.36</v>
+      </c>
+      <c r="F1" s="9">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10">
+        <v>2</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="11">
+        <v>11592.84</v>
+      </c>
+      <c r="F2" s="12">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="13">
+        <v>3</v>
+      </c>
+      <c r="B3" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C3" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D3" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="14">
+        <v>7185.22</v>
+      </c>
+      <c r="F3" s="15">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="16"/>
+      <c r="B4" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="17">
+        <v>2242.9000000000005</v>
+      </c>
+      <c r="F4" s="18">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="11">
+        <v>14826.3</v>
+      </c>
+      <c r="F5" s="12">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="7">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1">
-        <v>15389.899999999998</v>
-      </c>
-      <c r="F1" s="2">
+      <c r="E6" s="8">
+        <v>17673.060000000001</v>
+      </c>
+      <c r="F6" s="9">
         <v>0.375</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
-      <c r="B2" s="3" t="s">
+    <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="3">
-        <v>1975.4999999999998</v>
-      </c>
-      <c r="F2" s="4">
-        <v>0.375</v>
+      <c r="C7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="1">
+        <v>2021.5400000000002</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="19"/>
+      <c r="B8" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="20">
+        <v>13816.050000000001</v>
+      </c>
+      <c r="F8" s="21">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="6"/>
+      <c r="B9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F9" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="7">
+        <v>7</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="8">
+        <v>17211.36</v>
+      </c>
+      <c r="F10" s="9">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="5">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="1">
+        <v>3358.6800000000003</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="6"/>
+      <c r="B12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="3">
+        <v>8727.6</v>
+      </c>
+      <c r="F12" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="13">
+        <v>9</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="14">
+        <v>1491.6</v>
+      </c>
+      <c r="F13" s="15">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="16"/>
+      <c r="B14" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="17">
+        <v>8926.84</v>
+      </c>
+      <c r="F14" s="18">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A15" s="5">
+        <v>10</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="1">
+        <v>4416.8</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="6"/>
+      <c r="B16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="3">
+        <v>6702.72</v>
+      </c>
+      <c r="F16" s="4">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:A2"/>
+  <mergeCells count="5">
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A11:A12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{516A8E92-8009-4D87-96E3-D30ACDBD695F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A11E9746-2A13-4BC4-A78F-68AD369198F2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="09,01,26" sheetId="101" r:id="rId1"/>
+    <sheet name="12,01,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="4">
   <si>
     <t>КИ</t>
   </si>
@@ -39,19 +39,10 @@
     <t>ЛП</t>
   </si>
   <si>
-    <t>КСК</t>
-  </si>
-  <si>
-    <t>11,01,26</t>
-  </si>
-  <si>
-    <t>ЗПФ</t>
-  </si>
-  <si>
     <t>НВ</t>
   </si>
   <si>
-    <t>12,01,26</t>
+    <t>14,01,26</t>
   </si>
 </sst>
 </file>
@@ -92,7 +83,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -227,48 +218,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -282,55 +236,19 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -715,327 +633,112 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="14.140625" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7">
+    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="8">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="8">
-        <v>11061.36</v>
-      </c>
-      <c r="F1" s="9">
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1">
+        <v>5632.6200000000008</v>
+      </c>
+      <c r="F1" s="2">
         <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10">
+      <c r="A2" s="9"/>
+      <c r="B2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="11" t="s">
+      <c r="E2" s="3">
+        <v>4526.7000000000007</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="11">
-        <v>11592.84</v>
-      </c>
-      <c r="F2" s="12">
-        <v>0.375</v>
+      <c r="D3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6">
+        <v>14519.400000000001</v>
+      </c>
+      <c r="F3" s="7">
+        <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="13">
+    <row r="4" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="8">
         <v>3</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="14">
-        <v>7185.22</v>
-      </c>
-      <c r="F3" s="15">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="16"/>
-      <c r="B4" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="17">
-        <v>2242.9000000000005</v>
-      </c>
-      <c r="F4" s="18">
-        <v>0.41666666666666669</v>
+      <c r="D4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1">
+        <v>11804.050000000001</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.5</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="10">
-        <v>4</v>
-      </c>
-      <c r="B5" s="11" t="s">
+      <c r="A5" s="9"/>
+      <c r="B5" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="11">
-        <v>14826.3</v>
-      </c>
-      <c r="F5" s="12">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
-        <v>5</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" s="8">
-        <v>17673.060000000001</v>
-      </c>
-      <c r="F6" s="9">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="5">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="1">
-        <v>2021.5400000000002</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="19"/>
-      <c r="B8" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="20">
-        <v>13816.050000000001</v>
-      </c>
-      <c r="F8" s="21">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="6"/>
-      <c r="B9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="3">
-        <v>1500</v>
-      </c>
-      <c r="F9" s="4">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
-        <v>7</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="8">
-        <v>17211.36</v>
-      </c>
-      <c r="F10" s="9">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="5">
-        <v>8</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" s="1">
-        <v>3358.6800000000003</v>
-      </c>
-      <c r="F11" s="2">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="6"/>
-      <c r="B12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="3">
-        <v>8727.6</v>
-      </c>
-      <c r="F12" s="4">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="13">
-        <v>9</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="14">
-        <v>1491.6</v>
-      </c>
-      <c r="F13" s="15">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="16"/>
-      <c r="B14" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="17">
-        <v>8926.84</v>
-      </c>
-      <c r="F14" s="18">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A15" s="5">
-        <v>10</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" s="1">
-        <v>4416.8</v>
-      </c>
-      <c r="F15" s="2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="6"/>
-      <c r="B16" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E16" s="3">
-        <v>6702.72</v>
-      </c>
-      <c r="F16" s="4">
+      <c r="E5" s="3">
+        <v>2330.9300000000003</v>
+      </c>
+      <c r="F5" s="4">
         <v>0.5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A11:A12"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A4:A5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A11E9746-2A13-4BC4-A78F-68AD369198F2}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{001B848D-2FAB-4709-BE89-943DB332F380}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="12,01,26" sheetId="101" r:id="rId1"/>
+    <sheet name="13,01,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="3">
   <si>
     <t>КИ</t>
   </si>
@@ -39,10 +39,7 @@
     <t>ЛП</t>
   </si>
   <si>
-    <t>НВ</t>
-  </si>
-  <si>
-    <t>14,01,26</t>
+    <t>15,01,26</t>
   </si>
 </sst>
 </file>
@@ -83,7 +80,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -101,88 +98,6 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
       <bottom style="medium">
         <color auto="1"/>
       </bottom>
@@ -222,33 +137,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -633,113 +539,53 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="8">
+    <row r="1" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1">
-        <v>5632.6200000000008</v>
-      </c>
-      <c r="F1" s="2">
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2">
+        <v>17914.5</v>
+      </c>
+      <c r="F1" s="3">
         <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9"/>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="4">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="3">
-        <v>4526.7000000000007</v>
-      </c>
-      <c r="F2" s="4">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="6">
-        <v>14519.400000000001</v>
-      </c>
-      <c r="F3" s="7">
+      <c r="E2" s="5">
+        <v>18033.170000000002</v>
+      </c>
+      <c r="F2" s="6">
         <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="8">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="1">
-        <v>11804.050000000001</v>
-      </c>
-      <c r="F4" s="2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9"/>
-      <c r="B5" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="3">
-        <v>2330.9300000000003</v>
-      </c>
-      <c r="F5" s="4">
-        <v>0.5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A4:A5"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{001B848D-2FAB-4709-BE89-943DB332F380}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB61876-01FF-47FC-8F17-CBF7C7AA7A15}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="13,01,26" sheetId="101" r:id="rId1"/>
+    <sheet name="14,01,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="7">
   <si>
     <t>КИ</t>
   </si>
@@ -39,7 +39,19 @@
     <t>ЛП</t>
   </si>
   <si>
-    <t>15,01,26</t>
+    <t>16,01,26</t>
+  </si>
+  <si>
+    <t>КСК</t>
+  </si>
+  <si>
+    <t>17,01,26</t>
+  </si>
+  <si>
+    <t>НВ</t>
+  </si>
+  <si>
+    <t>ЗПФ</t>
   </si>
 </sst>
 </file>
@@ -80,7 +92,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -133,11 +145,130 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -155,6 +286,60 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -539,53 +724,322 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1">
+    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="7">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="8">
+        <v>11332.949999999997</v>
+      </c>
+      <c r="F1" s="9">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10"/>
+      <c r="B2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="11">
+        <v>5843.7</v>
+      </c>
+      <c r="F2" s="12">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="13">
+        <v>2</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="2">
-        <v>17914.5</v>
-      </c>
-      <c r="F1" s="3">
+      <c r="E3" s="14">
+        <v>13280.520000000002</v>
+      </c>
+      <c r="F3" s="15">
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+    <row r="4" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="16"/>
+      <c r="B4" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="D4" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="17">
+        <v>3909.85</v>
+      </c>
+      <c r="F4" s="18">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="7">
+        <v>3</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D5" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="5">
-        <v>18033.170000000002</v>
-      </c>
-      <c r="F2" s="6">
+      <c r="E5" s="8">
+        <v>4138.5599999999995</v>
+      </c>
+      <c r="F5" s="9">
         <v>0.45833333333333331</v>
       </c>
     </row>
+    <row r="6" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10"/>
+      <c r="B6" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="11">
+        <v>3564.8</v>
+      </c>
+      <c r="F6" s="12">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>4</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="5">
+        <v>17705.539999999997</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="7">
+        <v>5</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="8">
+        <v>1493.7000000000003</v>
+      </c>
+      <c r="F8" s="9">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="19"/>
+      <c r="B9" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="20">
+        <v>1568.2799999999997</v>
+      </c>
+      <c r="F9" s="21">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="19"/>
+      <c r="B10" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="20">
+        <v>1362.24</v>
+      </c>
+      <c r="F10" s="21">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="19"/>
+      <c r="B11" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="20">
+        <v>5167.7199999999993</v>
+      </c>
+      <c r="F11" s="21">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="10"/>
+      <c r="B12" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="11">
+        <v>8351.7200000000012</v>
+      </c>
+      <c r="F12" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="13">
+        <v>6</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="14">
+        <v>4936.93</v>
+      </c>
+      <c r="F13" s="15">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A14" s="22"/>
+      <c r="B14" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="23">
+        <v>2166.0299999999997</v>
+      </c>
+      <c r="F14" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="16"/>
+      <c r="B15" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="17">
+        <v>10466.16</v>
+      </c>
+      <c r="F15" s="18">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>7</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="2">
+        <v>12140.16</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0.375</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB61876-01FF-47FC-8F17-CBF7C7AA7A15}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF4D730A-2820-42C9-B05C-BADFA4FB0F9C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="14,01,26" sheetId="101" r:id="rId1"/>
+    <sheet name="15,01,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
   <si>
     <t>КИ</t>
   </si>
@@ -39,19 +39,10 @@
     <t>ЛП</t>
   </si>
   <si>
-    <t>16,01,26</t>
-  </si>
-  <si>
     <t>КСК</t>
   </si>
   <si>
-    <t>17,01,26</t>
-  </si>
-  <si>
-    <t>НВ</t>
-  </si>
-  <si>
-    <t>ЗПФ</t>
+    <t>18,01,26</t>
   </si>
 </sst>
 </file>
@@ -72,7 +63,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -85,64 +76,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="13">
+  <borders count="7">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -227,86 +167,16 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -315,31 +185,10 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -724,321 +573,53 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="7">
+      <c r="A1" s="5">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="8">
-        <v>11332.949999999997</v>
-      </c>
-      <c r="F1" s="9">
+      <c r="E1" s="1">
+        <v>15180.859999999999</v>
+      </c>
+      <c r="F1" s="2">
         <v>0.375</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10"/>
-      <c r="B2" s="11" t="s">
+      <c r="A2" s="6"/>
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="11" t="s">
+      <c r="C2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="11">
-        <v>5843.7</v>
-      </c>
-      <c r="F2" s="12">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="13">
-        <v>2</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="14" t="s">
+      <c r="D2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="14">
-        <v>13280.520000000002</v>
-      </c>
-      <c r="F3" s="15">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="16"/>
-      <c r="B4" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="17">
-        <v>3909.85</v>
-      </c>
-      <c r="F4" s="18">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="7">
-        <v>3</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="8">
-        <v>4138.5599999999995</v>
-      </c>
-      <c r="F5" s="9">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
-      <c r="B6" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="11">
-        <v>3564.8</v>
-      </c>
-      <c r="F6" s="12">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <v>4</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="5">
-        <v>17705.539999999997</v>
-      </c>
-      <c r="F7" s="6">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="7">
-        <v>5</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="8">
-        <v>1493.7000000000003</v>
-      </c>
-      <c r="F8" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="19"/>
-      <c r="B9" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="C9" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="20">
-        <v>1568.2799999999997</v>
-      </c>
-      <c r="F9" s="21">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="19"/>
-      <c r="B10" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="20">
-        <v>1362.24</v>
-      </c>
-      <c r="F10" s="21">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="19"/>
-      <c r="B11" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" s="20">
-        <v>5167.7199999999993</v>
-      </c>
-      <c r="F11" s="21">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="10"/>
-      <c r="B12" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="11">
-        <v>8351.7200000000012</v>
-      </c>
-      <c r="F12" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="13">
-        <v>6</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="14">
-        <v>4936.93</v>
-      </c>
-      <c r="F13" s="15">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A14" s="22"/>
-      <c r="B14" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="C14" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="23">
-        <v>2166.0299999999997</v>
-      </c>
-      <c r="F14" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="16"/>
-      <c r="B15" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" s="17">
-        <v>10466.16</v>
-      </c>
-      <c r="F15" s="18">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>7</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E16" s="2">
-        <v>12140.16</v>
-      </c>
-      <c r="F16" s="3">
+      <c r="E2" s="3">
+        <v>2377.9199999999996</v>
+      </c>
+      <c r="F2" s="4">
         <v>0.375</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="1">
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A8:A12"/>
-    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF4D730A-2820-42C9-B05C-BADFA4FB0F9C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA0FA2E2-53CA-4AE3-A311-60BFEFE0BBB8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="8">
   <si>
     <t>КИ</t>
   </si>
@@ -43,6 +43,18 @@
   </si>
   <si>
     <t>18,01,26</t>
+  </si>
+  <si>
+    <t>ЗПФ</t>
+  </si>
+  <si>
+    <t>НВ</t>
+  </si>
+  <si>
+    <t>19,01,26</t>
+  </si>
+  <si>
+    <t>20,01,26</t>
   </si>
 </sst>
 </file>
@@ -63,7 +75,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -76,8 +88,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -167,11 +185,93 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -189,6 +289,60 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -573,53 +727,511 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="5">
+    <row r="1" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1">
-        <v>15180.859999999999</v>
-      </c>
-      <c r="F1" s="2">
+      <c r="E1" s="8">
+        <v>13880.28</v>
+      </c>
+      <c r="F1" s="9">
         <v>0.375</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
-      <c r="B2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="A2" s="10">
+        <v>2</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="11">
+        <v>9602.64</v>
+      </c>
+      <c r="F2" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="13">
+        <v>3</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="14">
+        <v>6405.5300000000007</v>
+      </c>
+      <c r="F3" s="15">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="16"/>
+      <c r="B4" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="17">
+        <v>7049</v>
+      </c>
+      <c r="F4" s="18">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="11">
+        <v>17714.829999999998</v>
+      </c>
+      <c r="F5" s="12">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="13">
+        <v>5</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="14">
+        <v>3575.6900000000005</v>
+      </c>
+      <c r="F6" s="15">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="19"/>
+      <c r="B7" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="20">
+        <v>17.760000000000002</v>
+      </c>
+      <c r="F7" s="21">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="19"/>
+      <c r="B8" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="20">
+        <v>2990.49</v>
+      </c>
+      <c r="F8" s="21">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="19"/>
+      <c r="B9" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="20">
+        <v>28.860000000000003</v>
+      </c>
+      <c r="F9" s="21">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="16"/>
+      <c r="B10" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="17">
+        <v>9196.8599999999988</v>
+      </c>
+      <c r="F10" s="18">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="5">
+        <v>6</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="3">
-        <v>2377.9199999999996</v>
-      </c>
-      <c r="F2" s="4">
+      <c r="E11" s="1">
+        <v>13939.980000000001</v>
+      </c>
+      <c r="F11" s="2">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="22"/>
+      <c r="B12" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="23">
+        <v>3493.17</v>
+      </c>
+      <c r="F12" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="6"/>
+      <c r="B13" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="3">
+        <v>44.400000000000006</v>
+      </c>
+      <c r="F13" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A14" s="13">
+        <v>7</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E14" s="14">
+        <v>7347.9</v>
+      </c>
+      <c r="F14" s="15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A15" s="19"/>
+      <c r="B15" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="20">
+        <v>5437.0800000000008</v>
+      </c>
+      <c r="F15" s="21">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A16" s="19"/>
+      <c r="B16" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="20">
+        <v>44.400000000000006</v>
+      </c>
+      <c r="F16" s="21">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A17" s="19"/>
+      <c r="B17" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="20">
+        <v>2440.92</v>
+      </c>
+      <c r="F17" s="21">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="16"/>
+      <c r="B18" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="17">
+        <v>1938.3600000000001</v>
+      </c>
+      <c r="F18" s="18">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="10">
+        <v>8</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E19" s="11">
+        <v>17721.960000000003</v>
+      </c>
+      <c r="F19" s="12">
         <v>0.375</v>
       </c>
     </row>
+    <row r="20" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A20" s="13">
+        <v>9</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="14">
+        <v>7957.7999999999993</v>
+      </c>
+      <c r="F20" s="15">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="16"/>
+      <c r="B21" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" s="17">
+        <v>1628.16</v>
+      </c>
+      <c r="F21" s="18">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A22" s="5">
+        <v>10</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="1">
+        <v>7814.4400000000014</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="6"/>
+      <c r="B23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="3">
+        <v>5664.4800000000005</v>
+      </c>
+      <c r="F23" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A24" s="13">
+        <v>11</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="14">
+        <v>4014.96</v>
+      </c>
+      <c r="F24" s="15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A25" s="19"/>
+      <c r="B25" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E25" s="20">
+        <v>4923.2</v>
+      </c>
+      <c r="F25" s="21">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="16"/>
+      <c r="B26" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="17">
+        <v>4802.6799999999994</v>
+      </c>
+      <c r="F26" s="18">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:A2"/>
+  <mergeCells count="7">
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A6:A10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9542F496-9BCD-4239-BB21-486F47086F98}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88231011-54CD-4B59-B148-219BE240A6FA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="19,01,26" sheetId="101" r:id="rId1"/>
+    <sheet name="20,01,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="3">
   <si>
     <t>КИ</t>
   </si>
@@ -39,7 +39,7 @@
     <t>ЛП</t>
   </si>
   <si>
-    <t>21,01,26</t>
+    <t>22,01,26</t>
   </si>
 </sst>
 </file>
@@ -60,7 +60,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -73,8 +73,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -127,11 +133,93 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -140,6 +228,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -524,33 +639,114 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1">
+      <c r="A1" s="4">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="2">
-        <v>17421.900000000001</v>
-      </c>
-      <c r="F1" s="3">
+      <c r="E1" s="5">
+        <v>18067.14</v>
+      </c>
+      <c r="F1" s="6">
         <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>17970.34</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="11">
+        <v>3</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="7">
+        <v>10775.11</v>
+      </c>
+      <c r="F3" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="12"/>
+      <c r="B4" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="9">
+        <v>6525</v>
+      </c>
+      <c r="F4" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2">
+        <v>10156.560000000001</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0.54166666666666663</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A3:A4"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88231011-54CD-4B59-B148-219BE240A6FA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A578175-202E-43A2-85DF-44B0E54D72C6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="20,01,26" sheetId="101" r:id="rId1"/>
+    <sheet name="21,01,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,15 +31,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="6">
   <si>
     <t>КИ</t>
   </si>
   <si>
-    <t>ЛП</t>
+    <t>23,01,26</t>
   </si>
   <si>
-    <t>22,01,26</t>
+    <t>КСК</t>
+  </si>
+  <si>
+    <t>24,01,26</t>
+  </si>
+  <si>
+    <t>ЗПФ</t>
+  </si>
+  <si>
+    <t>НВ</t>
   </si>
 </sst>
 </file>
@@ -80,7 +89,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -215,11 +224,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -251,10 +297,37 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -639,88 +712,88 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4">
+    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="17">
         <v>1</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="7">
+        <v>11200.539999999999</v>
+      </c>
+      <c r="F1" s="8">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="18"/>
+      <c r="B2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="5">
-        <v>18067.14</v>
-      </c>
-      <c r="F1" s="6">
+      <c r="D2" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="9">
+        <v>6001.119999999999</v>
+      </c>
+      <c r="F2" s="10">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2">
+        <v>17696.570000000003</v>
+      </c>
+      <c r="F3" s="3">
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+    <row r="4" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="2">
-        <v>17970.34</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="11">
-        <v>3</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="7">
-        <v>10775.11</v>
-      </c>
-      <c r="F3" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
-      <c r="B4" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="9">
-        <v>6525</v>
-      </c>
-      <c r="F4" s="10">
-        <v>0.5</v>
+      <c r="E4" s="5">
+        <v>17749.739999999998</v>
+      </c>
+      <c r="F4" s="6">
+        <v>0.375</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -728,24 +801,179 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2">
+        <v>11049.6</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="2">
-        <v>10156.560000000001</v>
-      </c>
-      <c r="F5" s="3">
-        <v>0.54166666666666663</v>
+      <c r="D6" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="5">
+        <v>12942.6</v>
+      </c>
+      <c r="F6" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="19">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="11">
+        <v>7087.78</v>
+      </c>
+      <c r="F7" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="20"/>
+      <c r="B8" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="13">
+        <v>2183.4000000000005</v>
+      </c>
+      <c r="F8" s="14">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="21"/>
+      <c r="B9" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="15">
+        <v>8039.09</v>
+      </c>
+      <c r="F9" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="17">
+        <v>7</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="7">
+        <v>11630.26</v>
+      </c>
+      <c r="F10" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="18"/>
+      <c r="B11" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="9">
+        <v>5785.2</v>
+      </c>
+      <c r="F11" s="10">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="19">
+        <v>8</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="11">
+        <v>6120.4800000000014</v>
+      </c>
+      <c r="F12" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="21"/>
+      <c r="B13" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="15">
+        <v>11037.220000000001</v>
+      </c>
+      <c r="F13" s="16">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A3:A4"/>
+  <mergeCells count="4">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A578175-202E-43A2-85DF-44B0E54D72C6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4723CA76-201E-4ECB-81DA-DD6593742387}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="21,01,26" sheetId="101" r:id="rId1"/>
+    <sheet name="22,01,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,24 +31,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
   <si>
     <t>КИ</t>
-  </si>
-  <si>
-    <t>23,01,26</t>
   </si>
   <si>
     <t>КСК</t>
   </si>
   <si>
-    <t>24,01,26</t>
+    <t>25,01,26</t>
   </si>
   <si>
-    <t>ЗПФ</t>
-  </si>
-  <si>
-    <t>НВ</t>
+    <t>ЛП</t>
   </si>
 </sst>
 </file>
@@ -69,7 +63,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -78,68 +72,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="7">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -224,77 +167,16 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -303,31 +185,10 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -712,268 +573,53 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="14.140625" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="17">
+      <c r="A1" s="5">
         <v>1</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="7">
-        <v>11200.539999999999</v>
-      </c>
-      <c r="F1" s="8">
+      <c r="E1" s="1">
+        <v>15673.199999999999</v>
+      </c>
+      <c r="F1" s="2">
         <v>0.375</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18"/>
-      <c r="B2" s="9" t="s">
+      <c r="A2" s="6"/>
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="9" t="s">
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="9">
-        <v>6001.119999999999</v>
-      </c>
-      <c r="F2" s="10">
+      <c r="D2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="3">
+        <v>1906.5600000000004</v>
+      </c>
+      <c r="F2" s="4">
         <v>0.375</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2">
-        <v>17696.570000000003</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="5">
-        <v>17749.739999999998</v>
-      </c>
-      <c r="F4" s="6">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E5" s="2">
-        <v>11049.6</v>
-      </c>
-      <c r="F5" s="3">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
-        <v>5</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" s="5">
-        <v>12942.6</v>
-      </c>
-      <c r="F6" s="6">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="19">
-        <v>6</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="11">
-        <v>7087.78</v>
-      </c>
-      <c r="F7" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="20"/>
-      <c r="B8" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="13">
-        <v>2183.4000000000005</v>
-      </c>
-      <c r="F8" s="14">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="21"/>
-      <c r="B9" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="15">
-        <v>8039.09</v>
-      </c>
-      <c r="F9" s="16">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="17">
-        <v>7</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="7">
-        <v>11630.26</v>
-      </c>
-      <c r="F10" s="8">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="18"/>
-      <c r="B11" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" s="9">
-        <v>5785.2</v>
-      </c>
-      <c r="F11" s="10">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="19">
-        <v>8</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="11">
-        <v>6120.4800000000014</v>
-      </c>
-      <c r="F12" s="12">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="21"/>
-      <c r="B13" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="15">
-        <v>11037.220000000001</v>
-      </c>
-      <c r="F13" s="16">
-        <v>0.5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="1">
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4723CA76-201E-4ECB-81DA-DD6593742387}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B56DA1B1-B78A-4B1E-B3FE-F4318A41DD49}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="22,01,26" sheetId="101" r:id="rId1"/>
+    <sheet name="23,01,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="7">
   <si>
     <t>КИ</t>
   </si>
@@ -43,6 +43,15 @@
   </si>
   <si>
     <t>ЛП</t>
+  </si>
+  <si>
+    <t>ЗПФ</t>
+  </si>
+  <si>
+    <t>НВ</t>
+  </si>
+  <si>
+    <t>26,01,26</t>
   </si>
 </sst>
 </file>
@@ -63,7 +72,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -76,8 +85,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -167,11 +182,93 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -189,6 +286,51 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -573,53 +715,403 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="13.85546875" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="5">
+    <row r="1" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="7">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="8">
+        <v>12598.199999999997</v>
+      </c>
+      <c r="F1" s="9">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10">
+        <v>2</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="11">
+        <v>8971.32</v>
+      </c>
+      <c r="F2" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7">
+        <v>3</v>
+      </c>
+      <c r="B3" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="8">
+        <v>14017.2</v>
+      </c>
+      <c r="F3" s="9">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10">
+        <v>4</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="11">
+        <v>10692.560000000001</v>
+      </c>
+      <c r="F4" s="12">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="7">
+        <v>5</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1">
-        <v>15673.199999999999</v>
-      </c>
-      <c r="F1" s="2">
+      <c r="E5" s="8">
+        <v>17759.920000000002</v>
+      </c>
+      <c r="F5" s="9">
         <v>0.375</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
-      <c r="B2" s="3" t="s">
+    <row r="6" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="5">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="C6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="3">
-        <v>1906.5600000000004</v>
-      </c>
-      <c r="F2" s="4">
-        <v>0.375</v>
+      <c r="E6" s="1">
+        <v>3929.42</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="13"/>
+      <c r="B7" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="14">
+        <v>1657.8299999999997</v>
+      </c>
+      <c r="F7" s="15">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="13"/>
+      <c r="B8" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="14">
+        <v>2325</v>
+      </c>
+      <c r="F8" s="15">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="6"/>
+      <c r="B9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="3">
+        <v>9985.5000000000018</v>
+      </c>
+      <c r="F9" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="16">
+        <v>7</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="17">
+        <v>14195.099999999999</v>
+      </c>
+      <c r="F10" s="18">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="19"/>
+      <c r="B11" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="20">
+        <v>2917.7400000000002</v>
+      </c>
+      <c r="F11" s="21">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="5">
+        <v>8</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" s="1">
+        <v>7906.56</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="13"/>
+      <c r="B13" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="14">
+        <v>5870.1600000000008</v>
+      </c>
+      <c r="F13" s="15">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="6"/>
+      <c r="B14" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3">
+        <v>3555.46</v>
+      </c>
+      <c r="F14" s="4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A15" s="16">
+        <v>9</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="17">
+        <v>7136.8</v>
+      </c>
+      <c r="F15" s="18">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="19"/>
+      <c r="B16" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="20">
+        <v>5992.3200000000006</v>
+      </c>
+      <c r="F16" s="21">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A17" s="5">
+        <v>10</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="1">
+        <v>5292.56</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="6"/>
+      <c r="B18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="3">
+        <v>6446.24</v>
+      </c>
+      <c r="F18" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="7">
+        <v>11</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" s="8">
+        <v>7969.2</v>
+      </c>
+      <c r="F19" s="9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="10">
+        <v>12</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="11">
+        <v>11050.04</v>
+      </c>
+      <c r="F20" s="12">
+        <v>0.54166666666666663</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:A2"/>
+  <mergeCells count="5">
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="A15:A16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B56DA1B1-B78A-4B1E-B3FE-F4318A41DD49}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5DED378-B5BC-482A-A9B5-9EB3A56E3E96}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="23,01,26" sheetId="101" r:id="rId1"/>
+    <sheet name="26,01,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,27 +31,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="4">
   <si>
     <t>КИ</t>
-  </si>
-  <si>
-    <t>КСК</t>
-  </si>
-  <si>
-    <t>25,01,26</t>
   </si>
   <si>
     <t>ЛП</t>
   </si>
   <si>
-    <t>ЗПФ</t>
-  </si>
-  <si>
     <t>НВ</t>
   </si>
   <si>
-    <t>26,01,26</t>
+    <t>28,01,26</t>
   </si>
 </sst>
 </file>
@@ -92,7 +83,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -227,76 +218,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -306,31 +233,22 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -715,403 +633,112 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7">
+    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="8">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="8">
-        <v>12598.199999999997</v>
-      </c>
-      <c r="F1" s="9">
-        <v>0.375</v>
+      <c r="E1" s="4">
+        <v>5868.4800000000005</v>
+      </c>
+      <c r="F1" s="5">
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10">
+      <c r="A2" s="9"/>
+      <c r="B2" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="11">
-        <v>8971.32</v>
-      </c>
-      <c r="F2" s="12">
+      <c r="E2" s="6">
+        <v>5357.92</v>
+      </c>
+      <c r="F2" s="7">
         <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="D3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>15557.28</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="8">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="8" t="s">
+      <c r="C4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="8">
-        <v>14017.2</v>
-      </c>
-      <c r="F3" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10">
-        <v>4</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="11">
-        <v>10692.560000000001</v>
-      </c>
-      <c r="F4" s="12">
-        <v>0.45833333333333331</v>
+      <c r="D4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4">
+        <v>12754.819999999998</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0.5</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
-        <v>5</v>
-      </c>
-      <c r="B5" s="8" t="s">
+      <c r="A5" s="9"/>
+      <c r="B5" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="8" t="s">
+      <c r="C5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="8">
-        <v>17759.920000000002</v>
-      </c>
-      <c r="F5" s="9">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="5">
-        <v>6</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="1">
-        <v>3929.42</v>
-      </c>
-      <c r="F6" s="2">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="14">
-        <v>1657.8299999999997</v>
-      </c>
-      <c r="F7" s="15">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="14">
-        <v>2325</v>
-      </c>
-      <c r="F8" s="15">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="6"/>
-      <c r="B9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="3">
-        <v>9985.5000000000018</v>
-      </c>
-      <c r="F9" s="4">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="16">
-        <v>7</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="17">
-        <v>14195.099999999999</v>
-      </c>
-      <c r="F10" s="18">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="19"/>
-      <c r="B11" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" s="20">
-        <v>2917.7400000000002</v>
-      </c>
-      <c r="F11" s="21">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="5">
-        <v>8</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E12" s="1">
-        <v>7906.56</v>
-      </c>
-      <c r="F12" s="2">
+      <c r="E5" s="6">
+        <v>1703.0899999999997</v>
+      </c>
+      <c r="F5" s="7">
         <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="14">
-        <v>5870.1600000000008</v>
-      </c>
-      <c r="F13" s="15">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="6"/>
-      <c r="B14" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3">
-        <v>3555.46</v>
-      </c>
-      <c r="F14" s="4">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A15" s="16">
-        <v>9</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="E15" s="17">
-        <v>7136.8</v>
-      </c>
-      <c r="F15" s="18">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="19"/>
-      <c r="B16" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="E16" s="20">
-        <v>5992.3200000000006</v>
-      </c>
-      <c r="F16" s="21">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A17" s="5">
-        <v>10</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E17" s="1">
-        <v>5292.56</v>
-      </c>
-      <c r="F17" s="2">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="6"/>
-      <c r="B18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E18" s="3">
-        <v>6446.24</v>
-      </c>
-      <c r="F18" s="4">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
-        <v>11</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E19" s="8">
-        <v>7969.2</v>
-      </c>
-      <c r="F19" s="9">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="10">
-        <v>12</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="E20" s="11">
-        <v>11050.04</v>
-      </c>
-      <c r="F20" s="12">
-        <v>0.54166666666666663</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="A15:A16"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A4:A5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5DED378-B5BC-482A-A9B5-9EB3A56E3E96}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6269DFD-8A7C-47DA-975A-54FD1F40DF4C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="26,01,26" sheetId="101" r:id="rId1"/>
+    <sheet name="27,01,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="3">
   <si>
     <t>КИ</t>
   </si>
@@ -39,10 +39,7 @@
     <t>ЛП</t>
   </si>
   <si>
-    <t>НВ</t>
-  </si>
-  <si>
-    <t>28,01,26</t>
+    <t>29,01,26</t>
   </si>
 </sst>
 </file>
@@ -222,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -233,22 +230,31 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -636,109 +642,110 @@
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="8">
+    <row r="1" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4">
-        <v>5868.4800000000005</v>
-      </c>
-      <c r="F1" s="5">
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2">
+        <v>17976.520000000004</v>
+      </c>
+      <c r="F1" s="3">
         <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9"/>
-      <c r="B2" s="6" t="s">
+      <c r="A2" s="4">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="5">
+        <v>18027.259999999998</v>
+      </c>
+      <c r="F2" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="7">
         <v>3</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="B3" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="6">
-        <v>5357.92</v>
-      </c>
-      <c r="F2" s="7">
-        <v>0.41666666666666669</v>
+      <c r="D3" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="8">
+        <v>13332.490000000002</v>
+      </c>
+      <c r="F3" s="9">
+        <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+    <row r="4" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10"/>
+      <c r="B4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="D4" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="2">
-        <v>15557.28</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="8">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="4">
-        <v>12754.819999999998</v>
-      </c>
-      <c r="F4" s="5">
+      <c r="E4" s="11">
+        <v>4003.7999999999997</v>
+      </c>
+      <c r="F4" s="12">
         <v>0.5</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9"/>
-      <c r="B5" s="6" t="s">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="6" t="s">
+      <c r="C5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="6">
-        <v>1703.0899999999997</v>
-      </c>
-      <c r="F5" s="7">
-        <v>0.5</v>
+      <c r="E5" s="5">
+        <v>18187.68</v>
+      </c>
+      <c r="F5" s="6">
+        <v>0.54166666666666663</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A4:A5"/>
+  <mergeCells count="1">
+    <mergeCell ref="A3:A4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6269DFD-8A7C-47DA-975A-54FD1F40DF4C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A970CDC2-B9D7-44D5-9F94-050C8585AB04}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="27,01,26" sheetId="101" r:id="rId1"/>
+    <sheet name="28,01,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,15 +31,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="6">
   <si>
     <t>КИ</t>
   </si>
   <si>
-    <t>ЛП</t>
+    <t>30,01,26</t>
   </si>
   <si>
-    <t>29,01,26</t>
+    <t>КСК</t>
+  </si>
+  <si>
+    <t>31,01,26</t>
+  </si>
+  <si>
+    <t>НВ</t>
+  </si>
+  <si>
+    <t>ЗПФ</t>
   </si>
 </sst>
 </file>
@@ -80,7 +89,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -215,21 +224,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -239,22 +276,49 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -639,113 +703,324 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1">
+    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="8">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="4">
+        <v>13135.38</v>
+      </c>
+      <c r="F1" s="5">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9"/>
+      <c r="B2" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="2">
-        <v>17976.520000000004</v>
-      </c>
-      <c r="F1" s="3">
+      <c r="D2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="6">
+        <v>4379.0999999999995</v>
+      </c>
+      <c r="F2" s="7">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2">
+        <v>17748.520000000004</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="8">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="4">
+        <v>1282.92</v>
+      </c>
+      <c r="F4" s="5">
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+    <row r="5" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="10"/>
+      <c r="B5" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="11">
+        <v>1520.64</v>
+      </c>
+      <c r="F5" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="10"/>
+      <c r="B6" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="11">
+        <v>8143.3200000000006</v>
+      </c>
+      <c r="F6" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="9"/>
+      <c r="B7" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="6">
+        <v>6269.04</v>
+      </c>
+      <c r="F7" s="7">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>4</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="5">
-        <v>18027.259999999998</v>
-      </c>
-      <c r="F2" s="6">
+      <c r="E8" s="2">
+        <v>12531.120000000003</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="8">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="4">
+        <v>11229.630000000001</v>
+      </c>
+      <c r="F9" s="5">
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="7">
-        <v>3</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="8">
-        <v>13332.490000000002</v>
-      </c>
-      <c r="F3" s="9">
+    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="9"/>
+      <c r="B10" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="6">
+        <v>6592.4400000000005</v>
+      </c>
+      <c r="F10" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="13">
+        <v>6</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="14">
+        <v>12621.18</v>
+      </c>
+      <c r="F11" s="15">
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10"/>
-      <c r="B4" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="11">
-        <v>4003.7999999999997</v>
-      </c>
-      <c r="F4" s="12">
+    <row r="12" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="16"/>
+      <c r="B12" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="17">
+        <v>5229.0499999999993</v>
+      </c>
+      <c r="F12" s="18">
         <v>0.5</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="5">
-        <v>18187.68</v>
-      </c>
-      <c r="F5" s="6">
+    <row r="13" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="8">
+        <v>7</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="4">
+        <v>8038.5</v>
+      </c>
+      <c r="F13" s="5">
         <v>0.54166666666666663</v>
       </c>
     </row>
+    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="9"/>
+      <c r="B14" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="6">
+        <v>9674.1399999999976</v>
+      </c>
+      <c r="F14" s="7">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A15" s="13">
+        <v>8</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="14">
+        <v>7399.2</v>
+      </c>
+      <c r="F15" s="15">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="16"/>
+      <c r="B16" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" s="17">
+        <v>7845.42</v>
+      </c>
+      <c r="F16" s="18">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A3:A4"/>
+  <mergeCells count="6">
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A11:A12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A970CDC2-B9D7-44D5-9F94-050C8585AB04}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{336AB06D-5F6D-41B7-BA9B-97F1146E2A7D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="28,01,26" sheetId="101" r:id="rId1"/>
+    <sheet name="29,01,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,24 +31,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
   <si>
     <t>КИ</t>
-  </si>
-  <si>
-    <t>30,01,26</t>
   </si>
   <si>
     <t>КСК</t>
   </si>
   <si>
-    <t>31,01,26</t>
+    <t>01,02,26</t>
   </si>
   <si>
-    <t>НВ</t>
-  </si>
-  <si>
-    <t>ЗПФ</t>
+    <t>ЛП</t>
   </si>
 </sst>
 </file>
@@ -69,7 +63,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -82,14 +76,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="13">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -179,103 +167,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -292,33 +189,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -703,324 +573,53 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="8">
+      <c r="A1" s="5">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4">
-        <v>13135.38</v>
-      </c>
-      <c r="F1" s="5">
+      <c r="E1" s="1">
+        <v>16368.32</v>
+      </c>
+      <c r="F1" s="2">
         <v>0.375</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9"/>
-      <c r="B2" s="6" t="s">
+      <c r="A2" s="6"/>
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="6">
-        <v>4379.0999999999995</v>
-      </c>
-      <c r="F2" s="7">
+      <c r="D2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="3">
+        <v>1070.7</v>
+      </c>
+      <c r="F2" s="4">
         <v>0.375</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2">
-        <v>17748.520000000004</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="8">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="4">
-        <v>1282.92</v>
-      </c>
-      <c r="F4" s="5">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="10"/>
-      <c r="B5" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="11">
-        <v>1520.64</v>
-      </c>
-      <c r="F5" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="10"/>
-      <c r="B6" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="11">
-        <v>8143.3200000000006</v>
-      </c>
-      <c r="F6" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="9"/>
-      <c r="B7" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="6">
-        <v>6269.04</v>
-      </c>
-      <c r="F7" s="7">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>4</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E8" s="2">
-        <v>12531.120000000003</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="8">
-        <v>5</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="4">
-        <v>11229.630000000001</v>
-      </c>
-      <c r="F9" s="5">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="9"/>
-      <c r="B10" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="6">
-        <v>6592.4400000000005</v>
-      </c>
-      <c r="F10" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="13">
-        <v>6</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="14">
-        <v>12621.18</v>
-      </c>
-      <c r="F11" s="15">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="16"/>
-      <c r="B12" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="17">
-        <v>5229.0499999999993</v>
-      </c>
-      <c r="F12" s="18">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="8">
-        <v>7</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="4">
-        <v>8038.5</v>
-      </c>
-      <c r="F13" s="5">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="9"/>
-      <c r="B14" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="6">
-        <v>9674.1399999999976</v>
-      </c>
-      <c r="F14" s="7">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A15" s="13">
-        <v>8</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="14">
-        <v>7399.2</v>
-      </c>
-      <c r="F15" s="15">
-        <v>0.58333333333333337</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="16"/>
-      <c r="B16" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="E16" s="17">
-        <v>7845.42</v>
-      </c>
-      <c r="F16" s="18">
-        <v>0.58333333333333337</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="A15:A16"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A11:A12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -1,28 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\графики\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{336AB06D-5F6D-41B7-BA9B-97F1146E2A7D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85253AB5-414D-437F-8C55-0D68793EF5A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="29,01,26" sheetId="101" r:id="rId1"/>
+    <sheet name="26,06,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
@@ -31,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="8">
   <si>
     <t>КИ</t>
   </si>
@@ -39,10 +33,22 @@
     <t>КСК</t>
   </si>
   <si>
-    <t>01,02,26</t>
+    <t>ЛП</t>
   </si>
   <si>
-    <t>ЛП</t>
+    <t>29,06,26</t>
+  </si>
+  <si>
+    <t>30,06,26</t>
+  </si>
+  <si>
+    <t>ЗПФ</t>
+  </si>
+  <si>
+    <t>28,06,26</t>
+  </si>
+  <si>
+    <t>НВ</t>
   </si>
 </sst>
 </file>
@@ -63,7 +69,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -72,12 +78,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -167,12 +179,130 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -183,6 +313,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -573,53 +712,408 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="5">
+    <row r="1" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2">
+        <v>17764.18</v>
+      </c>
+      <c r="F1" s="3">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="1">
-        <v>16368.32</v>
-      </c>
-      <c r="F1" s="2">
+      <c r="E2" s="5">
+        <v>17712.7</v>
+      </c>
+      <c r="F2" s="6">
         <v>0.375</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
-      <c r="B2" s="3" t="s">
+    <row r="3" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2">
+        <v>10284</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="17">
+        <v>4</v>
+      </c>
+      <c r="B4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="3">
-        <v>1070.7</v>
-      </c>
-      <c r="F2" s="4">
-        <v>0.375</v>
+      <c r="E4" s="7">
+        <v>4615.8</v>
+      </c>
+      <c r="F4" s="8">
+        <v>0.35416666666666669</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="18"/>
+      <c r="B5" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="9">
+        <v>4386.6000000000004</v>
+      </c>
+      <c r="F5" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="19"/>
+      <c r="B6" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E6" s="11">
+        <v>3982.5</v>
+      </c>
+      <c r="F6" s="12">
+        <v>0.35416666666666669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="20">
+        <v>5</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="13">
+        <v>10358.920000000002</v>
+      </c>
+      <c r="F7" s="14">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="21"/>
+      <c r="B8" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="15">
+        <v>2163.3199999999997</v>
+      </c>
+      <c r="F8" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>6</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="5">
+        <v>11784.08</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>7</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="2">
+        <v>11481.999999999998</v>
+      </c>
+      <c r="F10" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="17">
+        <v>8</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="7">
+        <v>6328.52</v>
+      </c>
+      <c r="F11" s="8">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="19"/>
+      <c r="B12" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="11">
+        <v>4942.92</v>
+      </c>
+      <c r="F12" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>9</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="2">
+        <v>11669.64</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="5">
+        <v>15364.89</v>
+      </c>
+      <c r="F14" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="2">
+        <v>17510.97</v>
+      </c>
+      <c r="F15" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="5">
+        <v>14546.880000000003</v>
+      </c>
+      <c r="F16" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>13</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="2">
+        <v>13186.489999999998</v>
+      </c>
+      <c r="F17" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A18" s="17">
+        <v>14</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="7">
+        <v>9013.7999999999993</v>
+      </c>
+      <c r="F18" s="8">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="19"/>
+      <c r="B19" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E19" s="11">
+        <v>7599.9100000000008</v>
+      </c>
+      <c r="F19" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>15</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="2">
+        <v>17506.8</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0.45833333333333331</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:A2"/>
+  <mergeCells count="4">
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A18:A19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94CF69F4-E08A-4923-8C15-34F29CFDC69F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB57BB68-662B-48BB-9C00-53D0BAC269D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="26,06,26" sheetId="101" r:id="rId1"/>
+    <sheet name="26-27,06,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="8">
   <si>
     <t>КИ</t>
   </si>
@@ -34,6 +34,21 @@
   </si>
   <si>
     <t>29,06,26</t>
+  </si>
+  <si>
+    <t>КСК</t>
+  </si>
+  <si>
+    <t>30,06,26</t>
+  </si>
+  <si>
+    <t>ЗПФ</t>
+  </si>
+  <si>
+    <t>28,06,26</t>
+  </si>
+  <si>
+    <t>НВ</t>
   </si>
 </sst>
 </file>
@@ -54,7 +69,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -67,8 +82,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -121,11 +142,130 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -134,6 +274,72 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -518,33 +724,414 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1">
+      <c r="A1" s="4">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5">
+        <v>17764.18</v>
+      </c>
+      <c r="F1" s="6">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2">
+        <v>17712.7</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>3</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="2">
+      <c r="E3" s="5">
+        <v>10284</v>
+      </c>
+      <c r="F3" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="7">
+        <v>4</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="8">
+        <v>4615.8</v>
+      </c>
+      <c r="F4" s="9">
+        <v>0.35416666666666669</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="10"/>
+      <c r="B5" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="11">
+        <v>4386.6000000000004</v>
+      </c>
+      <c r="F5" s="12">
+        <v>0.35416666666666669</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13"/>
+      <c r="B6" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="14">
+        <v>3982.5</v>
+      </c>
+      <c r="F6" s="15">
+        <v>0.35416666666666669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="16">
+        <v>5</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="17">
+        <v>10358.920000000002</v>
+      </c>
+      <c r="F7" s="18">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="19"/>
+      <c r="B8" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="20">
+        <v>2163.3199999999997</v>
+      </c>
+      <c r="F8" s="21">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="2">
+        <v>11481.999999999998</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="23">
+        <v>7</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="24">
+        <v>7253.24</v>
+      </c>
+      <c r="F10" s="25">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="19"/>
+      <c r="B11" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="20">
+        <v>4942.92</v>
+      </c>
+      <c r="F11" s="21">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="22">
+        <v>8</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="14">
+        <v>11669.64</v>
+      </c>
+      <c r="F12" s="15">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="5">
+        <v>15364.89</v>
+      </c>
+      <c r="F13" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>10</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="2">
+        <v>17510.97</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <f>MAX(A2:A14)+1</f>
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="5">
+        <v>14546.880000000003</v>
+      </c>
+      <c r="F15" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <f>MAX(A3:A15)+1</f>
+        <v>12</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="2">
+        <v>13186.489999999998</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A17" s="16">
+        <f>MAX(A4:A16)+1</f>
+        <v>13</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="17">
+        <v>9013.7999999999993</v>
+      </c>
+      <c r="F17" s="18">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="19"/>
+      <c r="B18" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="20">
+        <v>7599.9100000000008</v>
+      </c>
+      <c r="F18" s="21">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <f>MAX(A6:A18)+1</f>
+        <v>14</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="2">
+        <v>17506.8</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <f>MAX(A7:A19)+1</f>
+        <v>15</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E20" s="5">
         <v>17849.460000000003</v>
       </c>
-      <c r="F1" s="3">
+      <c r="F20" s="6">
         <v>0.58333333333333337</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A17:A18"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -1,22 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\графики\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB57BB68-662B-48BB-9C00-53D0BAC269D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95398684-4364-493C-9590-9ED44255F9D9}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="26-27,06,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
@@ -25,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="15">
   <si>
     <t>КИ</t>
   </si>
@@ -49,6 +55,27 @@
   </si>
   <si>
     <t>НВ</t>
+  </si>
+  <si>
+    <t>Симферополь</t>
+  </si>
+  <si>
+    <t>Орёл</t>
+  </si>
+  <si>
+    <t>Луганск</t>
+  </si>
+  <si>
+    <t>Бердянск</t>
+  </si>
+  <si>
+    <t>Донецк</t>
+  </si>
+  <si>
+    <t>Мелитополь</t>
+  </si>
+  <si>
+    <t>Сочи</t>
   </si>
 </sst>
 </file>
@@ -89,7 +116,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -98,10 +125,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color auto="1"/>
       </right>
       <top style="medium">
@@ -116,7 +143,7 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color auto="1"/>
       </right>
       <top style="medium">
@@ -131,34 +158,6 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -186,17 +185,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -219,19 +207,6 @@
       <top/>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -265,27 +240,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -297,50 +269,41 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -727,411 +690,411 @@
   <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="1" max="1" width="21.140625" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4">
+      <c r="A1" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3">
+        <v>17764.18</v>
+      </c>
+      <c r="F1" s="4">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1">
+        <v>17712.7</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="E3" s="3">
+        <v>10284</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="5">
-        <v>17764.18</v>
-      </c>
-      <c r="F1" s="6">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>2</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="C4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5">
+        <v>4615.8</v>
+      </c>
+      <c r="F4" s="6">
+        <v>0.35416666666666669</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C5" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="7">
+        <v>4386.6000000000004</v>
+      </c>
+      <c r="F5" s="8">
+        <v>0.35416666666666669</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="9">
+        <v>3982.5</v>
+      </c>
+      <c r="F6" s="10">
+        <v>0.35416666666666669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="11">
+        <v>10358.920000000002</v>
+      </c>
+      <c r="F7" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="13">
+        <v>2163.3199999999997</v>
+      </c>
+      <c r="F8" s="14">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="3">
+        <v>11481.999999999998</v>
+      </c>
+      <c r="F9" s="4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="7">
+        <v>7253.24</v>
+      </c>
+      <c r="F10" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="2">
-        <v>17712.7</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>3</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="D11" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="9">
+        <v>4942.92</v>
+      </c>
+      <c r="F11" s="10">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="C12" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="13">
+        <v>11669.64</v>
+      </c>
+      <c r="F12" s="14">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="1">
+        <v>15364.89</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="3">
+        <v>17510.97</v>
+      </c>
+      <c r="F14" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="1">
+        <v>14546.880000000003</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="3">
+        <v>13186.489999999998</v>
+      </c>
+      <c r="F16" s="4">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A17" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="5">
+        <v>9013.7999999999993</v>
+      </c>
+      <c r="F17" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="5">
-        <v>10284</v>
-      </c>
-      <c r="F3" s="6">
+      <c r="E18" s="9">
+        <v>7599.9100000000008</v>
+      </c>
+      <c r="F18" s="10">
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="7">
+    <row r="19" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="D19" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="3">
+        <v>17506.8</v>
+      </c>
+      <c r="F19" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="8" t="s">
+      <c r="C20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="8">
-        <v>4615.8</v>
-      </c>
-      <c r="F4" s="9">
-        <v>0.35416666666666669</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="10"/>
-      <c r="B5" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="11">
-        <v>4386.6000000000004</v>
-      </c>
-      <c r="F5" s="12">
-        <v>0.35416666666666669</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13"/>
-      <c r="B6" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="14">
-        <v>3982.5</v>
-      </c>
-      <c r="F6" s="15">
-        <v>0.35416666666666669</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="16">
-        <v>5</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="17">
-        <v>10358.920000000002</v>
-      </c>
-      <c r="F7" s="18">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="19"/>
-      <c r="B8" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="20">
-        <v>2163.3199999999997</v>
-      </c>
-      <c r="F8" s="21">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>6</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="2">
-        <v>11481.999999999998</v>
-      </c>
-      <c r="F9" s="3">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="23">
-        <v>7</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="24">
-        <v>7253.24</v>
-      </c>
-      <c r="F10" s="25">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="19"/>
-      <c r="B11" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="20">
-        <v>4942.92</v>
-      </c>
-      <c r="F11" s="21">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="22">
-        <v>8</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="14">
-        <v>11669.64</v>
-      </c>
-      <c r="F12" s="15">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <v>9</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="5">
-        <v>15364.89</v>
-      </c>
-      <c r="F13" s="6">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>10</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="2">
-        <v>17510.97</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
-        <f>MAX(A2:A14)+1</f>
-        <v>11</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="5">
-        <v>14546.880000000003</v>
-      </c>
-      <c r="F15" s="6">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <f>MAX(A3:A15)+1</f>
-        <v>12</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E16" s="2">
-        <v>13186.489999999998</v>
-      </c>
-      <c r="F16" s="3">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A17" s="16">
-        <f>MAX(A4:A16)+1</f>
-        <v>13</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="17">
-        <v>9013.7999999999993</v>
-      </c>
-      <c r="F17" s="18">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="19"/>
-      <c r="B18" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="E18" s="20">
-        <v>7599.9100000000008</v>
-      </c>
-      <c r="F18" s="21">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
-        <f>MAX(A6:A18)+1</f>
-        <v>14</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="2">
-        <v>17506.8</v>
-      </c>
-      <c r="F19" s="3">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="4">
-        <f>MAX(A7:A19)+1</f>
-        <v>15</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E20" s="5">
+      <c r="E20" s="1">
         <v>17849.460000000003</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="2">
         <v>0.58333333333333337</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A17:A18"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D08C22C3-6162-4BF7-B757-BFD7CFD5CD2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1C9AD8D-4C38-4F4B-A6BB-98D3FA988032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="29,06,26" sheetId="101" r:id="rId1"/>
+    <sheet name="30,06,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="4">
   <si>
     <t>КИ</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Сочи</t>
   </si>
   <si>
-    <t>01,07,26</t>
+    <t>02,07,26</t>
   </si>
 </sst>
 </file>
@@ -57,7 +57,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -70,8 +70,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -80,16 +86,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color auto="1"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color auto="1"/>
       </right>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -98,13 +104,13 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color auto="1"/>
       </right>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -113,51 +119,14 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
       <right style="medium">
         <color auto="1"/>
       </right>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -167,28 +136,28 @@
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -573,60 +542,128 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="7">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1">
         <v>1</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="1">
-        <v>1275.8099999999997</v>
-      </c>
-      <c r="G1" s="2">
-        <v>0.5</v>
+      <c r="F1" s="3">
+        <v>18168.719999999998</v>
+      </c>
+      <c r="G1" s="4">
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
+      <c r="A2" s="5">
+        <v>2</v>
+      </c>
       <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="3">
-        <v>10302.659999999998</v>
-      </c>
-      <c r="G2" s="4">
+      <c r="F2" s="7">
+        <v>18122.22</v>
+      </c>
+      <c r="G2" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3">
+        <v>18019.8</v>
+      </c>
+      <c r="G3" s="4">
         <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>4</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="7">
+        <v>18036.84</v>
+      </c>
+      <c r="G4" s="8">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3">
+        <v>18085.100000000006</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0.58333333333333337</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:A2"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1C9AD8D-4C38-4F4B-A6BB-98D3FA988032}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D907B56-E7E6-47D3-BC2E-70F88AD6A585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="30,06,26" sheetId="101" r:id="rId1"/>
+    <sheet name="01,07,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="12">
   <si>
     <t>КИ</t>
   </si>
@@ -36,7 +36,31 @@
     <t>Сочи</t>
   </si>
   <si>
-    <t>02,07,26</t>
+    <t>03,07,26</t>
+  </si>
+  <si>
+    <t>КСК</t>
+  </si>
+  <si>
+    <t>Симферополь</t>
+  </si>
+  <si>
+    <t>04,07,26</t>
+  </si>
+  <si>
+    <t>ЗПФ</t>
+  </si>
+  <si>
+    <t>НВ</t>
+  </si>
+  <si>
+    <t>Донецк</t>
+  </si>
+  <si>
+    <t>Луганск</t>
+  </si>
+  <si>
+    <t>Мелитополь</t>
   </si>
 </sst>
 </file>
@@ -77,7 +101,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -130,11 +154,97 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -158,6 +268,54 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -542,128 +700,288 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="14.140625" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1">
+    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="9">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="11">
+        <v>9971.6399999999976</v>
+      </c>
+      <c r="G1" s="12">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="13"/>
+      <c r="B2" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="15">
+        <v>7124.5599999999986</v>
+      </c>
+      <c r="G2" s="16">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="17">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="B3" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D3" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E3" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="19">
+        <v>15541.739999999998</v>
+      </c>
+      <c r="G3" s="20">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="21"/>
+      <c r="B4" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="23">
+        <v>2022</v>
+      </c>
+      <c r="G4" s="24">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="7">
+        <v>17609.82</v>
+      </c>
+      <c r="G5" s="8">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="17">
+        <v>4</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="3">
-        <v>18168.719999999998</v>
-      </c>
-      <c r="G1" s="4">
+      <c r="F6" s="19">
+        <v>3851.1</v>
+      </c>
+      <c r="G6" s="20">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="21"/>
+      <c r="B7" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="23">
+        <v>9181.1200000000026</v>
+      </c>
+      <c r="G7" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>5</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="7">
+        <v>9582</v>
+      </c>
+      <c r="G8" s="8">
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
-        <v>2</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="7" t="s">
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="3">
+        <v>11917.079999999998</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="9">
+        <v>7</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="7">
-        <v>18122.22</v>
-      </c>
-      <c r="G2" s="8">
+      <c r="D10" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="11">
+        <v>17625.72</v>
+      </c>
+      <c r="G10" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13"/>
+      <c r="B11" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="15">
+        <v>240</v>
+      </c>
+      <c r="G11" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>8</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
+        <v>17435.47</v>
+      </c>
+      <c r="G12" s="4">
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="3">
-        <v>18019.8</v>
-      </c>
-      <c r="G3" s="4">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
-        <v>4</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="7">
-        <v>18036.84</v>
-      </c>
-      <c r="G4" s="8">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>5</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="3">
-        <v>18085.100000000006</v>
-      </c>
-      <c r="G5" s="4">
-        <v>0.58333333333333337</v>
-      </c>
-    </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A10:A11"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -1,22 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\графики\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D907B56-E7E6-47D3-BC2E-70F88AD6A585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61E98D9F-CA91-4024-8199-8D696A03AA43}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="01,07,26" sheetId="101" r:id="rId1"/>
+    <sheet name="02,07,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
@@ -25,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="10">
   <si>
     <t>КИ</t>
   </si>
@@ -45,22 +51,16 @@
     <t>Симферополь</t>
   </si>
   <si>
-    <t>04,07,26</t>
-  </si>
-  <si>
-    <t>ЗПФ</t>
-  </si>
-  <si>
     <t>НВ</t>
   </si>
   <si>
     <t>Донецк</t>
   </si>
   <si>
-    <t>Луганск</t>
+    <t>Мелитополь</t>
   </si>
   <si>
-    <t>Мелитополь</t>
+    <t>05,07,26</t>
   </si>
 </sst>
 </file>
@@ -101,7 +101,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -155,10 +155,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
         <color auto="1"/>
       </right>
       <top style="medium">
@@ -173,7 +173,7 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color auto="1"/>
       </right>
       <top style="medium">
@@ -181,36 +181,6 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -230,6 +200,104 @@
     <border>
       <left style="thin">
         <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
       </left>
       <right style="medium">
         <color indexed="64"/>
@@ -244,7 +312,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -258,65 +326,56 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -700,287 +759,238 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" customWidth="1"/>
+    <col min="2" max="2" width="22.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="9">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="20">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11">
-        <v>9971.6399999999976</v>
-      </c>
-      <c r="G1" s="12">
+      <c r="F1" s="16">
+        <v>1710</v>
+      </c>
+      <c r="G1" s="17">
         <v>0.375</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13"/>
-      <c r="B2" s="14" t="s">
+      <c r="A2" s="1">
+        <v>2</v>
+      </c>
+      <c r="B2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="15">
-        <v>7124.5599999999986</v>
-      </c>
-      <c r="G2" s="16">
-        <v>0.375</v>
+      <c r="F2" s="3">
+        <v>3510</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="17">
-        <v>2</v>
-      </c>
-      <c r="B3" s="18" t="s">
+      <c r="A3" s="18">
+        <v>3</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="19" t="s">
+      <c r="D3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="19">
-        <v>15541.739999999998</v>
-      </c>
-      <c r="G3" s="20">
-        <v>0.41666666666666669</v>
+      <c r="F3" s="6">
+        <v>1037.0999999999999</v>
+      </c>
+      <c r="G3" s="7">
+        <v>0.375</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="21"/>
-      <c r="B4" s="22" t="s">
+      <c r="A4" s="19"/>
+      <c r="B4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="23" t="s">
+      <c r="D4" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="23">
-        <v>2022</v>
-      </c>
-      <c r="G4" s="24">
-        <v>0.41666666666666669</v>
+      <c r="F4" s="9">
+        <v>16463.16</v>
+      </c>
+      <c r="G4" s="10">
+        <v>0.375</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
-        <v>3</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="7" t="s">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="7">
-        <v>17609.82</v>
-      </c>
-      <c r="G5" s="8">
-        <v>0.375</v>
+      <c r="F5" s="3">
+        <v>17495.000000000004</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0.45833333333333331</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="17">
-        <v>4</v>
-      </c>
-      <c r="B6" s="18" t="s">
+      <c r="A6" s="18">
+        <f>MAX(A2:A5)+1</f>
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="19" t="s">
+      <c r="D6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="19">
-        <v>3851.1</v>
-      </c>
-      <c r="G6" s="20">
-        <v>0.45833333333333331</v>
+      <c r="F6" s="6">
+        <v>6209.64</v>
+      </c>
+      <c r="G6" s="7">
+        <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="21"/>
-      <c r="B7" s="22" t="s">
+    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D7" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="23" t="s">
+      <c r="D7" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="F7" s="23">
-        <v>9181.1200000000026</v>
-      </c>
-      <c r="G7" s="24">
-        <v>0.45833333333333331</v>
+      <c r="F7" s="13">
+        <v>2112.9399999999996</v>
+      </c>
+      <c r="G7" s="14">
+        <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
-        <v>5</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="7" t="s">
+    <row r="8" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="11"/>
+      <c r="B8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="7">
-        <v>9582</v>
-      </c>
-      <c r="G8" s="8">
+      <c r="C8" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="13">
+        <v>1560.3600000000001</v>
+      </c>
+      <c r="G8" s="14">
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
+    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="11"/>
+      <c r="B9" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="F9" s="13">
+        <v>6987.72</v>
+      </c>
+      <c r="G9" s="14">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="19"/>
+      <c r="B10" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="3">
-        <v>11917.079999999998</v>
-      </c>
-      <c r="G9" s="4">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="9">
-        <v>7</v>
-      </c>
-      <c r="B10" s="10" t="s">
+      <c r="C10" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="11" t="s">
+      <c r="E10" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="11">
-        <v>17625.72</v>
-      </c>
-      <c r="G10" s="12">
+      <c r="F10" s="9">
+        <v>656.7</v>
+      </c>
+      <c r="G10" s="10">
         <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="15">
-        <v>240</v>
-      </c>
-      <c r="G11" s="16">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>8</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="3">
-        <v>17435.47</v>
-      </c>
-      <c r="G12" s="4">
-        <v>0.45833333333333331</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:A2"/>
+  <mergeCells count="2">
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A6:A10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -1,28 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61E98D9F-CA91-4024-8199-8D696A03AA43}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A35C56-B4A0-4087-951D-C4226CFDF0F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="02,07,26" sheetId="101" r:id="rId1"/>
+    <sheet name="03,07,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
@@ -31,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="15">
   <si>
     <t>КИ</t>
   </si>
@@ -42,9 +36,6 @@
     <t>Сочи</t>
   </si>
   <si>
-    <t>03,07,26</t>
-  </si>
-  <si>
     <t>КСК</t>
   </si>
   <si>
@@ -61,6 +52,24 @@
   </si>
   <si>
     <t>05,07,26</t>
+  </si>
+  <si>
+    <t>ЗПФ</t>
+  </si>
+  <si>
+    <t>06,07,26</t>
+  </si>
+  <si>
+    <t>07,07,26</t>
+  </si>
+  <si>
+    <t>Бердянск</t>
+  </si>
+  <si>
+    <t>Луганск</t>
+  </si>
+  <si>
+    <t>Орёл</t>
   </si>
 </sst>
 </file>
@@ -101,7 +110,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -243,41 +252,6 @@
       </right>
       <top/>
       <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -312,7 +286,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -344,38 +318,59 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -759,238 +754,490 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="22.5703125" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20">
+      <c r="A1" s="1">
         <v>1</v>
       </c>
-      <c r="B1" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="16" t="s">
+      <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="F1" s="3">
+        <v>10966.799999999997</v>
+      </c>
+      <c r="G1" s="4">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="11">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="16">
-        <v>1710</v>
-      </c>
-      <c r="G1" s="17">
+      <c r="C2" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="6">
+        <v>2839.9799999999996</v>
+      </c>
+      <c r="G2" s="7">
         <v>0.375</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="12"/>
+      <c r="B3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="9">
+        <v>14851.28</v>
+      </c>
+      <c r="G3" s="10">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="3">
+        <v>17708.68</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="11">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="6">
+        <v>10123.780000000001</v>
+      </c>
+      <c r="G5" s="7">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="12"/>
+      <c r="B6" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="9">
+        <v>3359.36</v>
+      </c>
+      <c r="G6" s="10">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="3">
+        <v>15167.900000000001</v>
+      </c>
+      <c r="G7" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13">
+        <v>6</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="15">
+        <v>15182.760000000002</v>
+      </c>
+      <c r="G8" s="16">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="17">
+        <v>7</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="19">
+        <v>6184.08</v>
+      </c>
+      <c r="G9" s="20">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="21"/>
+      <c r="B10" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="23">
+        <v>5905.2000000000007</v>
+      </c>
+      <c r="G10" s="24">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13">
+        <v>8</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="15">
+        <v>9574.08</v>
+      </c>
+      <c r="G11" s="16">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="17">
+        <v>9</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="19">
+        <v>6432.12</v>
+      </c>
+      <c r="G12" s="20">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="21"/>
+      <c r="B13" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" s="23">
+        <v>5321.36</v>
+      </c>
+      <c r="G13" s="24">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="13">
+        <v>10</v>
+      </c>
+      <c r="B14" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="3">
-        <v>3510</v>
-      </c>
-      <c r="G2" s="4">
+      <c r="C14" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="15">
+        <v>13113.15</v>
+      </c>
+      <c r="G14" s="16">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A15" s="17">
+        <v>11</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="19">
+        <v>3231.8</v>
+      </c>
+      <c r="G15" s="20">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A16" s="25"/>
+      <c r="B16" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="27">
+        <v>4302.3</v>
+      </c>
+      <c r="G16" s="28">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="21"/>
+      <c r="B17" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="23">
+        <v>3813.3</v>
+      </c>
+      <c r="G17" s="24">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A18" s="11">
+        <v>12</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="6">
+        <v>8902.56</v>
+      </c>
+      <c r="G18" s="7">
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="18">
-        <v>3</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="6" t="s">
+    <row r="19" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="12"/>
+      <c r="B19" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" s="9">
+        <v>8452.9599999999991</v>
+      </c>
+      <c r="G19" s="10">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>13</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3">
+        <v>17449.439999999999</v>
+      </c>
+      <c r="G20" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="13">
+        <v>14</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="6">
-        <v>1037.0999999999999</v>
-      </c>
-      <c r="G3" s="7">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="19"/>
-      <c r="B4" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="9">
-        <v>16463.16</v>
-      </c>
-      <c r="G4" s="10">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="3">
-        <v>17495.000000000004</v>
-      </c>
-      <c r="G5" s="4">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="18">
-        <f>MAX(A2:A5)+1</f>
-        <v>5</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="6">
-        <v>6209.64</v>
-      </c>
-      <c r="G6" s="7">
+      <c r="D21" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="15">
+        <v>11619.119999999997</v>
+      </c>
+      <c r="G21" s="16">
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="11"/>
-      <c r="B7" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="13">
-        <v>2112.9399999999996</v>
-      </c>
-      <c r="G7" s="14">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="11"/>
-      <c r="B8" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" s="13">
-        <v>1560.3600000000001</v>
-      </c>
-      <c r="G8" s="14">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="11"/>
-      <c r="B9" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="13">
-        <v>6987.72</v>
-      </c>
-      <c r="G9" s="14">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="19"/>
-      <c r="B10" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" s="9">
-        <v>656.7</v>
-      </c>
-      <c r="G10" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A6:A10"/>
+  <mergeCells count="6">
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A9:A10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B61C1F7-87F4-4B28-8923-DD06CC700131}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35BA588B-030B-4367-8944-B02AAAD52243}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="07,07,26" sheetId="101" r:id="rId1"/>
+    <sheet name="08,07,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="11">
   <si>
     <t>КИ</t>
   </si>
@@ -42,7 +42,28 @@
     <t>Сочи</t>
   </si>
   <si>
-    <t>09,07,26</t>
+    <t>Симферополь</t>
+  </si>
+  <si>
+    <t>10,07,26</t>
+  </si>
+  <si>
+    <t>КСК</t>
+  </si>
+  <si>
+    <t>11,07,26</t>
+  </si>
+  <si>
+    <t>ЗПФ</t>
+  </si>
+  <si>
+    <t>Донецк</t>
+  </si>
+  <si>
+    <t>НВ</t>
+  </si>
+  <si>
+    <t>Луганск</t>
   </si>
 </sst>
 </file>
@@ -83,7 +104,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -136,11 +157,130 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -164,6 +304,78 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -548,83 +760,328 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="11.7109375" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1">
+    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="9">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="B1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="3">
-        <v>18183.899999999998</v>
-      </c>
-      <c r="G1" s="4">
-        <v>0.41666666666666669</v>
+      <c r="C1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="11">
+        <v>15440.420000000002</v>
+      </c>
+      <c r="G1" s="12">
+        <v>0.375</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
-        <v>2</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="7" t="s">
+      <c r="A2" s="13"/>
+      <c r="B2" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="7">
-        <v>18086.3</v>
-      </c>
-      <c r="G2" s="8">
-        <v>0.45833333333333331</v>
+      <c r="C2" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="15">
+        <v>2124.6000000000004</v>
+      </c>
+      <c r="G2" s="16">
+        <v>0.375</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="3">
+        <v>17622.960000000003</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="7">
+        <v>17661.32</v>
+      </c>
+      <c r="G4" s="8">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="3">
+        <v>11744.88</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="11">
+        <v>10995.000000000002</v>
+      </c>
+      <c r="G6" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="17"/>
+      <c r="B7" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="C7" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="3">
-        <v>18202.02</v>
-      </c>
-      <c r="G3" s="4">
+      <c r="F7" s="19">
+        <v>3910.5600000000004</v>
+      </c>
+      <c r="G7" s="20">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="13"/>
+      <c r="B8" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="15">
+        <v>2502.3599999999997</v>
+      </c>
+      <c r="G8" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="21">
+        <v>6</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="23">
+        <v>8779.58</v>
+      </c>
+      <c r="G9" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="25"/>
+      <c r="B10" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="27">
+        <v>1465.92</v>
+      </c>
+      <c r="G10" s="28">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="29"/>
+      <c r="B11" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="31">
+        <v>7114.8400000000011</v>
+      </c>
+      <c r="G11" s="32">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="9">
+        <v>7</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="11">
+        <v>5368.14</v>
+      </c>
+      <c r="G12" s="12">
         <v>0.5</v>
       </c>
     </row>
+    <row r="13" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="17"/>
+      <c r="B13" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="19">
+        <v>6267.4000000000005</v>
+      </c>
+      <c r="G13" s="20">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="13"/>
+      <c r="B14" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="15">
+        <v>5560.8499999999995</v>
+      </c>
+      <c r="G14" s="16">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="A12:A14"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35BA588B-030B-4367-8944-B02AAAD52243}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494016EF-05A5-47B1-9195-1C92825269C6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="08,07,26" sheetId="101" r:id="rId1"/>
+    <sheet name="09,07,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="9">
   <si>
     <t>КИ</t>
   </si>
@@ -45,25 +45,19 @@
     <t>Симферополь</t>
   </si>
   <si>
-    <t>10,07,26</t>
-  </si>
-  <si>
     <t>КСК</t>
-  </si>
-  <si>
-    <t>11,07,26</t>
-  </si>
-  <si>
-    <t>ЗПФ</t>
-  </si>
-  <si>
-    <t>Донецк</t>
   </si>
   <si>
     <t>НВ</t>
   </si>
   <si>
-    <t>Луганск</t>
+    <t>12,07,26</t>
+  </si>
+  <si>
+    <t>Бердянск</t>
+  </si>
+  <si>
+    <t>Мелитополь</t>
   </si>
 </sst>
 </file>
@@ -280,7 +274,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -294,21 +288,6 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -318,9 +297,6 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -330,9 +306,6 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -342,9 +315,6 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -354,21 +324,6 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -376,6 +331,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -760,327 +730,149 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="9">
+      <c r="A1" s="20">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="11">
-        <v>15440.420000000002</v>
-      </c>
-      <c r="G1" s="12">
+      <c r="F1" s="15">
+        <v>1248.9000000000001</v>
+      </c>
+      <c r="G1" s="16">
         <v>0.375</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13"/>
-      <c r="B2" s="14" t="s">
+      <c r="A2" s="21"/>
+      <c r="B2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="F2" s="18">
+        <v>16208.800000000001</v>
+      </c>
+      <c r="G2" s="19">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="22">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="15">
-        <v>2124.6000000000004</v>
-      </c>
-      <c r="G2" s="16">
-        <v>0.375</v>
+      <c r="F3" s="6">
+        <v>5346.0999999999995</v>
+      </c>
+      <c r="G3" s="7">
+        <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="3" t="s">
+    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="23"/>
+      <c r="B4" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="D4" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="3">
-        <v>17622.960000000003</v>
-      </c>
-      <c r="G3" s="4">
+      <c r="F4" s="12">
+        <v>3983.12</v>
+      </c>
+      <c r="G4" s="13">
         <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="7">
-        <v>17661.32</v>
-      </c>
-      <c r="G4" s="8">
-        <v>0.375</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="A5" s="24"/>
+      <c r="B5" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="9">
+        <v>8168.28</v>
+      </c>
+      <c r="G5" s="10">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="3">
-        <v>11744.88</v>
-      </c>
-      <c r="G5" s="4">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="9">
-        <v>5</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="11" t="s">
+      <c r="B6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="11">
-        <v>10995.000000000002</v>
-      </c>
-      <c r="G6" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="17"/>
-      <c r="B7" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="19" t="s">
+      <c r="E6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F7" s="19">
-        <v>3910.5600000000004</v>
-      </c>
-      <c r="G7" s="20">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="15">
-        <v>2502.3599999999997</v>
-      </c>
-      <c r="G8" s="16">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="21">
-        <v>6</v>
-      </c>
-      <c r="B9" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="23">
-        <v>8779.58</v>
-      </c>
-      <c r="G9" s="24">
+      <c r="F6" s="3">
+        <v>18025.260000000002</v>
+      </c>
+      <c r="G6" s="4">
         <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="25"/>
-      <c r="B10" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="27">
-        <v>1465.92</v>
-      </c>
-      <c r="G10" s="28">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="29"/>
-      <c r="B11" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="31">
-        <v>7114.8400000000011</v>
-      </c>
-      <c r="G11" s="32">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="9">
-        <v>7</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="11">
-        <v>5368.14</v>
-      </c>
-      <c r="G12" s="12">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="17"/>
-      <c r="B13" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="F13" s="19">
-        <v>6267.4000000000005</v>
-      </c>
-      <c r="G13" s="20">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="F14" s="15">
-        <v>5560.8499999999995</v>
-      </c>
-      <c r="G14" s="16">
-        <v>0.5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="2">
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="A3:A5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{494016EF-05A5-47B1-9195-1C92825269C6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53D2FA39-CCF4-41B6-9771-0F214842D182}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="09,07,26" sheetId="101" r:id="rId1"/>
+    <sheet name="10,07,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="15">
   <si>
     <t>КИ</t>
   </si>
@@ -58,6 +58,24 @@
   </si>
   <si>
     <t>Мелитополь</t>
+  </si>
+  <si>
+    <t>Орёл</t>
+  </si>
+  <si>
+    <t>ЗПФ</t>
+  </si>
+  <si>
+    <t>13,07,26</t>
+  </si>
+  <si>
+    <t>Донецк</t>
+  </si>
+  <si>
+    <t>Луганск</t>
+  </si>
+  <si>
+    <t>14,07,26</t>
   </si>
 </sst>
 </file>
@@ -274,7 +292,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -346,6 +364,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -730,149 +760,445 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="20">
+      <c r="A1" s="22">
         <v>1</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="6">
+        <v>4039.04</v>
+      </c>
+      <c r="G1" s="7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="23"/>
+      <c r="B2" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="12">
+        <v>3676.74</v>
+      </c>
+      <c r="G2" s="13">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="23"/>
+      <c r="B3" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="12">
+        <v>1372.92</v>
+      </c>
+      <c r="G3" s="13">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="24"/>
+      <c r="B4" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="9">
+        <v>1527.12</v>
+      </c>
+      <c r="G4" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="15" t="s">
+      <c r="C5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="15">
-        <v>1248.9000000000001</v>
-      </c>
-      <c r="G1" s="16">
+      <c r="F5" s="3">
+        <v>12226.92</v>
+      </c>
+      <c r="G5" s="4">
         <v>0.375</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="21"/>
-      <c r="B2" s="17" t="s">
+    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="22">
         <v>3</v>
       </c>
-      <c r="C2" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="18" t="s">
+      <c r="B6" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="6">
+        <v>14707.929999999998</v>
+      </c>
+      <c r="G6" s="7">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="23"/>
+      <c r="B7" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="12">
+        <v>504</v>
+      </c>
+      <c r="G7" s="13">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="24"/>
+      <c r="B8" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="9">
+        <v>2382.9799999999996</v>
+      </c>
+      <c r="G8" s="10">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>4</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="3">
+        <v>17621.719999999998</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="25">
+        <v>5</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="27">
+        <v>15658.579999999998</v>
+      </c>
+      <c r="G10" s="28">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="20">
         <v>6</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="B11" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="15">
+        <v>11070.240000000002</v>
+      </c>
+      <c r="G11" s="16">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="21"/>
+      <c r="B12" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="18">
+        <v>6168.23</v>
+      </c>
+      <c r="G12" s="19">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="25">
+        <v>7</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" s="27">
+        <v>15718.009999999998</v>
+      </c>
+      <c r="G13" s="28">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>8</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
+        <v>9778.6799999999985</v>
+      </c>
+      <c r="G14" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="25">
+        <v>9</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="27">
+        <v>10842.28</v>
+      </c>
+      <c r="G15" s="28">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <f>MAX(A1:A15)+1</f>
+        <v>10</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="18">
-        <v>16208.800000000001</v>
-      </c>
-      <c r="G2" s="19">
+      <c r="F16" s="3">
+        <v>17690.740000000002</v>
+      </c>
+      <c r="G16" s="4">
         <v>0.375</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="22">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
+    <row r="17" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A17" s="22">
+        <f>MAX(A2:A16)+1</f>
+        <v>11</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="6" t="s">
+      <c r="C17" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="6">
-        <v>5346.0999999999995</v>
-      </c>
-      <c r="G3" s="7">
+      <c r="F17" s="6">
+        <v>8298.16</v>
+      </c>
+      <c r="G17" s="7">
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="23"/>
-      <c r="B4" s="11" t="s">
+    <row r="18" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="24"/>
+      <c r="B18" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="12" t="s">
+      <c r="C18" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="12">
-        <v>3983.12</v>
-      </c>
-      <c r="G4" s="13">
+      <c r="F18" s="9">
+        <v>5599.92</v>
+      </c>
+      <c r="G18" s="10">
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="24"/>
-      <c r="B5" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="9" t="s">
+    <row r="19" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <f>MAX(A4:A18)+1</f>
+        <v>12</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="9">
-        <v>8168.28</v>
-      </c>
-      <c r="G5" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>3</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3">
-        <v>18025.260000000002</v>
-      </c>
-      <c r="G6" s="4">
+      <c r="F19" s="3">
+        <v>17244.66</v>
+      </c>
+      <c r="G19" s="4">
         <v>0.45833333333333331</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A3:A5"/>
+  <mergeCells count="4">
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="A11:A12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50836A5A-FBF9-4662-AB2E-D51ADE57CDFA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0196676-01A1-4673-86B7-CEE19C76D1E5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="13,07,26" sheetId="101" r:id="rId1"/>
+    <sheet name="14,07,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="4">
   <si>
     <t>ЛП</t>
   </si>
@@ -39,7 +39,10 @@
     <t>Сочи</t>
   </si>
   <si>
-    <t>15,07,26</t>
+    <t>КИ</t>
+  </si>
+  <si>
+    <t>16,07,26</t>
   </si>
 </sst>
 </file>
@@ -60,7 +63,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -73,8 +76,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -92,20 +101,7 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -114,27 +110,14 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color auto="1"/>
       </right>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -142,25 +125,14 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color auto="1"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
       <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -170,6 +142,21 @@
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -177,21 +164,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -576,55 +548,105 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="15.5703125" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="7">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2">
-        <v>2367.1</v>
-      </c>
       <c r="F1" s="3">
+        <v>18119.349999999999</v>
+      </c>
+      <c r="G1" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5">
+        <v>2</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="7">
+        <v>18153.7</v>
+      </c>
+      <c r="G2" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>18022.2</v>
+      </c>
+      <c r="G3" s="4">
         <v>0.5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8"/>
-      <c r="B2" s="4" t="s">
+    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>4</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="5">
-        <v>15104.26</v>
-      </c>
-      <c r="F2" s="6">
-        <v>0.5</v>
+      <c r="F4" s="7">
+        <v>18155.820000000003</v>
+      </c>
+      <c r="G4" s="8">
+        <v>0.54166666666666663</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:A2"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0196676-01A1-4673-86B7-CEE19C76D1E5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D6B044B-A5AA-4D3A-8716-ABDD351D7773}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="14,07,26" sheetId="101" r:id="rId1"/>
+    <sheet name="16,07,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="9">
   <si>
     <t>ЛП</t>
   </si>
@@ -42,7 +42,22 @@
     <t>КИ</t>
   </si>
   <si>
-    <t>16,07,26</t>
+    <t>Симферополь</t>
+  </si>
+  <si>
+    <t>КСК</t>
+  </si>
+  <si>
+    <t>НВ</t>
+  </si>
+  <si>
+    <t>Луганск</t>
+  </si>
+  <si>
+    <t>Донецк</t>
+  </si>
+  <si>
+    <t>19,07,26</t>
   </si>
 </sst>
 </file>
@@ -83,7 +98,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -136,11 +151,130 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -154,16 +288,64 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -548,105 +730,195 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="12.42578125" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1">
+    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="19">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="3">
-        <v>18119.349999999999</v>
-      </c>
-      <c r="G1" s="4">
-        <v>0.41666666666666669</v>
+      <c r="D1" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="12">
+        <v>16592.62</v>
+      </c>
+      <c r="G1" s="13">
+        <v>0.375</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
+      <c r="A2" s="20"/>
+      <c r="B2" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="F2" s="7">
-        <v>18153.7</v>
-      </c>
-      <c r="G2" s="8">
-        <v>0.45833333333333331</v>
+      <c r="D2" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="15">
+        <v>1164.54</v>
+      </c>
+      <c r="G2" s="16">
+        <v>0.375</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="3">
+        <v>17862.260000000002</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="19">
         <v>3</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="B4" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="3">
-        <v>18022.2</v>
-      </c>
-      <c r="G3" s="4">
+      <c r="F4" s="12">
+        <v>3459.63</v>
+      </c>
+      <c r="G4" s="13">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="20"/>
+      <c r="B5" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="15">
+        <v>13946.94</v>
+      </c>
+      <c r="G5" s="16">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="17">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="6">
+        <v>517.44000000000005</v>
+      </c>
+      <c r="G6" s="7">
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
-        <v>4</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="7" t="s">
+    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="21"/>
+      <c r="B7" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="F4" s="7">
-        <v>18155.820000000003</v>
-      </c>
-      <c r="G4" s="8">
-        <v>0.54166666666666663</v>
+      <c r="D7" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="23">
+        <v>8268.52</v>
+      </c>
+      <c r="G7" s="24">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="18"/>
+      <c r="B8" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="9">
+        <v>8438.4</v>
+      </c>
+      <c r="G8" s="10">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A8"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D6B044B-A5AA-4D3A-8716-ABDD351D7773}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C61AC479-6FBD-455C-837E-53FF20B212E5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="16,07,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="12">
   <si>
     <t>ЛП</t>
   </si>
@@ -59,12 +59,21 @@
   <si>
     <t>19,07,26</t>
   </si>
+  <si>
+    <t>16,07,26</t>
+  </si>
+  <si>
+    <t>17,07,26</t>
+  </si>
+  <si>
+    <t>дозаказ</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -76,6 +85,14 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="4">
@@ -98,7 +115,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -270,11 +287,63 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -297,15 +366,6 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -324,21 +384,6 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -346,6 +391,63 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -730,58 +832,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.85546875" customWidth="1"/>
     <col min="4" max="4" width="15.140625" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="19">
+    <row r="1" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="17">
         <v>1</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="12">
+      <c r="F1" s="9">
         <v>16592.62</v>
       </c>
-      <c r="G1" s="13">
+      <c r="G1" s="10">
         <v>0.375</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20"/>
-      <c r="B2" s="14" t="s">
+    <row r="2" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="18"/>
+      <c r="B2" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="12">
         <v>1164.54</v>
       </c>
-      <c r="G2" s="16">
+      <c r="G2" s="13">
         <v>0.375</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -804,52 +907,52 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="19">
+    <row r="4" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="17">
         <v>3</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="9">
         <v>3459.63</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="10">
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="20"/>
-      <c r="B5" s="14" t="s">
+    <row r="5" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="18"/>
+      <c r="B5" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="12">
         <v>13946.94</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="13">
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="17">
+    <row r="6" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="19">
         <v>4</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -871,46 +974,124 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="21"/>
-      <c r="B7" s="22" t="s">
+    <row r="7" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="20"/>
+      <c r="B7" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="E7" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="15">
         <v>8268.52</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="16">
         <v>0.5</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="18"/>
-      <c r="B8" s="8" t="s">
+    <row r="8" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="20"/>
+      <c r="B8" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="31">
         <v>8438.4</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="25">
         <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="24">
+        <v>5</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="F9" s="33">
+        <v>2100</v>
+      </c>
+      <c r="G9" s="34">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="H9" s="35" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>6</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="27">
+        <v>1905</v>
+      </c>
+      <c r="G10" s="4">
+        <v>0.375</v>
+      </c>
+      <c r="H10" s="28" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="24">
+        <v>7</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11" s="22">
+        <v>1905</v>
+      </c>
+      <c r="G11" s="23">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="H11" s="29" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -1,28 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C61AC479-6FBD-455C-837E-53FF20B212E5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30F1CF80-CE40-43C7-AE40-852B74A7A8A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="16,07,26" sheetId="101" r:id="rId1"/>
+    <sheet name="17,07,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
@@ -31,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="16">
   <si>
     <t>ЛП</t>
   </si>
@@ -60,13 +54,25 @@
     <t>19,07,26</t>
   </si>
   <si>
-    <t>16,07,26</t>
-  </si>
-  <si>
-    <t>17,07,26</t>
-  </si>
-  <si>
     <t>дозаказ</t>
+  </si>
+  <si>
+    <t>ЗПФ</t>
+  </si>
+  <si>
+    <t>20,07,26</t>
+  </si>
+  <si>
+    <t>Мелитополь</t>
+  </si>
+  <si>
+    <t>Бердянск</t>
+  </si>
+  <si>
+    <t>21,07,26</t>
+  </si>
+  <si>
+    <t>18,07,26</t>
   </si>
 </sst>
 </file>
@@ -115,7 +121,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -317,33 +323,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -384,58 +368,7 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -447,7 +380,67 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -832,273 +825,622 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="20.85546875" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" customWidth="1"/>
-    <col min="8" max="8" width="13.28515625" customWidth="1"/>
+    <col min="2" max="2" width="22.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="8" max="8" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="17">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="14">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="22">
+        <v>18025.18</v>
+      </c>
+      <c r="G1" s="17">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="9" t="s">
+      <c r="C2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9">
-        <v>16592.62</v>
-      </c>
-      <c r="G1" s="10">
+      <c r="F2" s="3">
+        <v>12033.279999999999</v>
+      </c>
+      <c r="G2" s="4">
         <v>0.375</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18"/>
-      <c r="B2" s="11" t="s">
+    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="18">
         <v>3</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="12" t="s">
+      <c r="B3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="9">
+        <v>12827.199999999999</v>
+      </c>
+      <c r="G3" s="10">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="23"/>
+      <c r="B4" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="25">
+        <v>2894.42</v>
+      </c>
+      <c r="G4" s="26">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="19"/>
+      <c r="B5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="12">
+        <v>1925.24</v>
+      </c>
+      <c r="G5" s="13">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="3">
+        <v>17672.740000000002</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="14">
+        <v>5</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="22">
+        <v>11225.12</v>
+      </c>
+      <c r="G7" s="17">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="3">
+        <v>11345.68</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="14">
+        <v>7</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="22">
+        <v>11480.960000000001</v>
+      </c>
+      <c r="G9" s="17">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="20">
         <v>8</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="B10" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="6">
+        <v>7917.2999999999993</v>
+      </c>
+      <c r="G10" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="27"/>
+      <c r="B11" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="29" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="29">
+        <v>8185.32</v>
+      </c>
+      <c r="G11" s="30">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="14">
+        <v>9</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="22">
+        <v>15657.02</v>
+      </c>
+      <c r="G12" s="17">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>10</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" s="3">
+        <v>15985.570000000002</v>
+      </c>
+      <c r="G13" s="4">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="14">
+        <v>11</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E14" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="12">
-        <v>1164.54</v>
-      </c>
-      <c r="G2" s="13">
+      <c r="F14" s="22">
+        <v>17496.179999999997</v>
+      </c>
+      <c r="G14" s="17">
         <v>0.375</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="15" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A15" s="20">
+        <v>12</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="6">
+        <v>3586.8</v>
+      </c>
+      <c r="G15" s="7">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="27"/>
+      <c r="B16" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="29" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" s="29">
+        <v>6921.6</v>
+      </c>
+      <c r="G16" s="30">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A17" s="18">
+        <v>13</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="9">
+        <v>4043.64</v>
+      </c>
+      <c r="G17" s="10">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="19"/>
+      <c r="B18" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F18" s="12">
+        <v>13282.3</v>
+      </c>
+      <c r="G18" s="13">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A19" s="20">
+        <v>14</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" s="6">
+        <v>3401.82</v>
+      </c>
+      <c r="G19" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="27"/>
+      <c r="B20" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="F20" s="29">
+        <v>13908.660000000002</v>
+      </c>
+      <c r="G20" s="30">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="14">
+        <v>15</v>
+      </c>
+      <c r="B21" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="C21" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="22">
+        <v>17527.2</v>
+      </c>
+      <c r="G21" s="17">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="14">
+        <v>16</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="16">
+        <v>1800</v>
+      </c>
+      <c r="G22" s="17">
+        <v>0.375</v>
+      </c>
+      <c r="H22" s="37" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="34">
+        <v>17</v>
+      </c>
+      <c r="B23" s="35" t="s">
+        <v>3</v>
+      </c>
+      <c r="C23" s="36" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="36" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23" s="36">
+        <v>1800</v>
+      </c>
+      <c r="G23" s="30">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="H23" s="38" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="14">
+        <v>18</v>
+      </c>
+      <c r="B24" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E24" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="3">
-        <v>17862.260000000002</v>
-      </c>
-      <c r="G3" s="4">
+      <c r="F24" s="16">
+        <v>3510</v>
+      </c>
+      <c r="G24" s="17">
+        <v>0.375</v>
+      </c>
+      <c r="H24" s="37" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>19</v>
+      </c>
+      <c r="B25" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="D25" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="F25" s="32">
+        <v>4305</v>
+      </c>
+      <c r="G25" s="33">
         <v>0.41666666666666669</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="17">
-        <v>3</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="9" t="s">
+      <c r="H25" s="38" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="14">
+        <v>20</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D26" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="F4" s="9">
-        <v>3459.63</v>
-      </c>
-      <c r="G4" s="10">
+      <c r="E26" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" s="16">
+        <v>4022.4</v>
+      </c>
+      <c r="G26" s="17">
         <v>0.45833333333333331</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
-      <c r="B5" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="12">
-        <v>13946.94</v>
-      </c>
-      <c r="G5" s="13">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="19">
-        <v>4</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="6">
-        <v>517.44000000000005</v>
-      </c>
-      <c r="G6" s="7">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="20"/>
-      <c r="B7" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" s="15">
-        <v>8268.52</v>
-      </c>
-      <c r="G7" s="16">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="20"/>
-      <c r="B8" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="31" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" s="31">
-        <v>8438.4</v>
-      </c>
-      <c r="G8" s="25">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="24">
-        <v>5</v>
-      </c>
-      <c r="B9" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" s="33" t="s">
+      <c r="H26" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="F9" s="33">
-        <v>2100</v>
-      </c>
-      <c r="G9" s="34">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="H9" s="35" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>6</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="27">
-        <v>1905</v>
-      </c>
-      <c r="G10" s="4">
-        <v>0.375</v>
-      </c>
-      <c r="H10" s="28" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="24">
-        <v>7</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="F11" s="22">
-        <v>1905</v>
-      </c>
-      <c r="G11" s="23">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="H11" s="29" t="s">
-        <v>11</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A6:A8"/>
+  <mergeCells count="5">
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A10:A11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{541B397F-BB24-4A96-BC56-887CBC266021}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E75687E-D43A-4B76-B1C3-1958C1C6205B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="20,07,26" sheetId="101" r:id="rId1"/>
+    <sheet name="21,07,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,46 +31,25 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="4">
   <si>
     <t>КИ</t>
   </si>
   <si>
-    <t>Симферополь</t>
+    <t>23,07,26</t>
   </si>
   <si>
-    <t>КСК</t>
+    <t>ЛП</t>
   </si>
   <si>
-    <t>НВ</t>
-  </si>
-  <si>
-    <t>Луганск</t>
-  </si>
-  <si>
-    <t>Донецк</t>
-  </si>
-  <si>
-    <t>19,07,26</t>
-  </si>
-  <si>
-    <t>дозаказ</t>
-  </si>
-  <si>
-    <t>20,07,26</t>
-  </si>
-  <si>
-    <t>Мелитополь</t>
-  </si>
-  <si>
-    <t>21,07,26</t>
+    <t>Сочи</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -82,22 +61,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
   </fonts>
   <fills count="4">
@@ -120,7 +83,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -129,16 +92,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color auto="1"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color auto="1"/>
       </right>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -147,119 +110,29 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color auto="1"/>
       </right>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
+      <right style="medium">
+        <color auto="1"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
+      <top style="medium">
+        <color auto="1"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -267,69 +140,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -712,169 +548,103 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="19.7109375" customWidth="1"/>
-    <col min="3" max="3" width="9.28515625" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" style="21" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="14">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1">
         <v>1</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="3">
+        <v>18153.29</v>
+      </c>
+      <c r="G1" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5">
+        <v>2</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="7">
+        <v>18135.710000000003</v>
+      </c>
+      <c r="G2" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3">
+        <v>18078.599999999999</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
         <v>4</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="B4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="18">
-        <v>4020</v>
-      </c>
-      <c r="H1" s="1">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="15">
+      <c r="D4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="8">
-        <v>1525.2</v>
-      </c>
-      <c r="H2" s="2">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="16">
-        <v>3</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="11">
-        <v>918</v>
-      </c>
-      <c r="H3" s="20">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="15">
-        <v>4</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>3</v>
+      <c r="F4" s="7">
+        <v>18156.96</v>
       </c>
       <c r="G4" s="8">
-        <v>1728</v>
-      </c>
-      <c r="H4" s="2">
         <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="16">
-        <v>5</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="G5" s="11">
-        <v>1305</v>
-      </c>
-      <c r="H5" s="20">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
-        <v>6</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="G6" s="4">
-        <v>810</v>
-      </c>
-      <c r="H6" s="5">
-        <v>0.66666666666666663</v>
       </c>
     </row>
   </sheetData>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E75687E-D43A-4B76-B1C3-1958C1C6205B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA588A6-DC02-4FB8-94FB-737F384B8DB1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="21,07,26" sheetId="101" r:id="rId1"/>
+    <sheet name="22,07,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,18 +31,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="12">
   <si>
     <t>КИ</t>
   </si>
   <si>
-    <t>23,07,26</t>
-  </si>
-  <si>
     <t>ЛП</t>
   </si>
   <si>
     <t>Сочи</t>
+  </si>
+  <si>
+    <t>Симферополь</t>
+  </si>
+  <si>
+    <t>24,07,26</t>
+  </si>
+  <si>
+    <t>КСК</t>
+  </si>
+  <si>
+    <t>ЗПФ</t>
+  </si>
+  <si>
+    <t>25,07,26</t>
+  </si>
+  <si>
+    <t>Бердянск</t>
+  </si>
+  <si>
+    <t>НВ</t>
+  </si>
+  <si>
+    <t>Мелитополь</t>
+  </si>
+  <si>
+    <t>Луганск</t>
   </si>
 </sst>
 </file>
@@ -83,7 +107,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -136,11 +160,130 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -164,6 +307,66 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -548,11 +751,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="10.28515625" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -566,16 +769,16 @@
         <v>0</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F1" s="3">
-        <v>18153.29</v>
+        <v>17734.39</v>
       </c>
       <c r="G1" s="4">
-        <v>0.41666666666666669</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -589,16 +792,16 @@
         <v>0</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F2" s="7">
-        <v>18135.710000000003</v>
+        <v>17497.330000000002</v>
       </c>
       <c r="G2" s="8">
-        <v>0.45833333333333331</v>
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -612,42 +815,269 @@
         <v>0</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="3">
+        <v>17469.330000000002</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="9">
+        <v>4</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F4" s="11">
+        <v>10316.100000000002</v>
+      </c>
+      <c r="G4" s="12">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="13"/>
+      <c r="B5" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="3">
-        <v>18078.599999999999</v>
-      </c>
-      <c r="G3" s="4">
+      <c r="C5" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="15">
+        <v>4769.0999999999995</v>
+      </c>
+      <c r="G5" s="16">
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
+    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="17"/>
+      <c r="B6" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="E6" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="19">
+        <v>2503.7999999999997</v>
+      </c>
+      <c r="G6" s="20">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="7">
-        <v>18156.96</v>
-      </c>
-      <c r="G4" s="8">
+      <c r="C7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="3">
+        <v>13055.56</v>
+      </c>
+      <c r="G7" s="4">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>6</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="7">
+        <v>17758.39</v>
+      </c>
+      <c r="G8" s="8">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="3">
+        <v>17577.29</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="9">
+        <v>8</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="11">
+        <v>9815.5400000000009</v>
+      </c>
+      <c r="G10" s="12">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="17"/>
+      <c r="B11" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="19">
+        <v>7637.880000000001</v>
+      </c>
+      <c r="G11" s="20">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="21">
+        <v>9</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="23">
+        <v>6098.88</v>
+      </c>
+      <c r="G12" s="24">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="25"/>
+      <c r="B13" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="27">
+        <v>11147.4</v>
+      </c>
+      <c r="G13" s="28">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
+        <v>10</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="7">
+        <v>17691.16</v>
+      </c>
+      <c r="G14" s="8">
         <v>0.54166666666666663</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A12:A13"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EA588A6-DC02-4FB8-94FB-737F384B8DB1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B3B011B-BD83-4AA3-82D4-8871F3C76AE3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="22,07,26" sheetId="101" r:id="rId1"/>
+    <sheet name="23,07,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="18">
   <si>
     <t>КИ</t>
   </si>
@@ -39,15 +39,9 @@
     <t>ЛП</t>
   </si>
   <si>
-    <t>Сочи</t>
-  </si>
-  <si>
     <t>Симферополь</t>
   </si>
   <si>
-    <t>24,07,26</t>
-  </si>
-  <si>
     <t>КСК</t>
   </si>
   <si>
@@ -67,13 +61,37 @@
   </si>
   <si>
     <t>Луганск</t>
+  </si>
+  <si>
+    <t>Пушкарный</t>
+  </si>
+  <si>
+    <t>23,07,26</t>
+  </si>
+  <si>
+    <t>дозаказ</t>
+  </si>
+  <si>
+    <t>26,07,26</t>
+  </si>
+  <si>
+    <t>Ибрагимова</t>
+  </si>
+  <si>
+    <t>Николаенко</t>
+  </si>
+  <si>
+    <t>ПРС</t>
+  </si>
+  <si>
+    <t>Донецк</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -85,6 +103,14 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="4">
@@ -107,7 +133,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -279,11 +305,141 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -297,21 +453,6 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -321,18 +462,6 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -345,9 +474,6 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -367,6 +493,102 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -751,332 +973,362 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="20">
+        <v>2310</v>
+      </c>
+      <c r="H1" s="22">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="15">
+        <v>2</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="20">
+        <v>3510</v>
+      </c>
+      <c r="H2" s="22">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="47">
         <v>3</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="B3" s="39" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D3" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" s="27">
+        <v>2010</v>
+      </c>
+      <c r="H3" s="26">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="47"/>
+      <c r="B4" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="30">
+        <v>3510</v>
+      </c>
+      <c r="H4" s="32">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="B5" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="3">
-        <v>17734.39</v>
-      </c>
-      <c r="G1" s="4">
-        <v>0.375</v>
+      <c r="F5" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="G5" s="43">
+        <v>6207.6</v>
+      </c>
+      <c r="H5" s="4">
+        <v>0.5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
-        <v>2</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="7" t="s">
+    <row r="6" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8">
+        <v>5</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="7" t="s">
+      <c r="D6" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="7">
-        <v>17497.330000000002</v>
-      </c>
-      <c r="G2" s="8">
-        <v>0.41666666666666669</v>
+      <c r="F6" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="30">
+        <v>4320</v>
+      </c>
+      <c r="H6" s="41">
+        <v>0.54166666666666663</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>3</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="3" t="s">
+    <row r="7" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <f>MAX(A2:A6)+1</f>
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="3">
-        <v>17469.330000000002</v>
-      </c>
-      <c r="G3" s="4">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="9">
-        <v>4</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="11">
-        <v>10316.100000000002</v>
-      </c>
-      <c r="G4" s="12">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="13"/>
-      <c r="B5" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="15">
-        <v>4769.0999999999995</v>
-      </c>
-      <c r="G5" s="16">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
-      <c r="B6" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="19">
-        <v>2503.7999999999997</v>
-      </c>
-      <c r="G6" s="20">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>4</v>
-      </c>
+      <c r="D7" s="24"/>
       <c r="E7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="3">
-        <v>13055.56</v>
-      </c>
-      <c r="G7" s="4">
+      <c r="F7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3">
+        <v>17635.8</v>
+      </c>
+      <c r="H7" s="4">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="45">
+        <f>MAX(A2:A7)+1</f>
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="25"/>
+      <c r="E8" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" s="6">
+        <v>8288.880000000001</v>
+      </c>
+      <c r="H8" s="7">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="46"/>
+      <c r="B9" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="23"/>
+      <c r="E9" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="10">
+        <v>5308.32</v>
+      </c>
+      <c r="H9" s="11">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="48">
+        <f>MAX(A3:A9)+1</f>
+        <v>8</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="19"/>
+      <c r="E10" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="13">
+        <v>15056.58</v>
+      </c>
+      <c r="H10" s="14">
         <v>0.375</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
-        <v>6</v>
-      </c>
-      <c r="B8" s="6" t="s">
+    <row r="11" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="49"/>
+      <c r="B11" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="35"/>
+      <c r="E11" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="G11" s="34">
+        <v>834.54000000000008</v>
+      </c>
+      <c r="H11" s="36">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="50"/>
+      <c r="B12" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D12" s="37"/>
+      <c r="E12" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" s="17">
+        <v>1693.38</v>
+      </c>
+      <c r="H12" s="18">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="45">
+        <f>MAX(A3:A12)+1</f>
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="25"/>
+      <c r="E13" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" s="6">
+        <v>2616.8999999999996</v>
+      </c>
+      <c r="H13" s="7">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="46"/>
+      <c r="B14" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="23"/>
+      <c r="E14" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" s="7">
-        <v>17758.39</v>
-      </c>
-      <c r="G8" s="8">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="3">
-        <v>17577.29</v>
-      </c>
-      <c r="G9" s="4">
+      <c r="G14" s="10">
+        <v>14596.900000000001</v>
+      </c>
+      <c r="H14" s="11">
         <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="9">
-        <v>8</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="11">
-        <v>9815.5400000000009</v>
-      </c>
-      <c r="G10" s="12">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="17"/>
-      <c r="B11" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="19">
-        <v>7637.880000000001</v>
-      </c>
-      <c r="G11" s="20">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="21">
-        <v>9</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="23">
-        <v>6098.88</v>
-      </c>
-      <c r="G12" s="24">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="25"/>
-      <c r="B13" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="27">
-        <v>11147.4</v>
-      </c>
-      <c r="G13" s="28">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5">
-        <v>10</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="7">
-        <v>17691.16</v>
-      </c>
-      <c r="G14" s="8">
-        <v>0.54166666666666663</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
+  <mergeCells count="4">
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B3B011B-BD83-4AA3-82D4-8871F3C76AE3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCA4F632-1D50-4CCF-84AA-3F7668D85353}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="19">
   <si>
     <t>КИ</t>
   </si>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t>Донецк</t>
+  </si>
+  <si>
+    <t>24,07,26</t>
   </si>
 </sst>
 </file>
@@ -133,7 +136,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -435,11 +438,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -589,6 +607,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -973,7 +1009,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19.42578125" customWidth="1"/>
@@ -1323,6 +1359,84 @@
         <v>0.41666666666666669</v>
       </c>
     </row>
+    <row r="15" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>10</v>
+      </c>
+      <c r="B15" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="C15" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="G15" s="43">
+        <v>1200</v>
+      </c>
+      <c r="H15" s="4">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="52">
+        <v>11</v>
+      </c>
+      <c r="B16" s="53" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="54" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16" s="55" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="54" t="s">
+        <v>3</v>
+      </c>
+      <c r="G16" s="54">
+        <v>1500</v>
+      </c>
+      <c r="H16" s="56">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>12</v>
+      </c>
+      <c r="B17" s="51" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="D17" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="43" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" s="43">
+        <v>1500</v>
+      </c>
+      <c r="H17" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A13:A14"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -1,22 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\графики\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF38610-ECB4-40A0-9CDE-E58CDAE006B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4567EABC-411D-42AF-B1D4-670FC5717F5A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="23,07,26" sheetId="101" r:id="rId1"/>
+    <sheet name="24,07,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
@@ -25,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="13">
   <si>
     <t>КИ</t>
   </si>
@@ -39,15 +45,6 @@
     <t>КСК</t>
   </si>
   <si>
-    <t>ЗПФ</t>
-  </si>
-  <si>
-    <t>25,07,26</t>
-  </si>
-  <si>
-    <t>Бердянск</t>
-  </si>
-  <si>
     <t>НВ</t>
   </si>
   <si>
@@ -60,15 +57,9 @@
     <t>дозаказ</t>
   </si>
   <si>
-    <t>26,07,26</t>
-  </si>
-  <si>
     <t>Донецк</t>
   </si>
   <si>
-    <t>24,07,26</t>
-  </si>
-  <si>
     <t>27,07,26</t>
   </si>
   <si>
@@ -76,13 +67,16 @@
   </si>
   <si>
     <t>Сочи</t>
+  </si>
+  <si>
+    <t>29,07,26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -102,6 +96,21 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -124,7 +133,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -259,68 +268,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -338,15 +292,6 @@
     <xf numFmtId="49" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -356,9 +301,6 @@
     <xf numFmtId="49" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -368,46 +310,37 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -792,493 +725,170 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:H19"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="21"/>
+    <col min="2" max="2" width="20.140625" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="19">
         <v>1</v>
       </c>
-      <c r="B1" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="20" t="s">
+      <c r="B1" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="E1" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" s="20">
-        <v>210</v>
-      </c>
-      <c r="H1" s="22">
-        <v>0.375</v>
+      <c r="D1" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="8">
+        <v>2415</v>
+      </c>
+      <c r="H1" s="1">
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+      <c r="A2" s="20">
         <v>2</v>
       </c>
-      <c r="B2" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="17" t="s">
+      <c r="B2" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="17">
-        <v>510</v>
-      </c>
-      <c r="H2" s="3">
-        <v>0.41666666666666669</v>
+      <c r="D2" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="10">
+        <v>2520</v>
+      </c>
+      <c r="H2" s="12">
+        <v>0.45833333333333331</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="19">
         <v>3</v>
       </c>
-      <c r="B3" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="20">
-        <v>765</v>
-      </c>
-      <c r="H3" s="22">
-        <v>0.45833333333333331</v>
+      <c r="D3" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="8">
+        <v>2115</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0.5</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+      <c r="A4" s="20">
         <v>4</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="F4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="10">
+        <v>1205.2</v>
+      </c>
+      <c r="H4" s="12">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="17">
         <v>5</v>
       </c>
-      <c r="F4" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="17">
-        <v>4410</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="19">
-        <v>5</v>
-      </c>
-      <c r="B5" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="20" t="s">
+      <c r="B5" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="G5" s="20">
-        <v>4020</v>
-      </c>
-      <c r="H5" s="22">
-        <v>0.41666666666666669</v>
+      <c r="D5" s="6"/>
+      <c r="E5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2">
+        <v>2601.0499999999997</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0.5</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <f>MAX(A4:A5)+1</f>
-        <v>6</v>
-      </c>
-      <c r="B6" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="A6" s="18"/>
+      <c r="B6" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="D6" s="7"/>
+      <c r="E6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G6" s="2">
-        <v>9332.9999999999982</v>
-      </c>
-      <c r="H6" s="3">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="19">
-        <f>MAX(A4:A6)+1</f>
-        <v>7</v>
-      </c>
-      <c r="B7" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="28"/>
-      <c r="E7" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="G7" s="27">
-        <v>12856.319999999998</v>
-      </c>
-      <c r="H7" s="22">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <f>MAX(A4:A7)+1</f>
-        <v>8</v>
-      </c>
-      <c r="B8" s="31" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" s="2">
-        <v>17646</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="23">
-        <f>MAX(A5:A8)+1</f>
-        <v>9</v>
-      </c>
-      <c r="B9" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G9" s="4">
-        <v>9687.74</v>
-      </c>
-      <c r="H9" s="5">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="24"/>
-      <c r="B10" s="34" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="G10" s="6">
-        <v>8010.5199999999995</v>
-      </c>
-      <c r="H10" s="7">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <f>MAX(A6:A10)+1</f>
-        <v>10</v>
-      </c>
-      <c r="B11" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G11" s="2">
-        <v>15695.96</v>
-      </c>
-      <c r="H11" s="3">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="19">
-        <f>MAX(A6:A11)+1</f>
-        <v>11</v>
-      </c>
-      <c r="B12" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="28"/>
-      <c r="E12" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="G12" s="27">
-        <v>13721.14</v>
-      </c>
-      <c r="H12" s="22">
+      <c r="G6" s="4">
+        <v>11756.989999999996</v>
+      </c>
+      <c r="H6" s="5">
         <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="25">
-        <f>MAX(A6:A12)+1</f>
-        <v>12</v>
-      </c>
-      <c r="B13" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="12"/>
-      <c r="E13" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="G13" s="8">
-        <v>5919.48</v>
-      </c>
-      <c r="H13" s="9">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="26"/>
-      <c r="B14" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="16"/>
-      <c r="E14" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="G14" s="10">
-        <v>5871.7199999999993</v>
-      </c>
-      <c r="H14" s="11">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="19">
-        <f>MAX(A6:A14)+1</f>
-        <v>13</v>
-      </c>
-      <c r="B15" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="C15" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="D15" s="28"/>
-      <c r="E15" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="G15" s="27">
-        <v>17478.29</v>
-      </c>
-      <c r="H15" s="22">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <f>MAX(A6:A15)+1</f>
-        <v>14</v>
-      </c>
-      <c r="B16" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D16" s="14"/>
-      <c r="E16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G16" s="2">
-        <v>14641.119999999999</v>
-      </c>
-      <c r="H16" s="3">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="19">
-        <f>MAX(A6:A16)+1</f>
-        <v>15</v>
-      </c>
-      <c r="B17" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="D17" s="28"/>
-      <c r="E17" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="G17" s="27">
-        <v>17585.059999999998</v>
-      </c>
-      <c r="H17" s="22">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="1">
-        <f>MAX(A6:A17)+1</f>
-        <v>16</v>
-      </c>
-      <c r="B18" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D18" s="14"/>
-      <c r="E18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G18" s="2">
-        <v>18026.280000000002</v>
-      </c>
-      <c r="H18" s="3">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="19">
-        <f>MAX(A6:A18)+1</f>
-        <v>17</v>
-      </c>
-      <c r="B19" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="C19" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="D19" s="28"/>
-      <c r="E19" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="G19" s="27">
-        <v>17476.72</v>
-      </c>
-      <c r="H19" s="22">
-        <v>0.58333333333333337</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A13:A14"/>
+  <mergeCells count="1">
+    <mergeCell ref="A5:A6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4567EABC-411D-42AF-B1D4-670FC5717F5A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96B59840-4059-40E8-B355-2F78269D8603}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="24,07,26" sheetId="101" r:id="rId1"/>
+    <sheet name="28,07,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
@@ -31,18 +31,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="11">
   <si>
     <t>КИ</t>
   </si>
   <si>
     <t>ЛП</t>
-  </si>
-  <si>
-    <t>Симферополь</t>
-  </si>
-  <si>
-    <t>КСК</t>
   </si>
   <si>
     <t>НВ</t>
@@ -54,29 +48,29 @@
     <t>Луганск</t>
   </si>
   <si>
-    <t>дозаказ</t>
-  </si>
-  <si>
     <t>Донецк</t>
   </si>
   <si>
-    <t>27,07,26</t>
+    <t>30,07,26</t>
   </si>
   <si>
-    <t>28,07,26</t>
+    <t>01,08,26</t>
+  </si>
+  <si>
+    <t>Бердянск</t>
+  </si>
+  <si>
+    <t>предзаказ</t>
   </si>
   <si>
     <t>Сочи</t>
-  </si>
-  <si>
-    <t>29,07,26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -88,29 +82,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -133,7 +104,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -268,11 +239,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -289,24 +297,6 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -316,32 +306,77 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -725,168 +760,350 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H14"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="21"/>
-    <col min="2" max="2" width="20.140625" customWidth="1"/>
-    <col min="4" max="4" width="11.140625" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" customWidth="1"/>
+    <col min="2" max="2" width="17.140625" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19">
+      <c r="A1" s="9">
         <v>1</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="11">
+        <v>18126.759999999998</v>
+      </c>
+      <c r="G1" s="6">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="12">
+        <v>2</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="14">
+        <v>18171.45</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="9">
+        <v>3</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="11">
+        <v>17890.199999999997</v>
+      </c>
+      <c r="G3" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="12">
+        <v>4</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="14">
+        <v>18182.159999999996</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="9">
+        <v>5</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="11">
+        <v>18167.34</v>
+      </c>
+      <c r="G5" s="6">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="27">
+        <v>6</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1104.48</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="28"/>
+      <c r="B7" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="16">
+        <v>8809.7200000000012</v>
+      </c>
+      <c r="G7" s="17">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="29"/>
+      <c r="B8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F8" s="4">
+        <v>8130.0599999999995</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="30">
+        <v>7</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="19">
+        <v>4005</v>
+      </c>
+      <c r="G9" s="20">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="H9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="31"/>
+      <c r="B10" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="F10" s="22">
+        <v>1472.01</v>
+      </c>
+      <c r="G10" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="H10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="32"/>
+      <c r="B11" s="24" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" s="25">
+        <v>12426.6</v>
+      </c>
+      <c r="G11" s="26">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="H11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="12">
         <v>8</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="9" t="s">
+      <c r="B12" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E12" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="F12" s="14">
+        <v>5401.7999999999993</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="H12" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="8" t="s">
+    </row>
+    <row r="13" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="9">
+        <v>9</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="F13" s="11">
+        <v>5454.6</v>
+      </c>
+      <c r="G13" s="6">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="H13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="12">
+        <v>10</v>
+      </c>
+      <c r="B14" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="8">
-        <v>2415</v>
-      </c>
-      <c r="H1" s="1">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20">
+      <c r="C14" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="10" t="s">
+      <c r="F14" s="14">
+        <v>15500.699999999999</v>
+      </c>
+      <c r="G14" s="1">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H14" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="10">
-        <v>2520</v>
-      </c>
-      <c r="H2" s="12">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="19">
-        <v>3</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="8">
-        <v>2115</v>
-      </c>
-      <c r="H3" s="1">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="20">
-        <v>4</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="10">
-        <v>1205.2</v>
-      </c>
-      <c r="H4" s="12">
-        <v>0.58333333333333337</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="17">
-        <v>5</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" s="2">
-        <v>2601.0499999999997</v>
-      </c>
-      <c r="H5" s="3">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="18"/>
-      <c r="B6" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" s="4">
-        <v>11756.989999999996</v>
-      </c>
-      <c r="H6" s="5">
-        <v>0.5</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A5:A6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="A9:A11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96B59840-4059-40E8-B355-2F78269D8603}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F89CCE2-6684-4B3C-86B6-02E5E2D8BECA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="28,07,26" sheetId="101" r:id="rId1"/>
+    <sheet name="29,07,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="15">
   <si>
     <t>КИ</t>
   </si>
@@ -60,17 +60,29 @@
     <t>Бердянск</t>
   </si>
   <si>
-    <t>предзаказ</t>
-  </si>
-  <si>
     <t>Сочи</t>
+  </si>
+  <si>
+    <t>дозаказ</t>
+  </si>
+  <si>
+    <t>Симферополь</t>
+  </si>
+  <si>
+    <t>31,07,26</t>
+  </si>
+  <si>
+    <t>КСК</t>
+  </si>
+  <si>
+    <t>ЗПФ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -82,6 +94,14 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="4">
@@ -104,7 +124,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -227,19 +247,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -252,27 +259,61 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </left>
       <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -280,7 +321,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -291,21 +332,12 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -324,15 +356,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -342,37 +365,79 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -760,350 +825,323 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
-    <col min="8" max="8" width="9.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9">
+      <c r="A1" s="15">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="E1" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="20">
+        <v>5715</v>
+      </c>
+      <c r="H1" s="21">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="38">
+        <v>2</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="11">
-        <v>18126.759999999998</v>
-      </c>
-      <c r="G1" s="6">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12">
-        <v>2</v>
-      </c>
-      <c r="B2" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="14" t="s">
+      <c r="D2" s="22"/>
+      <c r="E2" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="13">
+        <v>13866.84</v>
+      </c>
+      <c r="H2" s="14">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="39"/>
+      <c r="B3" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="14">
-        <v>18171.45</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="9">
-        <v>3</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="D3" s="25"/>
+      <c r="E3" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="24">
+        <v>2539.8399999999997</v>
+      </c>
+      <c r="H3" s="26">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="40"/>
+      <c r="B4" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="11">
-        <v>17890.199999999997</v>
-      </c>
-      <c r="G3" s="6">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="12">
-        <v>4</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="14">
-        <v>18182.159999999996</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0.54166666666666663</v>
+      <c r="D4" s="29"/>
+      <c r="E4" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="28">
+        <v>1265.2599999999995</v>
+      </c>
+      <c r="H4" s="30">
+        <v>0.375</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9">
+        <v>3</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="31"/>
+      <c r="E5" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G5" s="11">
+        <v>11131.199999999999</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="38">
+        <v>4</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="22"/>
+      <c r="E6" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" s="13">
+        <v>10512.859999999997</v>
+      </c>
+      <c r="H6" s="14">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="39"/>
+      <c r="B7" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="25"/>
+      <c r="E7" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="24">
+        <v>1752.3000000000002</v>
+      </c>
+      <c r="H7" s="26">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="40"/>
+      <c r="B8" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="29"/>
+      <c r="E8" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" s="28">
+        <v>5701.8</v>
+      </c>
+      <c r="H8" s="30">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="36">
         <v>5</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="11" t="s">
+      <c r="B9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D9" s="16"/>
+      <c r="E9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G9" s="2">
+        <v>2720.36</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="37"/>
+      <c r="B10" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="34"/>
+      <c r="E10" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="33" t="s">
+        <v>2</v>
+      </c>
+      <c r="G10" s="33">
+        <v>4295.45</v>
+      </c>
+      <c r="H10" s="21">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
         <v>6</v>
       </c>
-      <c r="E5" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="11">
-        <v>18167.34</v>
-      </c>
-      <c r="G5" s="6">
+      <c r="B11" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="35"/>
+      <c r="E11" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="G11" s="8">
+        <v>2371.2200000000003</v>
+      </c>
+      <c r="H11" s="4">
         <v>0.58333333333333337</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="27">
-        <v>6</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="2" t="s">
+    <row r="12" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="9">
+        <v>7</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="D12" s="31"/>
+      <c r="E12" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="11">
+        <v>17441.560000000001</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
+        <v>8</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="35"/>
+      <c r="E13" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="2">
-        <v>1104.48</v>
-      </c>
-      <c r="G6" s="3">
+      <c r="G13" s="8">
+        <v>17649.77</v>
+      </c>
+      <c r="H13" s="4">
         <v>0.625</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="28"/>
-      <c r="B7" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="F7" s="16">
-        <v>8809.7200000000012</v>
-      </c>
-      <c r="G7" s="17">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="29"/>
-      <c r="B8" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F8" s="4">
-        <v>8130.0599999999995</v>
-      </c>
-      <c r="G8" s="5">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="30">
-        <v>7</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="19">
-        <v>4005</v>
-      </c>
-      <c r="G9" s="20">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="H9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="31"/>
-      <c r="B10" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="F10" s="22">
-        <v>1472.01</v>
-      </c>
-      <c r="G10" s="23">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="H10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="32"/>
-      <c r="B11" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="25" t="s">
-        <v>2</v>
-      </c>
-      <c r="F11" s="25">
-        <v>12426.6</v>
-      </c>
-      <c r="G11" s="26">
-        <v>0.45833333333333331</v>
-      </c>
-      <c r="H11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="12">
-        <v>8</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="F12" s="14">
-        <v>5401.7999999999993</v>
-      </c>
-      <c r="G12" s="1">
-        <v>0.5</v>
-      </c>
-      <c r="H12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9">
-        <v>9</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="F13" s="11">
-        <v>5454.6</v>
-      </c>
-      <c r="G13" s="6">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="H13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="12">
-        <v>10</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="F14" s="14">
-        <v>15500.699999999999</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="H14" t="s">
-        <v>9</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A9:A10"/>
     <mergeCell ref="A6:A8"/>
-    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="A2:A4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F89CCE2-6684-4B3C-86B6-02E5E2D8BECA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7860875-917C-4B86-B0A0-82E437453800}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="29,07,26" sheetId="101" r:id="rId1"/>
+    <sheet name="30,07,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="11">
   <si>
     <t>КИ</t>
   </si>
@@ -42,47 +42,35 @@
     <t>НВ</t>
   </si>
   <si>
-    <t>Мелитополь</t>
-  </si>
-  <si>
     <t>Луганск</t>
   </si>
   <si>
     <t>Донецк</t>
   </si>
   <si>
-    <t>30,07,26</t>
-  </si>
-  <si>
     <t>01,08,26</t>
   </si>
   <si>
-    <t>Бердянск</t>
-  </si>
-  <si>
     <t>Сочи</t>
   </si>
   <si>
-    <t>дозаказ</t>
-  </si>
-  <si>
     <t>Симферополь</t>
   </si>
   <si>
-    <t>31,07,26</t>
-  </si>
-  <si>
     <t>КСК</t>
   </si>
   <si>
     <t>ЗПФ</t>
+  </si>
+  <si>
+    <t>02,08,26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -94,14 +82,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
   </fonts>
   <fills count="4">
@@ -124,7 +104,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -259,44 +239,12 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -304,16 +252,27 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -321,11 +280,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -347,15 +303,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -365,82 +312,46 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -825,323 +736,217 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5">
         <v>1</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="7">
+        <v>15280.68</v>
+      </c>
+      <c r="G1" s="3">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="11">
+        <v>2</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1">
+        <v>15820.990000000002</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="12"/>
+      <c r="B3" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="16">
+        <v>1743.48</v>
+      </c>
+      <c r="G3" s="17">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="13">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="9">
+        <v>9497.5999999999985</v>
+      </c>
+      <c r="G4" s="10">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="14"/>
+      <c r="B5" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="19">
+        <v>8634.7800000000007</v>
+      </c>
+      <c r="G5" s="20">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="11">
         <v>4</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="B6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1">
+        <v>13800.840000000002</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="21"/>
+      <c r="B7" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="C7" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="23">
+        <v>2417.71</v>
+      </c>
+      <c r="G7" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12"/>
+      <c r="B8" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="20">
-        <v>5715</v>
-      </c>
-      <c r="H1" s="21">
-        <v>0.625</v>
+      <c r="F8" s="16">
+        <v>1612.56</v>
+      </c>
+      <c r="G8" s="17">
+        <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="38">
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>5</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="22"/>
-      <c r="E2" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="13">
-        <v>13866.84</v>
-      </c>
-      <c r="H2" s="14">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="39"/>
-      <c r="B3" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="25"/>
-      <c r="E3" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="24">
-        <v>2539.8399999999997</v>
-      </c>
-      <c r="H3" s="26">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="40"/>
-      <c r="B4" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="29"/>
-      <c r="E4" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="28">
-        <v>1265.2599999999995</v>
-      </c>
-      <c r="H4" s="30">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9">
-        <v>3</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="31"/>
-      <c r="E5" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="G5" s="11">
-        <v>11131.199999999999</v>
-      </c>
-      <c r="H5" s="1">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="38">
-        <v>4</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="22"/>
-      <c r="E6" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" s="13">
-        <v>10512.859999999997</v>
-      </c>
-      <c r="H6" s="14">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="39"/>
-      <c r="B7" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="25"/>
-      <c r="E7" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" s="24">
-        <v>1752.3000000000002</v>
-      </c>
-      <c r="H7" s="26">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="40"/>
-      <c r="B8" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="29"/>
-      <c r="E8" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G8" s="28">
-        <v>5701.8</v>
-      </c>
-      <c r="H8" s="30">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="36">
-        <v>5</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="16"/>
-      <c r="E9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G9" s="2">
-        <v>2720.36</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="F9" s="7">
+        <v>17606.16</v>
+      </c>
+      <c r="G9" s="3">
         <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="37"/>
-      <c r="B10" s="32" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="33" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="34"/>
-      <c r="E10" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="33" t="s">
-        <v>2</v>
-      </c>
-      <c r="G10" s="33">
-        <v>4295.45</v>
-      </c>
-      <c r="H10" s="21">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
-        <v>6</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="35"/>
-      <c r="E11" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="G11" s="8">
-        <v>2371.2200000000003</v>
-      </c>
-      <c r="H11" s="4">
-        <v>0.58333333333333337</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="9">
-        <v>7</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="31"/>
-      <c r="E12" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="11">
-        <v>17441.560000000001</v>
-      </c>
-      <c r="H12" s="1">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
-        <v>8</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="35"/>
-      <c r="E13" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="G13" s="8">
-        <v>17649.77</v>
-      </c>
-      <c r="H13" s="4">
-        <v>0.625</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A9:A10"/>
     <mergeCell ref="A6:A8"/>
-    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -1,28 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7860875-917C-4B86-B0A0-82E437453800}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C14E9F6-C862-4B17-BB1D-45A986BC3C38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="30,07,26" sheetId="101" r:id="rId1"/>
+    <sheet name="31,07,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
@@ -31,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="16">
   <si>
     <t>КИ</t>
   </si>
@@ -65,12 +59,27 @@
   <si>
     <t>02,08,26</t>
   </si>
+  <si>
+    <t>дозаказ</t>
+  </si>
+  <si>
+    <t>Бердянск</t>
+  </si>
+  <si>
+    <t>Мелитополь</t>
+  </si>
+  <si>
+    <t>03,08,26</t>
+  </si>
+  <si>
+    <t>04,08,26</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -82,6 +91,14 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="4">
@@ -104,7 +121,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -276,11 +293,54 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -312,15 +372,6 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -342,9 +393,6 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -352,6 +400,111 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -736,217 +889,617 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5">
+    <row r="1" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="51">
         <v>1</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="37" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="39" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="38">
+        <v>1981.2</v>
+      </c>
+      <c r="H1" s="2">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="52"/>
+      <c r="B2" s="40" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="42" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="41">
+        <v>6325.8</v>
+      </c>
+      <c r="H2" s="43">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="54">
+        <v>2</v>
+      </c>
+      <c r="B3" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="47" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="47" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="45">
+        <v>1377.6</v>
+      </c>
+      <c r="H3" s="10">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="55"/>
+      <c r="B4" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="49" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="49" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" s="49">
+        <v>2160</v>
+      </c>
+      <c r="H4" s="22">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="25">
+        <v>3</v>
+      </c>
+      <c r="B5" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="C5" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F5" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="7">
-        <v>15280.68</v>
-      </c>
-      <c r="G1" s="3">
+      <c r="G5" s="35">
+        <v>510</v>
+      </c>
+      <c r="H5" s="29">
         <v>0.375</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="11">
-        <v>2</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1">
-        <v>15820.990000000002</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12"/>
-      <c r="B3" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="16">
-        <v>1743.48</v>
-      </c>
-      <c r="G3" s="17">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="13">
-        <v>3</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="9">
-        <v>9497.5999999999985</v>
-      </c>
-      <c r="G4" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
-      <c r="B5" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="F5" s="19">
-        <v>8634.7800000000007</v>
-      </c>
-      <c r="G5" s="20">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>4</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="30"/>
+      <c r="E6" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="16">
+        <v>17561.68</v>
+      </c>
+      <c r="H6" s="17">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="51">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="23"/>
+      <c r="E7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="1">
+        <v>13866.14</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="53"/>
+      <c r="B8" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="33"/>
+      <c r="E8" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="19">
+        <v>1966.3799999999997</v>
+      </c>
+      <c r="H8" s="20">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="52"/>
+      <c r="B9" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="31"/>
+      <c r="E9" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="13">
+        <v>1759.38</v>
+      </c>
+      <c r="H9" s="14">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
         <v>6</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="B10" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="32"/>
+      <c r="E10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="7">
+        <v>14860.759999999997</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="51">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="23"/>
+      <c r="E11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G11" s="1">
+        <v>5256.92</v>
+      </c>
+      <c r="H11" s="2">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="52"/>
+      <c r="B12" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="31"/>
+      <c r="E12" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="G12" s="13">
+        <v>11740.74</v>
+      </c>
+      <c r="H12" s="14">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="54">
+        <v>8</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="21"/>
+      <c r="E13" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="G13" s="9">
+        <v>12834.22</v>
+      </c>
+      <c r="H13" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="55"/>
+      <c r="B14" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="30"/>
+      <c r="E14" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="G14" s="16">
+        <v>4831</v>
+      </c>
+      <c r="H14" s="17">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A15" s="51">
+        <v>9</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D15" s="23"/>
+      <c r="E15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G15" s="1">
+        <v>7129.7199999999993</v>
+      </c>
+      <c r="H15" s="2">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="52"/>
+      <c r="B16" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D16" s="31"/>
+      <c r="E16" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="G16" s="13">
+        <v>6414</v>
+      </c>
+      <c r="H16" s="14">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
         <v>10</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1">
-        <v>13800.840000000002</v>
-      </c>
-      <c r="G6" s="2">
+      <c r="B17" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="32"/>
+      <c r="E17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G17" s="7">
+        <v>10672.2</v>
+      </c>
+      <c r="H17" s="3">
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="21"/>
-      <c r="B7" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="23">
-        <v>2417.71</v>
-      </c>
-      <c r="G7" s="24">
+    <row r="18" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="25">
+        <v>11</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="28"/>
+      <c r="E18" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="G18" s="27">
+        <v>12325.52</v>
+      </c>
+      <c r="H18" s="29">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="5">
+        <v>12</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D19" s="32"/>
+      <c r="E19" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="7">
+        <v>17583.84</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="25">
+        <v>13</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="D20" s="28"/>
+      <c r="E20" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="27">
+        <v>17665.38</v>
+      </c>
+      <c r="H20" s="29">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="5">
+        <v>14</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" s="32"/>
+      <c r="E21" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G21" s="7">
+        <v>16782.48</v>
+      </c>
+      <c r="H21" s="3">
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="12"/>
-      <c r="B8" s="15" t="s">
+    <row r="22" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="25">
+        <v>15</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="D22" s="28"/>
+      <c r="E22" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="G22" s="27">
+        <v>16885.699999999997</v>
+      </c>
+      <c r="H22" s="29">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="5">
+        <v>16</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="E8" s="16" t="s">
+      <c r="C23" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="32"/>
+      <c r="E23" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F8" s="16">
-        <v>1612.56</v>
-      </c>
-      <c r="G8" s="17">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="5">
-        <v>5</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E9" s="7" t="s">
+      <c r="G23" s="7">
+        <v>12749.48</v>
+      </c>
+      <c r="H23" s="3">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A24" s="51">
+        <v>17</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="23"/>
+      <c r="E24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F9" s="7">
-        <v>17606.16</v>
-      </c>
-      <c r="G9" s="3">
-        <v>0.5</v>
+      <c r="G24" s="1">
+        <v>9308.8799999999992</v>
+      </c>
+      <c r="H24" s="2">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="52"/>
+      <c r="B25" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="31"/>
+      <c r="E25" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="G25" s="13">
+        <v>5568.24</v>
+      </c>
+      <c r="H25" s="14">
+        <v>0.41666666666666669</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A5"/>
+  <mergeCells count="7">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A13:A14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FC91C99-9CC8-420C-B527-5869878EA3D8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{749BD997-77E4-4045-A6EC-51D2A22FD23B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="03,08,26" sheetId="101" r:id="rId1"/>
+    <sheet name="04,08,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="6">
   <si>
     <t>КИ</t>
   </si>
@@ -39,16 +39,10 @@
     <t>ЛП</t>
   </si>
   <si>
-    <t>НВ</t>
+    <t>Сочи</t>
   </si>
   <si>
-    <t>Луганск</t>
-  </si>
-  <si>
-    <t>Донецк</t>
-  </si>
-  <si>
-    <t>Сочи</t>
+    <t>06,08,26</t>
   </si>
   <si>
     <t>Симферополь</t>
@@ -56,27 +50,12 @@
   <si>
     <t>КСК</t>
   </si>
-  <si>
-    <t>дозаказ</t>
-  </si>
-  <si>
-    <t>Мелитополь</t>
-  </si>
-  <si>
-    <t>03,08,26</t>
-  </si>
-  <si>
-    <t>04,08,26</t>
-  </si>
-  <si>
-    <t>05,08,26</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -88,14 +67,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
   </fonts>
   <fills count="4">
@@ -118,7 +89,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -171,147 +142,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -325,59 +160,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -761,186 +554,149 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="12.28515625" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" customWidth="1"/>
-    <col min="4" max="4" width="9.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5">
         <v>1</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>10</v>
+      <c r="B1" s="6" t="s">
+        <v>2</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G1" s="8" t="s">
+      <c r="D1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="7">
+        <v>18176.620000000003</v>
+      </c>
+      <c r="G1" s="8">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
         <v>2</v>
       </c>
-      <c r="H1" s="8">
-        <v>3615</v>
-      </c>
-      <c r="I1" s="10">
+      <c r="B2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4">
+        <v>18044.509999999998</v>
+      </c>
+      <c r="G2" s="1">
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18">
+    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="21" t="s">
+      <c r="C3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="H2" s="21">
-        <v>2715</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.375</v>
+      <c r="D3" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="7">
+        <v>18013.8</v>
+      </c>
+      <c r="G3" s="8">
+        <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13">
+    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="16" t="s">
+      <c r="E4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="4">
+        <v>18081.12</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>5</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="H3" s="16">
-        <v>3105</v>
-      </c>
-      <c r="I3" s="5">
-        <v>0.41666666666666669</v>
+      <c r="D5" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="7">
+        <v>18120.239999999994</v>
+      </c>
+      <c r="G5" s="8">
+        <v>0.58333333333333337</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="18">
+    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
         <v>4</v>
       </c>
-      <c r="B4" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="20" t="s">
+      <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="C6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="H4" s="21">
-        <v>1005</v>
-      </c>
-      <c r="I4" s="1">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="13">
+      <c r="D6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="E5" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="H5" s="16">
-        <v>2610</v>
-      </c>
-      <c r="I5" s="5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>6</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" s="4">
-        <v>17807.399999999998</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0.41666666666666669</v>
+      <c r="F6" s="4">
+        <v>17131.080000000002</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.625</v>
       </c>
     </row>
   </sheetData>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{749BD997-77E4-4045-A6EC-51D2A22FD23B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15D120CD-8FF3-492D-AE37-319196B6BCEA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="04,08,26" sheetId="101" r:id="rId1"/>
+    <sheet name="05,08,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,18 +31,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="7">
   <si>
     <t>КИ</t>
-  </si>
-  <si>
-    <t>ЛП</t>
-  </si>
-  <si>
-    <t>Сочи</t>
-  </si>
-  <si>
-    <t>06,08,26</t>
   </si>
   <si>
     <t>Симферополь</t>
@@ -50,11 +41,26 @@
   <si>
     <t>КСК</t>
   </si>
+  <si>
+    <t>07,08,26</t>
+  </si>
+  <si>
+    <t>08,08,26</t>
+  </si>
+  <si>
+    <t>НВ</t>
+  </si>
+  <si>
+    <t>Луганск</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -89,7 +95,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -142,11 +148,130 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -170,6 +295,57 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -554,152 +730,169 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5">
         <v>1</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="9">
+        <v>17.503</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="7">
-        <v>18176.620000000003</v>
-      </c>
-      <c r="G1" s="8">
-        <v>0.41666666666666669</v>
+      <c r="G1" s="7">
+        <v>17616.700000000004</v>
+      </c>
+      <c r="H1" s="8">
+        <v>0.375</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="10">
+        <v>17.475999999999999</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="4">
-        <v>18044.509999999998</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.45833333333333331</v>
+      <c r="G2" s="4">
+        <v>17627.53</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.375</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>3</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="9">
+        <v>17.457999999999998</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="G3" s="7">
+        <v>17619.18</v>
+      </c>
+      <c r="H3" s="8">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="11">
+        <v>4</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="13">
+        <v>0.51700000000000002</v>
+      </c>
+      <c r="D4" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="7">
-        <v>18013.8</v>
-      </c>
-      <c r="G3" s="8">
-        <v>0.5</v>
+      <c r="E4" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="14">
+        <v>517.43999999999994</v>
+      </c>
+      <c r="H4" s="15">
+        <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
+    <row r="5" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="16"/>
+      <c r="B5" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="18">
+        <v>10.718</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="F5" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" s="19">
+        <v>10718.320000000002</v>
+      </c>
+      <c r="H5" s="20">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="21"/>
+      <c r="B6" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="23">
+        <v>6.5919999999999996</v>
+      </c>
+      <c r="D6" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="4">
-        <v>18081.12</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
+      <c r="E6" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="24" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="7">
-        <v>18120.239999999994</v>
-      </c>
-      <c r="G5" s="8">
-        <v>0.58333333333333337</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="4">
-        <v>17131.080000000002</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0.625</v>
+      <c r="G6" s="24">
+        <v>6721.67</v>
+      </c>
+      <c r="H6" s="25">
+        <v>0.45833333333333331</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A4:A6"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15D120CD-8FF3-492D-AE37-319196B6BCEA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66000193-4B9E-4434-A14B-0468F3663273}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="9">
   <si>
     <t>КИ</t>
   </si>
@@ -53,15 +53,18 @@
   <si>
     <t>Луганск</t>
   </si>
+  <si>
+    <t>06,08,26</t>
+  </si>
+  <si>
+    <t>дозаказ</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -73,6 +76,14 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="4">
@@ -271,7 +282,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -297,56 +308,53 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -730,10 +738,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="1" max="1" width="7.140625" customWidth="1"/>
     <col min="2" max="2" width="20.42578125" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" customWidth="1"/>
     <col min="5" max="5" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -744,12 +754,10 @@
       <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9">
-        <v>17.503</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>0</v>
       </c>
+      <c r="D1" s="7"/>
       <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
@@ -770,12 +778,10 @@
       <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="10">
-        <v>17.475999999999999</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>0</v>
       </c>
+      <c r="D2" s="4"/>
       <c r="E2" s="4" t="s">
         <v>4</v>
       </c>
@@ -796,12 +802,10 @@
       <c r="B3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="9">
-        <v>17.457999999999998</v>
-      </c>
-      <c r="D3" s="7" t="s">
+      <c r="C3" s="7" t="s">
         <v>0</v>
       </c>
+      <c r="D3" s="7"/>
       <c r="E3" s="7" t="s">
         <v>4</v>
       </c>
@@ -816,77 +820,97 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="11">
+      <c r="A4" s="18">
         <v>4</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="13">
-        <v>0.51700000000000002</v>
-      </c>
-      <c r="D4" s="14" t="s">
+      <c r="C4" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="D4" s="10"/>
+      <c r="E4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="10">
         <v>517.43999999999994</v>
       </c>
-      <c r="H4" s="15">
+      <c r="H4" s="11">
         <v>0.45833333333333331</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="16"/>
-      <c r="B5" s="17" t="s">
+      <c r="A5" s="19"/>
+      <c r="B5" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="18">
-        <v>10.718</v>
-      </c>
-      <c r="D5" s="19" t="s">
+      <c r="C5" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="D5" s="13"/>
+      <c r="E5" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="19">
+      <c r="G5" s="13">
         <v>10718.320000000002</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5" s="14">
         <v>0.45833333333333331</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="21"/>
-      <c r="B6" s="22" t="s">
+      <c r="A6" s="20"/>
+      <c r="B6" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="23">
-        <v>6.5919999999999996</v>
-      </c>
-      <c r="D6" s="24" t="s">
+      <c r="C6" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="D6" s="16"/>
+      <c r="E6" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F6" s="24" t="s">
+      <c r="F6" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="16">
         <v>6721.67</v>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="17">
         <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="21">
+        <v>5</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="G7" s="23">
+        <v>855</v>
+      </c>
+      <c r="H7" s="8">
+        <v>0.625</v>
       </c>
     </row>
   </sheetData>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66000193-4B9E-4434-A14B-0468F3663273}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{804461CC-7F34-4BAB-AE61-7B3B88D17D06}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="05,08,26" sheetId="101" r:id="rId1"/>
+    <sheet name="06,08,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="14">
   <si>
     <t>КИ</t>
   </si>
@@ -42,22 +42,37 @@
     <t>КСК</t>
   </si>
   <si>
-    <t>07,08,26</t>
-  </si>
-  <si>
     <t>08,08,26</t>
   </si>
   <si>
     <t>НВ</t>
   </si>
   <si>
-    <t>Луганск</t>
-  </si>
-  <si>
     <t>06,08,26</t>
   </si>
   <si>
     <t>дозаказ</t>
+  </si>
+  <si>
+    <t>Пенза</t>
+  </si>
+  <si>
+    <t>ЛП</t>
+  </si>
+  <si>
+    <t>ЗПФ</t>
+  </si>
+  <si>
+    <t>Донецк</t>
+  </si>
+  <si>
+    <t>09,08,26</t>
+  </si>
+  <si>
+    <t>Сочи</t>
+  </si>
+  <si>
+    <t>07,08,26</t>
   </si>
 </sst>
 </file>
@@ -106,7 +121,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -278,11 +293,113 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -291,9 +408,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -335,26 +449,125 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -738,184 +951,397 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.140625" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5">
+      <c r="A1" s="2">
         <v>1</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="56" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="55" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="55">
+        <v>2505</v>
+      </c>
+      <c r="H1" s="1">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="36">
+        <v>2</v>
+      </c>
+      <c r="B2" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="44" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="35" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="44">
+        <v>2505</v>
+      </c>
+      <c r="H2" s="25">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="37">
+        <v>3</v>
+      </c>
+      <c r="B3" s="45" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C3" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7" t="s">
+      <c r="D3" s="34" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="18">
+        <v>3105</v>
+      </c>
+      <c r="H3" s="19">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>4</v>
+      </c>
+      <c r="B4" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="27"/>
+      <c r="E4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="7">
-        <v>17616.700000000004</v>
-      </c>
-      <c r="H1" s="8">
+      <c r="G4" s="6">
+        <v>13753.279999999999</v>
+      </c>
+      <c r="H4" s="7">
         <v>0.375</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
+    <row r="5" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>5</v>
+      </c>
+      <c r="B5" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="26"/>
+      <c r="E5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G5" s="3">
+        <v>11680.56</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="38">
+        <v>6</v>
+      </c>
+      <c r="B6" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="29"/>
+      <c r="E6" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="20">
+        <v>5061.3999999999996</v>
+      </c>
+      <c r="H6" s="21">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="39"/>
+      <c r="B7" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="31"/>
+      <c r="E7" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="30">
+        <v>6174.7400000000007</v>
+      </c>
+      <c r="H7" s="32">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="39"/>
+      <c r="B8" s="49" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="31"/>
+      <c r="E8" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="30">
+        <v>5007.5999999999995</v>
+      </c>
+      <c r="H8" s="32">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="40"/>
+      <c r="B9" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="24"/>
+      <c r="E9" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="23">
+        <v>7059.08</v>
+      </c>
+      <c r="H9" s="25">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="41">
+        <v>7</v>
+      </c>
+      <c r="B10" s="51" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="22"/>
+      <c r="E10" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="G10" s="9">
+        <v>5007.5999999999995</v>
+      </c>
+      <c r="H10" s="10">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="42"/>
+      <c r="B11" s="52" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="33"/>
+      <c r="E11" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="G11" s="15">
+        <v>5007.5999999999995</v>
+      </c>
+      <c r="H11" s="16">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="27"/>
+      <c r="E12" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="6">
+        <v>17807.399999999998</v>
+      </c>
+      <c r="H12" s="7">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="41">
+        <v>9</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="22"/>
+      <c r="E13" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="G13" s="9">
+        <v>14972.180000000002</v>
+      </c>
+      <c r="H13" s="10">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A14" s="43"/>
+      <c r="B14" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C14" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4" t="s">
+      <c r="D14" s="28"/>
+      <c r="E14" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="G14" s="12">
+        <v>2490.54</v>
+      </c>
+      <c r="H14" s="13">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="42"/>
+      <c r="B15" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" s="33"/>
+      <c r="E15" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="G15" s="15">
+        <v>57.12</v>
+      </c>
+      <c r="H15" s="16">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>10</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16" s="27"/>
+      <c r="E16" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="G2" s="4">
-        <v>17627.53</v>
-      </c>
-      <c r="H2" s="1">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
-        <v>3</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="7">
-        <v>17619.18</v>
-      </c>
-      <c r="H3" s="8">
+      <c r="G16" s="6">
+        <v>17697.579999999998</v>
+      </c>
+      <c r="H16" s="7">
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="18">
-        <v>4</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4" s="10">
-        <v>517.43999999999994</v>
-      </c>
-      <c r="H4" s="11">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="19"/>
-      <c r="B5" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="G5" s="13">
-        <v>10718.320000000002</v>
-      </c>
-      <c r="H5" s="14">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="20"/>
-      <c r="B6" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="G6" s="16">
-        <v>6721.67</v>
-      </c>
-      <c r="H6" s="17">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="21">
-        <v>5</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="G7" s="23">
-        <v>855</v>
-      </c>
-      <c r="H7" s="8">
-        <v>0.625</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A4:A6"/>
+  <mergeCells count="3">
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{804461CC-7F34-4BAB-AE61-7B3B88D17D06}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE305B3-40F5-4FC8-975F-44C3157A98F8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="06,08,26" sheetId="101" r:id="rId1"/>
+    <sheet name="07,08,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="13">
   <si>
     <t>КИ</t>
   </si>
@@ -42,21 +42,9 @@
     <t>КСК</t>
   </si>
   <si>
-    <t>08,08,26</t>
-  </si>
-  <si>
     <t>НВ</t>
   </si>
   <si>
-    <t>06,08,26</t>
-  </si>
-  <si>
-    <t>дозаказ</t>
-  </si>
-  <si>
-    <t>Пенза</t>
-  </si>
-  <si>
     <t>ЛП</t>
   </si>
   <si>
@@ -66,20 +54,29 @@
     <t>Донецк</t>
   </si>
   <si>
-    <t>09,08,26</t>
-  </si>
-  <si>
     <t>Сочи</t>
   </si>
   <si>
-    <t>07,08,26</t>
+    <t>10,08,26</t>
+  </si>
+  <si>
+    <t>11,08,26</t>
+  </si>
+  <si>
+    <t>Бердянск</t>
+  </si>
+  <si>
+    <t>Мелитополь</t>
+  </si>
+  <si>
+    <t>Луганск</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -91,14 +88,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
   </fonts>
   <fills count="4">
@@ -121,7 +110,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -293,113 +282,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -431,15 +318,6 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -449,124 +327,49 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -951,397 +754,332 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2">
         <v>1</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="B1" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="3">
+        <v>14951.8</v>
+      </c>
+      <c r="G1" s="1">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="6">
+        <v>17579.580000000002</v>
+      </c>
+      <c r="G2" s="7">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>3</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3">
+        <v>17560.620000000003</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="20">
+        <v>4</v>
+      </c>
+      <c r="B4" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="55" t="s">
+      <c r="C4" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="56" t="s">
+      <c r="D4" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="14">
+        <v>6141.4000000000015</v>
+      </c>
+      <c r="G4" s="15">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="21"/>
+      <c r="B5" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="18">
+        <v>2316.8000000000002</v>
+      </c>
+      <c r="G5" s="19">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="22"/>
+      <c r="B6" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="55" t="s">
+      <c r="C6" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="16">
+        <v>9080.2800000000007</v>
+      </c>
+      <c r="G6" s="17">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
         <v>5</v>
       </c>
-      <c r="F1" s="55" t="s">
+      <c r="B7" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="55">
-        <v>2505</v>
-      </c>
-      <c r="H1" s="1">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="36">
+      <c r="E7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="3">
+        <v>17161.580000000002</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="20">
+        <v>6</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="14">
+        <v>3030.72</v>
+      </c>
+      <c r="G8" s="15">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="22"/>
+      <c r="B9" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="16">
+        <v>8964.840000000002</v>
+      </c>
+      <c r="G9" s="17">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>7</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="53" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="44" t="s">
+      <c r="F10" s="3">
+        <v>17644.68</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>8</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="35" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="44" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="44" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="44">
-        <v>2505</v>
-      </c>
-      <c r="H2" s="25">
-        <v>0.58333333333333337</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="37">
+      <c r="D11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" s="6">
+        <v>17646.919999999998</v>
+      </c>
+      <c r="G11" s="7">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="23">
+        <v>9</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="45" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="17" t="s">
+      <c r="F12" s="9">
+        <v>6694.68</v>
+      </c>
+      <c r="G12" s="10">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="24"/>
+      <c r="B13" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="34" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="18">
-        <v>3105</v>
-      </c>
-      <c r="H3" s="19">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
-        <v>4</v>
-      </c>
-      <c r="B4" s="46" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="6" t="s">
+      <c r="D13" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="27"/>
-      <c r="E4" s="6" t="s">
+      <c r="E13" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G4" s="6">
-        <v>13753.279999999999</v>
-      </c>
-      <c r="H4" s="7">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>5</v>
-      </c>
-      <c r="B5" s="47" t="s">
+      <c r="F13" s="12">
+        <v>9667.34</v>
+      </c>
+      <c r="G13" s="13">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C14" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="26"/>
-      <c r="E5" s="3" t="s">
+      <c r="E14" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G5" s="3">
-        <v>11680.56</v>
-      </c>
-      <c r="H5" s="1">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="38">
-        <v>6</v>
-      </c>
-      <c r="B6" s="48" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="29"/>
-      <c r="E6" s="20" t="s">
-        <v>3</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" s="20">
-        <v>5061.3999999999996</v>
-      </c>
-      <c r="H6" s="21">
+      <c r="F14" s="6">
+        <v>16702.310000000001</v>
+      </c>
+      <c r="G14" s="7">
         <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="39"/>
-      <c r="B7" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="31"/>
-      <c r="E7" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="G7" s="30">
-        <v>6174.7400000000007</v>
-      </c>
-      <c r="H7" s="32">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="39"/>
-      <c r="B8" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="31"/>
-      <c r="E8" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="G8" s="30">
-        <v>5007.5999999999995</v>
-      </c>
-      <c r="H8" s="32">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="40"/>
-      <c r="B9" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="24"/>
-      <c r="E9" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="G9" s="23">
-        <v>7059.08</v>
-      </c>
-      <c r="H9" s="25">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="41">
-        <v>7</v>
-      </c>
-      <c r="B10" s="51" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="22"/>
-      <c r="E10" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="G10" s="9">
-        <v>5007.5999999999995</v>
-      </c>
-      <c r="H10" s="10">
-        <v>0.58333333333333337</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="42"/>
-      <c r="B11" s="52" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="33"/>
-      <c r="E11" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="G11" s="15">
-        <v>5007.5999999999995</v>
-      </c>
-      <c r="H11" s="16">
-        <v>0.58333333333333337</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
-        <v>8</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="27"/>
-      <c r="E12" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="G12" s="6">
-        <v>17807.399999999998</v>
-      </c>
-      <c r="H12" s="7">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="41">
-        <v>9</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="22"/>
-      <c r="E13" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="G13" s="9">
-        <v>14972.180000000002</v>
-      </c>
-      <c r="H13" s="10">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A14" s="43"/>
-      <c r="B14" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D14" s="28"/>
-      <c r="E14" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="G14" s="12">
-        <v>2490.54</v>
-      </c>
-      <c r="H14" s="13">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="42"/>
-      <c r="B15" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D15" s="33"/>
-      <c r="E15" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="G15" s="15">
-        <v>57.12</v>
-      </c>
-      <c r="H15" s="16">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
-        <v>10</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D16" s="27"/>
-      <c r="E16" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="G16" s="6">
-        <v>17697.579999999998</v>
-      </c>
-      <c r="H16" s="7">
-        <v>0.41666666666666669</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A12:A13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CE305B3-40F5-4FC8-975F-44C3157A98F8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF681F6-7011-4E0F-9117-28AE7C7C29F6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="07,08,26" sheetId="101" r:id="rId1"/>
+    <sheet name="10,08,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,52 +31,43 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="10">
   <si>
     <t>КИ</t>
   </si>
   <si>
-    <t>Симферополь</t>
-  </si>
-  <si>
-    <t>КСК</t>
-  </si>
-  <si>
     <t>НВ</t>
   </si>
   <si>
     <t>ЛП</t>
   </si>
   <si>
-    <t>ЗПФ</t>
-  </si>
-  <si>
     <t>Донецк</t>
   </si>
   <si>
-    <t>Сочи</t>
-  </si>
-  <si>
     <t>10,08,26</t>
   </si>
   <si>
-    <t>11,08,26</t>
-  </si>
-  <si>
-    <t>Бердянск</t>
-  </si>
-  <si>
-    <t>Мелитополь</t>
-  </si>
-  <si>
-    <t>Луганск</t>
+    <t>дозаказ</t>
+  </si>
+  <si>
+    <t>Бычков</t>
+  </si>
+  <si>
+    <t>№1</t>
+  </si>
+  <si>
+    <t>12,08,26</t>
+  </si>
+  <si>
+    <t>№2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -88,6 +79,14 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="4">
@@ -208,13 +207,15 @@
     </border>
     <border>
       <left style="medium">
-        <color auto="1"/>
+        <color indexed="64"/>
       </left>
       <right style="medium">
-        <color auto="1"/>
+        <color indexed="64"/>
       </right>
       <top/>
-      <bottom/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -225,8 +226,8 @@
         <color auto="1"/>
       </right>
       <top/>
-      <bottom style="thin">
-        <color auto="1"/>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -235,19 +236,6 @@
         <color auto="1"/>
       </left>
       <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
         <color indexed="64"/>
       </right>
       <top/>
@@ -257,9 +245,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -270,13 +269,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -286,7 +285,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -294,82 +293,58 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -754,332 +729,119 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
     <col min="4" max="4" width="13.140625" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2">
+    <row r="1" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3">
         <v>1</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="B1" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="G1" s="14">
+        <v>2497.62</v>
+      </c>
+      <c r="H1" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>2</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E2" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="13">
+        <v>2100</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="9">
+        <v>3</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="3">
-        <v>14951.8</v>
-      </c>
-      <c r="G1" s="1">
-        <v>0.375</v>
+      <c r="G3" s="5">
+        <v>2721.37</v>
+      </c>
+      <c r="H3" s="6">
+        <v>0.5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+    <row r="4" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10"/>
+      <c r="B4" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="6">
-        <v>17579.580000000002</v>
-      </c>
-      <c r="G2" s="7">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>3</v>
-      </c>
-      <c r="B3" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="3">
-        <v>17560.620000000003</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="20">
-        <v>4</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="14">
-        <v>6141.4000000000015</v>
-      </c>
-      <c r="G4" s="15">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="21"/>
-      <c r="B5" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="18">
-        <v>2316.8000000000002</v>
-      </c>
-      <c r="G5" s="19">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="22"/>
-      <c r="B6" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="F6" s="16">
-        <v>9080.2800000000007</v>
-      </c>
-      <c r="G6" s="17">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>5</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" s="3">
-        <v>17161.580000000002</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="20">
-        <v>6</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="14">
-        <v>3030.72</v>
-      </c>
-      <c r="G8" s="15">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="22"/>
-      <c r="B9" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="16">
-        <v>8964.840000000002</v>
-      </c>
-      <c r="G9" s="17">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2">
-        <v>7</v>
-      </c>
-      <c r="B10" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F10" s="3">
-        <v>17644.68</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
-        <v>8</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="F11" s="6">
-        <v>17646.919999999998</v>
-      </c>
-      <c r="G11" s="7">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="23">
-        <v>9</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="9">
-        <v>6694.68</v>
-      </c>
-      <c r="G12" s="10">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="24"/>
-      <c r="B13" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="F13" s="12">
-        <v>9667.34</v>
-      </c>
-      <c r="G13" s="13">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
-        <v>10</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="6">
-        <v>16702.310000000001</v>
-      </c>
-      <c r="G14" s="7">
+      <c r="G4" s="7">
+        <v>13142.089999999997</v>
+      </c>
+      <c r="H4" s="8">
         <v>0.5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
+  <mergeCells count="1">
+    <mergeCell ref="A3:A4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF681F6-7011-4E0F-9117-28AE7C7C29F6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1177D46-C6D4-49F4-BC8A-B6FC28575CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,12 +17,6 @@
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
@@ -31,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="15">
   <si>
     <t>КИ</t>
   </si>
@@ -61,6 +55,21 @@
   </si>
   <si>
     <t>№2</t>
+  </si>
+  <si>
+    <t>Симферополь</t>
+  </si>
+  <si>
+    <t>11,08,26</t>
+  </si>
+  <si>
+    <t>КСК</t>
+  </si>
+  <si>
+    <t>Луганск</t>
+  </si>
+  <si>
+    <t>ЗПФ</t>
   </si>
 </sst>
 </file>
@@ -285,7 +294,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -311,12 +320,6 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -346,6 +349,21 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -729,10 +747,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" customWidth="1"/>
     <col min="4" max="4" width="13.140625" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
@@ -741,22 +759,22 @@
       <c r="A1" s="3">
         <v>1</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="14">
+      <c r="G1" s="12">
         <v>2497.62</v>
       </c>
       <c r="H1" s="4">
@@ -767,81 +785,157 @@
       <c r="A2" s="2">
         <v>2</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="13">
+      <c r="G2" s="11">
         <v>2100</v>
       </c>
       <c r="H2" s="1">
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="9">
+    <row r="3" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>3</v>
       </c>
-      <c r="B3" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="5">
-        <v>2721.37</v>
-      </c>
-      <c r="H3" s="6">
-        <v>0.5</v>
+      <c r="D3" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="12">
+        <v>3555</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0.375</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10"/>
-      <c r="B4" s="19" t="s">
+      <c r="A4" s="2">
+        <v>4</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="11">
+        <v>3540</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="19">
+        <v>5</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C5" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D5" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G5" s="5">
+        <v>2721.37</v>
+      </c>
+      <c r="H5" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="20"/>
+      <c r="B6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F6" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G6" s="7">
         <v>13142.089999999997</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H6" s="8">
         <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="23"/>
+      <c r="E7" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="22">
+        <v>13088.68</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0.41666666666666669</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A5:A6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -1,22 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\графики\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1177D46-C6D4-49F4-BC8A-B6FC28575CAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32FE34B5-FA2D-416A-B1FB-7A432E5FBD6C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="10,08,26" sheetId="101" r:id="rId1"/>
+    <sheet name="11,08,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
@@ -25,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="8">
   <si>
     <t>КИ</t>
   </si>
@@ -45,31 +51,10 @@
     <t>дозаказ</t>
   </si>
   <si>
-    <t>Бычков</t>
+    <t>13,08,26</t>
   </si>
   <si>
-    <t>№1</t>
-  </si>
-  <si>
-    <t>12,08,26</t>
-  </si>
-  <si>
-    <t>№2</t>
-  </si>
-  <si>
-    <t>Симферополь</t>
-  </si>
-  <si>
-    <t>11,08,26</t>
-  </si>
-  <si>
-    <t>КСК</t>
-  </si>
-  <si>
-    <t>Луганск</t>
-  </si>
-  <si>
-    <t>ЗПФ</t>
+    <t>Сочи</t>
   </si>
 </sst>
 </file>
@@ -118,7 +103,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -228,13 +213,45 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -242,47 +259,12 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="medium">
@@ -294,7 +276,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -308,52 +290,7 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -362,8 +299,47 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -747,190 +723,158 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="19.28515625" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" style="19" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3">
         <v>1</v>
       </c>
-      <c r="B1" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="12" t="s">
+      <c r="B1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="12">
-        <v>2497.62</v>
+      <c r="D1" s="15"/>
+      <c r="E1" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="9">
+        <v>18069.04</v>
       </c>
       <c r="H1" s="4">
-        <v>0.45833333333333331</v>
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>2</v>
       </c>
-      <c r="B2" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="11" t="s">
+      <c r="B2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="11">
-        <v>2100</v>
+      <c r="D2" s="16"/>
+      <c r="E2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="7">
+        <v>18036.810000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>0.5</v>
+        <v>0.45833333333333331</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>3</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="12" t="s">
+      <c r="B3" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="12">
-        <v>3555</v>
+      <c r="D3" s="15"/>
+      <c r="E3" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="9">
+        <v>17503.2</v>
       </c>
       <c r="H3" s="4">
-        <v>0.375</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>4</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="11" t="s">
+      <c r="B4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="11">
-        <v>3540</v>
+      <c r="D4" s="16"/>
+      <c r="E4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" s="7">
+        <v>18177.039999999997</v>
       </c>
       <c r="H4" s="1">
-        <v>0.41666666666666669</v>
+        <v>0.54166666666666663</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="19">
+      <c r="A5" s="20">
         <v>5</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="B5" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G5" s="5">
-        <v>2721.37</v>
-      </c>
-      <c r="H5" s="6">
+      <c r="D5" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="11">
+        <v>1005</v>
+      </c>
+      <c r="H5" s="5">
         <v>0.5</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="20"/>
-      <c r="B6" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="A6" s="21"/>
+      <c r="B6" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="G6" s="7">
-        <v>13142.089999999997</v>
-      </c>
-      <c r="H6" s="8">
+      <c r="D6" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" s="13">
+        <v>570</v>
+      </c>
+      <c r="H6" s="14">
         <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="23"/>
-      <c r="E7" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" s="22">
-        <v>13088.68</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0.41666666666666669</v>
       </c>
     </row>
   </sheetData>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32FE34B5-FA2D-416A-B1FB-7A432E5FBD6C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C079BCA8-7AAC-483D-9BC1-70379210FD70}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="11,08,26" sheetId="101" r:id="rId1"/>
+    <sheet name="12,08,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="11">
   <si>
     <t>КИ</t>
   </si>
@@ -42,26 +42,35 @@
     <t>ЛП</t>
   </si>
   <si>
-    <t>Донецк</t>
+    <t>Сочи</t>
   </si>
   <si>
-    <t>10,08,26</t>
+    <t>Симферополь</t>
   </si>
   <si>
-    <t>дозаказ</t>
+    <t>14,08,26</t>
   </si>
   <si>
-    <t>13,08,26</t>
+    <t>КСК</t>
   </si>
   <si>
-    <t>Сочи</t>
+    <t>15,08,26</t>
+  </si>
+  <si>
+    <t>Бердянск</t>
+  </si>
+  <si>
+    <t>Мелитополь</t>
+  </si>
+  <si>
+    <t>Луганск</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -73,14 +82,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
   </fonts>
   <fills count="4">
@@ -103,7 +104,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -214,29 +215,49 @@
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
+        <color auto="1"/>
+      </right>
+      <top/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+        <color auto="1"/>
+      </right>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -244,29 +265,12 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -276,7 +280,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -305,40 +309,73 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -723,163 +760,324 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="12.28515625" customWidth="1"/>
-    <col min="4" max="4" width="11.85546875" style="19" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3">
         <v>1</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="15"/>
+      <c r="D1" s="9" t="s">
+        <v>5</v>
+      </c>
       <c r="E1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="9">
-        <v>18069.04</v>
-      </c>
-      <c r="H1" s="4">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="F1" s="9">
+        <v>17009.400000000001</v>
+      </c>
+      <c r="G1" s="4">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>2</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="16"/>
+      <c r="D2" s="7" t="s">
+        <v>5</v>
+      </c>
       <c r="E2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="7">
+        <v>17628.839999999997</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="10">
+        <v>3</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="7">
-        <v>18036.810000000001</v>
-      </c>
-      <c r="H2" s="1">
+      <c r="F3" s="13">
+        <v>4727.74</v>
+      </c>
+      <c r="G3" s="5">
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="14"/>
+      <c r="B4" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="C4" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="16">
+        <v>2004.6</v>
+      </c>
+      <c r="G4" s="17">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="14"/>
+      <c r="B5" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="16">
+        <v>4606.380000000001</v>
+      </c>
+      <c r="G5" s="17">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="14"/>
+      <c r="B6" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" s="16">
+        <v>5007.5999999999995</v>
+      </c>
+      <c r="G6" s="17">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="11"/>
+      <c r="B7" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="19">
+        <v>3968.3</v>
+      </c>
+      <c r="G7" s="20">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>4</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="15"/>
-      <c r="E3" s="9" t="s">
+      <c r="E8" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="9">
-        <v>17503.2</v>
-      </c>
-      <c r="H3" s="4">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>4</v>
-      </c>
-      <c r="B4" s="6" t="s">
+      <c r="F8" s="7">
+        <v>17570.419999999998</v>
+      </c>
+      <c r="G8" s="1">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="10">
+        <v>5</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="7" t="s">
+      <c r="E9" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="13">
+        <v>5035.8899999999994</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="14"/>
+      <c r="B10" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="16">
+        <v>3810.32</v>
+      </c>
+      <c r="G10" s="17">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="11"/>
+      <c r="B11" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="19">
+        <v>9153.0000000000018</v>
+      </c>
+      <c r="G11" s="20">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="21">
         <v>6</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="G4" s="7">
-        <v>18177.039999999997</v>
-      </c>
-      <c r="H4" s="1">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="20">
-        <v>5</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="11" t="s">
+      <c r="B12" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="G5" s="11">
-        <v>1005</v>
-      </c>
-      <c r="H5" s="5">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="21"/>
-      <c r="B6" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="13" t="s">
+      <c r="F12" s="23">
+        <v>593.28</v>
+      </c>
+      <c r="G12" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A13" s="25"/>
+      <c r="B13" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="G6" s="13">
-        <v>570</v>
-      </c>
-      <c r="H6" s="14">
-        <v>0.5</v>
+      <c r="F13" s="27">
+        <v>8360.8799999999992</v>
+      </c>
+      <c r="G13" s="28">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="29"/>
+      <c r="B14" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="31">
+        <v>8891.8900000000012</v>
+      </c>
+      <c r="G14" s="32">
+        <v>0.45833333333333331</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A5:A6"/>
+  <mergeCells count="3">
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="A12:A14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C079BCA8-7AAC-483D-9BC1-70379210FD70}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A90AEBC1-64A5-4E5E-85DE-3B298E6146F5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="12,08,26" sheetId="101" r:id="rId1"/>
+    <sheet name="13,08,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="10">
   <si>
     <t>КИ</t>
   </si>
@@ -48,22 +48,19 @@
     <t>Симферополь</t>
   </si>
   <si>
-    <t>14,08,26</t>
-  </si>
-  <si>
     <t>КСК</t>
   </si>
   <si>
     <t>15,08,26</t>
   </si>
   <si>
-    <t>Бердянск</t>
-  </si>
-  <si>
-    <t>Мелитополь</t>
-  </si>
-  <si>
-    <t>Луганск</t>
+    <t>ЗПФ</t>
+  </si>
+  <si>
+    <t>16,08,26</t>
+  </si>
+  <si>
+    <t>Донецк</t>
   </si>
 </sst>
 </file>
@@ -104,7 +101,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -214,43 +211,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color auto="1"/>
       </left>
@@ -280,7 +240,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -309,12 +269,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -322,60 +276,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -760,11 +672,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="18.85546875" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -775,16 +687,16 @@
         <v>4</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D1" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>6</v>
-      </c>
       <c r="F1" s="9">
-        <v>17009.400000000001</v>
+        <v>14669.72</v>
       </c>
       <c r="G1" s="4">
         <v>0.375</v>
@@ -795,289 +707,94 @@
         <v>2</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F2" s="7">
-        <v>17628.839999999997</v>
+        <v>17503.2</v>
       </c>
       <c r="G2" s="1">
-        <v>0.41666666666666669</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="10">
+      <c r="A3" s="15">
         <v>3</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="13" t="s">
+      <c r="B3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="13">
-        <v>4727.74</v>
+      <c r="F3" s="11">
+        <v>15744.24</v>
       </c>
       <c r="G3" s="5">
-        <v>0.45833333333333331</v>
+        <v>0.375</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="14"/>
-      <c r="B4" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="16" t="s">
+    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="16"/>
+      <c r="B4" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="16">
-        <v>2004.6</v>
-      </c>
-      <c r="G4" s="17">
-        <v>0.45833333333333331</v>
+      <c r="F4" s="13">
+        <v>1968.0600000000002</v>
+      </c>
+      <c r="G4" s="14">
+        <v>0.375</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="14"/>
-      <c r="B5" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="16" t="s">
+    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="F5" s="16">
-        <v>4606.380000000001</v>
-      </c>
-      <c r="G5" s="17">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="14"/>
-      <c r="B6" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="F6" s="16">
-        <v>5007.5999999999995</v>
-      </c>
-      <c r="G6" s="17">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="11"/>
-      <c r="B7" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="F7" s="19">
-        <v>3968.3</v>
-      </c>
-      <c r="G7" s="20">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2">
-        <v>4</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" s="7">
-        <v>17570.419999999998</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="10">
-        <v>5</v>
-      </c>
-      <c r="B9" s="12" t="s">
+      <c r="D5" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="13" t="s">
+      <c r="E5" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F9" s="13">
-        <v>5035.8899999999994</v>
-      </c>
-      <c r="G9" s="5">
+      <c r="F5" s="7">
+        <v>17859.079999999998</v>
+      </c>
+      <c r="G5" s="1">
         <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="14"/>
-      <c r="B10" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" s="16">
-        <v>3810.32</v>
-      </c>
-      <c r="G10" s="17">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="11"/>
-      <c r="B11" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="19">
-        <v>9153.0000000000018</v>
-      </c>
-      <c r="G11" s="20">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="21">
-        <v>6</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" s="23">
-        <v>593.28</v>
-      </c>
-      <c r="G12" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A13" s="25"/>
-      <c r="B13" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="F13" s="27">
-        <v>8360.8799999999992</v>
-      </c>
-      <c r="G13" s="28">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="29"/>
-      <c r="B14" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="D14" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="E14" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="F14" s="31">
-        <v>8891.8900000000012</v>
-      </c>
-      <c r="G14" s="32">
-        <v>0.45833333333333331</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="A12:A14"/>
+  <mergeCells count="1">
+    <mergeCell ref="A3:A4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A90AEBC1-64A5-4E5E-85DE-3B298E6146F5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{045430F9-387C-4C6A-B6FC-4FB877E2FB6F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="13,08,26" sheetId="101" r:id="rId1"/>
+    <sheet name="14,08,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="14">
   <si>
     <t>КИ</t>
   </si>
@@ -51,9 +51,6 @@
     <t>КСК</t>
   </si>
   <si>
-    <t>15,08,26</t>
-  </si>
-  <si>
     <t>ЗПФ</t>
   </si>
   <si>
@@ -61,6 +58,21 @@
   </si>
   <si>
     <t>Донецк</t>
+  </si>
+  <si>
+    <t>17,08,26</t>
+  </si>
+  <si>
+    <t>Бердянск</t>
+  </si>
+  <si>
+    <t>Мелитополь</t>
+  </si>
+  <si>
+    <t>Луганск</t>
+  </si>
+  <si>
+    <t>18,08,26</t>
   </si>
 </sst>
 </file>
@@ -101,7 +113,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -236,11 +248,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -288,6 +337,54 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -672,129 +769,398 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="4" max="4" width="16.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3">
+    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="15">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="11">
+        <v>3276.3599999999997</v>
+      </c>
+      <c r="G1" s="5">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="16"/>
+      <c r="B2" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="13">
+        <v>6962.9999999999991</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="17">
+        <v>2</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="19">
+        <v>9082.1999999999989</v>
+      </c>
+      <c r="G3" s="20">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="21"/>
+      <c r="B4" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="23">
+        <v>5004</v>
+      </c>
+      <c r="G4" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="25"/>
+      <c r="B5" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="27">
+        <v>8964.15</v>
+      </c>
+      <c r="G5" s="28">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="15">
+        <v>3</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C6" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="11">
+        <v>11215.979999999998</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="29"/>
+      <c r="B7" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="31">
+        <v>4649.4599999999991</v>
+      </c>
+      <c r="G7" s="32">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="16"/>
+      <c r="B8" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="13">
+        <v>1850.04</v>
+      </c>
+      <c r="G8" s="14">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>4</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="7">
+        <v>17547.560000000001</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="15">
+        <v>5</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="11">
+        <v>8593.130000000001</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="16"/>
+      <c r="B11" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="13">
+        <v>8484.9500000000007</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>6</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="7">
+        <v>17819.179999999997</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
         <v>7</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="B13" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="9">
+        <v>17754.54</v>
+      </c>
+      <c r="G13" s="4">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>8</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="D14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="9">
-        <v>14669.72</v>
-      </c>
-      <c r="G1" s="4">
+      <c r="F14" s="7">
+        <v>14386.36</v>
+      </c>
+      <c r="G14" s="1">
         <v>0.375</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>2</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="7" t="s">
+    <row r="15" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3">
+        <v>9</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="7">
-        <v>17503.2</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="15">
-        <v>3</v>
-      </c>
-      <c r="B3" s="10" t="s">
+      <c r="D15" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="9">
+        <v>10834.199999999999</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>10</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="11" t="s">
+      <c r="C16" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F16" s="7">
+        <v>17508.819999999992</v>
+      </c>
+      <c r="G16" s="1">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
+        <v>11</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="11">
-        <v>15744.24</v>
-      </c>
-      <c r="G3" s="5">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="16"/>
-      <c r="B4" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="13">
-        <v>1968.0600000000002</v>
-      </c>
-      <c r="G4" s="14">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="7" t="s">
+      <c r="C17" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="7">
-        <v>17859.079999999998</v>
-      </c>
-      <c r="G5" s="1">
+      <c r="F17" s="9">
+        <v>17310.52</v>
+      </c>
+      <c r="G17" s="4">
         <v>0.41666666666666669</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A3:A4"/>
+  <mergeCells count="4">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="A10:A11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{045430F9-387C-4C6A-B6FC-4FB877E2FB6F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FEB92DC-B1BC-4418-A385-ABE73C192A68}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="14,08,26" sheetId="101" r:id="rId1"/>
+    <sheet name="17,08,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="14">
   <si>
     <t>КИ</t>
   </si>
@@ -54,9 +54,6 @@
     <t>ЗПФ</t>
   </si>
   <si>
-    <t>16,08,26</t>
-  </si>
-  <si>
     <t>Донецк</t>
   </si>
   <si>
@@ -72,14 +69,17 @@
     <t>Луганск</t>
   </si>
   <si>
-    <t>18,08,26</t>
+    <t>дозаказ</t>
+  </si>
+  <si>
+    <t>19,08,26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -91,6 +91,14 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="4">
@@ -113,7 +121,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -252,9 +260,18 @@
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -266,22 +283,65 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </left>
       <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -289,7 +349,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -303,89 +363,107 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -769,398 +847,240 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="19.42578125" customWidth="1"/>
-    <col min="4" max="4" width="16.85546875" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" customWidth="1"/>
+    <col min="5" max="5" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="15">
+    <row r="1" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="30">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="33" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="33">
+        <v>1905</v>
+      </c>
+      <c r="H1" s="34">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="16">
+        <v>2</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="26">
+        <v>1718.64</v>
+      </c>
+      <c r="H2" s="10">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="17"/>
+      <c r="B3" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="28">
+        <v>2115</v>
+      </c>
+      <c r="H3" s="29">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="30">
+        <v>3</v>
+      </c>
+      <c r="B4" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C4" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="36">
+        <v>3215.04</v>
+      </c>
+      <c r="H4" s="7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="23">
+        <v>1264.08</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D6" s="19"/>
+      <c r="E6" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" s="6">
+        <v>14736.039999999999</v>
+      </c>
+      <c r="H6" s="4">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="14">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="20"/>
+      <c r="E7" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="G7" s="9">
+        <v>1159.2</v>
+      </c>
+      <c r="H7" s="10">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15"/>
+      <c r="B8" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" s="21"/>
+      <c r="E8" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" s="12">
+        <v>11289.920000000002</v>
+      </c>
+      <c r="H8" s="13">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
         <v>7</v>
       </c>
-      <c r="E1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="11">
-        <v>3276.3599999999997</v>
-      </c>
-      <c r="G1" s="5">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="16"/>
-      <c r="B2" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="13">
-        <v>6962.9999999999991</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="17">
+      <c r="B9" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="19"/>
+      <c r="E9" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="19">
-        <v>9082.1999999999989</v>
-      </c>
-      <c r="G3" s="20">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="21"/>
-      <c r="B4" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="23">
-        <v>5004</v>
-      </c>
-      <c r="G4" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="25"/>
-      <c r="B5" s="26" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="F5" s="27">
-        <v>8964.15</v>
-      </c>
-      <c r="G5" s="28">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="15">
-        <v>3</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="11">
-        <v>11215.979999999998</v>
-      </c>
-      <c r="G6" s="5">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="29"/>
-      <c r="B7" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" s="31">
-        <v>4649.4599999999991</v>
-      </c>
-      <c r="G7" s="32">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="16"/>
-      <c r="B8" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" s="13">
-        <v>1850.04</v>
-      </c>
-      <c r="G8" s="14">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2">
-        <v>4</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="7">
-        <v>17547.560000000001</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="15">
-        <v>5</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" s="11">
-        <v>8593.130000000001</v>
-      </c>
-      <c r="G10" s="5">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="16"/>
-      <c r="B11" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="13">
-        <v>8484.9500000000007</v>
-      </c>
-      <c r="G11" s="14">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>6</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F12" s="7">
-        <v>17819.179999999997</v>
-      </c>
-      <c r="G12" s="1">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
-        <v>7</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="F13" s="9">
-        <v>17754.54</v>
-      </c>
-      <c r="G13" s="4">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2">
-        <v>8</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="7">
-        <v>14386.36</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3">
-        <v>9</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="F15" s="9">
-        <v>10834.199999999999</v>
-      </c>
-      <c r="G15" s="4">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2">
-        <v>10</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" s="7">
-        <v>17508.819999999992</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3">
-        <v>11</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="F17" s="9">
-        <v>17310.52</v>
-      </c>
-      <c r="G17" s="4">
+      <c r="G9" s="6">
+        <v>17503.2</v>
+      </c>
+      <c r="H9" s="4">
         <v>0.41666666666666669</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="A10:A11"/>
+  <mergeCells count="2">
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A2:A3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FEB92DC-B1BC-4418-A385-ABE73C192A68}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F840CD98-5A6E-42C4-820D-ABD0F42B2E2D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="17,08,26" sheetId="101" r:id="rId1"/>
+    <sheet name="18,08,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,12 +31,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="4">
   <si>
     <t>КИ</t>
-  </si>
-  <si>
-    <t>НВ</t>
   </si>
   <si>
     <t>ЛП</t>
@@ -45,41 +42,14 @@
     <t>Сочи</t>
   </si>
   <si>
-    <t>Симферополь</t>
-  </si>
-  <si>
-    <t>КСК</t>
-  </si>
-  <si>
-    <t>ЗПФ</t>
-  </si>
-  <si>
-    <t>Донецк</t>
-  </si>
-  <si>
-    <t>17,08,26</t>
-  </si>
-  <si>
-    <t>Бердянск</t>
-  </si>
-  <si>
-    <t>Мелитополь</t>
-  </si>
-  <si>
-    <t>Луганск</t>
-  </si>
-  <si>
-    <t>дозаказ</t>
-  </si>
-  <si>
-    <t>19,08,26</t>
+    <t>20,08,26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -91,14 +61,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
   </fonts>
   <fills count="4">
@@ -121,7 +83,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -174,182 +136,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -369,101 +160,11 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -847,241 +548,129 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="19.5703125" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" customWidth="1"/>
-    <col min="5" max="5" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="8.5703125" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2">
         <v>1</v>
       </c>
-      <c r="B1" s="32" t="s">
+      <c r="B1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="8">
+        <v>18255.400000000001</v>
+      </c>
+      <c r="G1" s="1">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="6">
+        <v>18039.280000000002</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>3</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="8">
+        <v>18018</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
         <v>4</v>
       </c>
-      <c r="C1" s="33" t="s">
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="33" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" s="33" t="s">
+      <c r="D4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="6">
+        <v>17810.400000000001</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
         <v>5</v>
       </c>
-      <c r="G1" s="33">
-        <v>1905</v>
-      </c>
-      <c r="H1" s="34">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="16">
+      <c r="B5" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="26" t="s">
+      <c r="C5" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="37" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="26" t="s">
+      <c r="D5" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="26">
-        <v>1718.64</v>
-      </c>
-      <c r="H2" s="10">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="17"/>
-      <c r="B3" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="28">
-        <v>2115</v>
-      </c>
-      <c r="H3" s="29">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="30">
-        <v>3</v>
-      </c>
-      <c r="B4" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="36">
-        <v>3215.04</v>
-      </c>
-      <c r="H4" s="7">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" s="23">
-        <v>1264.08</v>
-      </c>
-      <c r="H5" s="1">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
-        <v>5</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="19"/>
-      <c r="E6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G6" s="6">
-        <v>14736.039999999999</v>
-      </c>
-      <c r="H6" s="4">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="14">
-        <v>6</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D7" s="20"/>
-      <c r="E7" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="G7" s="9">
-        <v>1159.2</v>
-      </c>
-      <c r="H7" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15"/>
-      <c r="B8" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="21"/>
-      <c r="E8" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="G8" s="12">
-        <v>11289.920000000002</v>
-      </c>
-      <c r="H8" s="13">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
-        <v>7</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="19"/>
-      <c r="E9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G9" s="6">
-        <v>17503.2</v>
-      </c>
-      <c r="H9" s="4">
-        <v>0.41666666666666669</v>
+      <c r="F5" s="8">
+        <v>18144.8</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.58333333333333337</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A2:A3"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -1,28 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F840CD98-5A6E-42C4-820D-ABD0F42B2E2D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01873897-8A24-430A-BCF9-F6483E738F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="18,08,26" sheetId="101" r:id="rId1"/>
+    <sheet name="19,08,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
@@ -31,18 +25,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="9">
   <si>
     <t>КИ</t>
   </si>
   <si>
-    <t>ЛП</t>
-  </si>
-  <si>
-    <t>Сочи</t>
-  </si>
-  <si>
-    <t>20,08,26</t>
+    <t>Симферополь</t>
+  </si>
+  <si>
+    <t>21,08,26</t>
+  </si>
+  <si>
+    <t>КСК</t>
+  </si>
+  <si>
+    <t>Донецк</t>
+  </si>
+  <si>
+    <t>ЗПФ</t>
+  </si>
+  <si>
+    <t>НВ</t>
+  </si>
+  <si>
+    <t>22,08,26</t>
+  </si>
+  <si>
+    <t>Луганск</t>
   </si>
 </sst>
 </file>
@@ -548,126 +557,172 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="8.5703125" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" customWidth="1"/>
+    <col min="2" max="2" width="26.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2">
+      <c r="A1" s="3">
         <v>1</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="8">
-        <v>18255.400000000001</v>
-      </c>
-      <c r="G1" s="1">
-        <v>0.41666666666666669</v>
+      <c r="F1" s="6">
+        <v>17506.84</v>
+      </c>
+      <c r="G1" s="4">
+        <v>0.375</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+      <c r="A2" s="2">
         <v>2</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="6">
-        <v>18039.280000000002</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0.45833333333333331</v>
+      <c r="F2" s="8">
+        <v>17492.02</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
+      <c r="A3" s="3">
         <v>3</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="8">
-        <v>18018</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0.5</v>
+      <c r="E3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="6">
+        <v>11180.84</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+      <c r="A4" s="2">
         <v>4</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="6" t="s">
+      <c r="B4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="6">
-        <v>17810.400000000001</v>
-      </c>
-      <c r="G4" s="4">
-        <v>0.54166666666666663</v>
+      <c r="F4" s="8">
+        <v>17234.2</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.375</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2">
+      <c r="A5" s="3">
         <v>5</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="8" t="s">
+      <c r="B5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="8">
-        <v>18144.8</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0.58333333333333337</v>
+      <c r="F5" s="6">
+        <v>17498</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>6</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="8">
+        <v>17760.07</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
+        <v>7</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="6">
+        <v>17830.800000000003</v>
+      </c>
+      <c r="G7" s="4">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -1,22 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\графики\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01873897-8A24-430A-BCF9-F6483E738F45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{532B4E2C-F0AE-4E5D-BBD1-2AECE28A7707}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="19,08,26" sheetId="101" r:id="rId1"/>
+    <sheet name="20,08,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
@@ -25,15 +31,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="11">
   <si>
     <t>КИ</t>
   </si>
   <si>
     <t>Симферополь</t>
-  </si>
-  <si>
-    <t>21,08,26</t>
   </si>
   <si>
     <t>КСК</t>
@@ -52,6 +55,15 @@
   </si>
   <si>
     <t>Луганск</t>
+  </si>
+  <si>
+    <t>ЛП</t>
+  </si>
+  <si>
+    <t>23,08,26</t>
+  </si>
+  <si>
+    <t>Сочи</t>
   </si>
 </sst>
 </file>
@@ -92,7 +104,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -145,11 +157,130 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,22 +288,70 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -557,175 +736,282 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="26.5703125" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="1" max="1" width="6.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3">
+      <c r="A1" s="2">
         <v>1</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="4">
+        <v>14094.68</v>
+      </c>
+      <c r="G1" s="1">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="5">
+        <v>2</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="7">
+        <v>1388.7</v>
+      </c>
+      <c r="G2" s="8">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="9"/>
+      <c r="B3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="11">
+        <v>3003</v>
+      </c>
+      <c r="G3" s="12">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="9"/>
+      <c r="B4" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="11">
+        <v>13139.839999999998</v>
+      </c>
+      <c r="G4" s="12">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="9"/>
+      <c r="B5" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="11">
+        <v>2633.25</v>
+      </c>
+      <c r="G5" s="12">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="13"/>
+      <c r="B6" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="15">
+        <v>2496</v>
+      </c>
+      <c r="G6" s="16">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="17">
+        <v>3</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F7" s="19">
+        <v>15614.080000000002</v>
+      </c>
+      <c r="G7" s="20">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="21"/>
+      <c r="B8" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="F8" s="23">
+        <v>2077.64</v>
+      </c>
+      <c r="G8" s="24">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="5">
+        <v>4</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="7">
+        <v>933.12</v>
+      </c>
+      <c r="G9" s="8">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="9"/>
+      <c r="B10" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="11">
+        <v>9104.880000000001</v>
+      </c>
+      <c r="G10" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13"/>
+      <c r="B11" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="15">
+        <v>8075.0400000000009</v>
+      </c>
+      <c r="G11" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>5</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="6">
-        <v>17506.84</v>
-      </c>
-      <c r="G1" s="4">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2">
-        <v>2</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="8" t="s">
+      <c r="C12" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="8">
-        <v>17492.02</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
-        <v>3</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="6" t="s">
+      <c r="D12" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="6">
-        <v>11180.84</v>
-      </c>
-      <c r="G3" s="4">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2">
-        <v>4</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="8">
-        <v>17234.2</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
-        <v>5</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="F5" s="6">
-        <v>17498</v>
-      </c>
-      <c r="G5" s="4">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2">
-        <v>6</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" s="8">
-        <v>17760.07</v>
-      </c>
-      <c r="G6" s="1">
+      <c r="F12" s="4">
+        <v>17828.04</v>
+      </c>
+      <c r="G12" s="1">
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
-        <v>7</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" s="6">
-        <v>17830.800000000003</v>
-      </c>
-      <c r="G7" s="4">
-        <v>0.5</v>
-      </c>
-    </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A11"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{532B4E2C-F0AE-4E5D-BBD1-2AECE28A7707}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D80B9D6-901B-4F27-A3C2-7CF1238D2B58}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="20,08,26" sheetId="101" r:id="rId1"/>
+    <sheet name="21,08,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="13">
   <si>
     <t>КИ</t>
   </si>
@@ -51,19 +51,25 @@
     <t>НВ</t>
   </si>
   <si>
-    <t>22,08,26</t>
-  </si>
-  <si>
     <t>Луганск</t>
   </si>
   <si>
     <t>ЛП</t>
   </si>
   <si>
-    <t>23,08,26</t>
+    <t>Сочи</t>
   </si>
   <si>
-    <t>Сочи</t>
+    <t>24,08,26</t>
+  </si>
+  <si>
+    <t>Бердянск</t>
+  </si>
+  <si>
+    <t>Мелитополь</t>
+  </si>
+  <si>
+    <t>25,08,26</t>
   </si>
 </sst>
 </file>
@@ -280,7 +286,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -294,9 +300,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -306,21 +309,6 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -330,9 +318,6 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -342,9 +327,6 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -352,6 +334,42 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -736,281 +754,509 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.85546875" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2">
+      <c r="A1" s="21">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="23">
+        <v>17563.52</v>
+      </c>
+      <c r="G1" s="24">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="19">
+        <v>2</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="12">
+        <v>11514.16</v>
+      </c>
+      <c r="G2" s="13">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="25"/>
+      <c r="B3" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="27" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="27">
+        <v>2624.5599999999995</v>
+      </c>
+      <c r="G3" s="28">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="20"/>
+      <c r="B4" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="15">
+        <v>3601.7400000000002</v>
+      </c>
+      <c r="G4" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="21">
+        <v>3</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D5" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="23">
+        <v>14427.119999999999</v>
+      </c>
+      <c r="G5" s="24">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="19">
+        <v>4</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="12">
+        <v>10934.48</v>
+      </c>
+      <c r="G6" s="13">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="20"/>
+      <c r="B7" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="15">
+        <v>6103.3</v>
+      </c>
+      <c r="G7" s="16">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="21">
+        <v>5</v>
+      </c>
+      <c r="B8" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="C8" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="23">
+        <v>17356.240000000002</v>
+      </c>
+      <c r="G8" s="24">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="19">
+        <v>6</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="12">
+        <v>1678.8</v>
+      </c>
+      <c r="G9" s="13">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="25"/>
+      <c r="B10" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="27">
+        <v>6306</v>
+      </c>
+      <c r="G10" s="28">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="25"/>
+      <c r="B11" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="27">
+        <v>1612.3799999999999</v>
+      </c>
+      <c r="G11" s="28">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="20"/>
+      <c r="B12" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="15">
+        <v>8033.42</v>
+      </c>
+      <c r="G12" s="16">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="21">
+        <v>7</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="23">
+        <v>5004</v>
+      </c>
+      <c r="G13" s="24">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A14" s="19">
+        <v>8</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="12">
+        <v>8996.880000000001</v>
+      </c>
+      <c r="G14" s="13">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="20"/>
+      <c r="B15" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="15">
+        <v>5006.3999999999996</v>
+      </c>
+      <c r="G15" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="21">
+        <v>9</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="4">
-        <v>14094.68</v>
-      </c>
-      <c r="G1" s="1">
+      <c r="F16" s="23">
+        <v>17533.699999999997</v>
+      </c>
+      <c r="G16" s="24">
         <v>0.375</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="5">
-        <v>2</v>
-      </c>
-      <c r="B2" s="6" t="s">
+    <row r="17" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
         <v>10</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="7" t="s">
+      <c r="B17" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="7">
-        <v>1388.7</v>
-      </c>
-      <c r="G2" s="8">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="9"/>
-      <c r="B3" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="11" t="s">
+      <c r="C17" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="4">
+        <v>18040.5</v>
+      </c>
+      <c r="G17" s="1">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="21">
+        <v>11</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="23">
+        <v>17121.98</v>
+      </c>
+      <c r="G18" s="24">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A19" s="19">
+        <v>12</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" s="12">
+        <v>6655.2000000000007</v>
+      </c>
+      <c r="G19" s="13">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="20"/>
+      <c r="B20" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="15">
+        <v>5391.2</v>
+      </c>
+      <c r="G20" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A21" s="17">
+        <v>13</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="11">
-        <v>3003</v>
-      </c>
-      <c r="G3" s="12">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="9"/>
-      <c r="B4" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="11" t="s">
+      <c r="C21" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="6">
+        <v>7875</v>
+      </c>
+      <c r="G21" s="7">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="18"/>
+      <c r="B22" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="11">
-        <v>13139.839999999998</v>
-      </c>
-      <c r="G4" s="12">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="9"/>
-      <c r="B5" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="11">
-        <v>2633.25</v>
-      </c>
-      <c r="G5" s="12">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="13"/>
-      <c r="B6" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="15">
-        <v>2496</v>
-      </c>
-      <c r="G6" s="16">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="17">
-        <v>3</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>2</v>
-      </c>
-      <c r="F7" s="19">
-        <v>15614.080000000002</v>
-      </c>
-      <c r="G7" s="20">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="21"/>
-      <c r="B8" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="F8" s="23">
-        <v>2077.64</v>
-      </c>
-      <c r="G8" s="24">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="5">
+      <c r="C22" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="7">
-        <v>933.12</v>
-      </c>
-      <c r="G9" s="8">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="9"/>
-      <c r="B10" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="11">
-        <v>9104.880000000001</v>
-      </c>
-      <c r="G10" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" s="15">
-        <v>8075.0400000000009</v>
-      </c>
-      <c r="G11" s="16">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2">
-        <v>5</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" s="4">
-        <v>17828.04</v>
-      </c>
-      <c r="G12" s="1">
+      <c r="D22" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="9">
+        <v>5542.4</v>
+      </c>
+      <c r="G22" s="10">
         <v>0.45833333333333331</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A2:A6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A9:A11"/>
+  <mergeCells count="6">
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A6:A7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D80B9D6-901B-4F27-A3C2-7CF1238D2B58}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CB29911-BB44-4FDD-A64F-3326B20C32C3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="21,08,26" sheetId="101" r:id="rId1"/>
+    <sheet name="24,08,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,27 +31,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="4">
   <si>
     <t>КИ</t>
-  </si>
-  <si>
-    <t>Симферополь</t>
-  </si>
-  <si>
-    <t>КСК</t>
-  </si>
-  <si>
-    <t>Донецк</t>
-  </si>
-  <si>
-    <t>ЗПФ</t>
-  </si>
-  <si>
-    <t>НВ</t>
-  </si>
-  <si>
-    <t>Луганск</t>
   </si>
   <si>
     <t>ЛП</t>
@@ -60,16 +42,7 @@
     <t>Сочи</t>
   </si>
   <si>
-    <t>24,08,26</t>
-  </si>
-  <si>
-    <t>Бердянск</t>
-  </si>
-  <si>
-    <t>Мелитополь</t>
-  </si>
-  <si>
-    <t>25,08,26</t>
+    <t>26,08,26</t>
   </si>
 </sst>
 </file>
@@ -110,7 +83,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -208,43 +181,6 @@
     </border>
     <border>
       <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="medium">
@@ -286,38 +222,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -327,25 +233,13 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -360,16 +254,10 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -754,509 +642,82 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="21">
+    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="11">
         <v>1</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="23" t="s">
+      <c r="F1" s="2">
+        <v>14211.409999999998</v>
+      </c>
+      <c r="G1" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="12"/>
+      <c r="B2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="23" t="s">
+      <c r="D2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="5">
+        <v>3487.7999999999997</v>
+      </c>
+      <c r="G2" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="7">
         <v>2</v>
       </c>
-      <c r="F1" s="23">
-        <v>17563.52</v>
-      </c>
-      <c r="G1" s="24">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="19">
+      <c r="B3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="C3" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="12">
-        <v>11514.16</v>
-      </c>
-      <c r="G2" s="13">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="25"/>
-      <c r="B3" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="27">
-        <v>2624.5599999999995</v>
-      </c>
-      <c r="G3" s="28">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="20"/>
-      <c r="B4" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="15">
-        <v>3601.7400000000002</v>
-      </c>
-      <c r="G4" s="16">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="21">
-        <v>3</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="F5" s="23">
-        <v>14427.119999999999</v>
-      </c>
-      <c r="G5" s="24">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="19">
-        <v>4</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="12">
-        <v>10934.48</v>
-      </c>
-      <c r="G6" s="13">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="20"/>
-      <c r="B7" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" s="15">
-        <v>6103.3</v>
-      </c>
-      <c r="G7" s="16">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="21">
-        <v>5</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" s="23">
-        <v>17356.240000000002</v>
-      </c>
-      <c r="G8" s="24">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="19">
-        <v>6</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="12">
-        <v>1678.8</v>
-      </c>
-      <c r="G9" s="13">
+      <c r="F3" s="9">
+        <v>17503.2</v>
+      </c>
+      <c r="G3" s="10">
         <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="25"/>
-      <c r="B10" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="27">
-        <v>6306</v>
-      </c>
-      <c r="G10" s="28">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="25"/>
-      <c r="B11" s="26" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" s="27">
-        <v>1612.3799999999999</v>
-      </c>
-      <c r="G11" s="28">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="20"/>
-      <c r="B12" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" s="15">
-        <v>8033.42</v>
-      </c>
-      <c r="G12" s="16">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="21">
-        <v>7</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" s="23">
-        <v>5004</v>
-      </c>
-      <c r="G13" s="24">
-        <v>0.58333333333333337</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A14" s="19">
-        <v>8</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="12">
-        <v>8996.880000000001</v>
-      </c>
-      <c r="G14" s="13">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="20"/>
-      <c r="B15" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" s="15">
-        <v>5006.3999999999996</v>
-      </c>
-      <c r="G15" s="16">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="21">
-        <v>9</v>
-      </c>
-      <c r="B16" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D16" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="F16" s="23">
-        <v>17533.699999999997</v>
-      </c>
-      <c r="G16" s="24">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2">
-        <v>10</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" s="4">
-        <v>18040.5</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="21">
-        <v>11</v>
-      </c>
-      <c r="B18" s="22" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D18" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" s="23">
-        <v>17121.98</v>
-      </c>
-      <c r="G18" s="24">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A19" s="19">
-        <v>12</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" s="12">
-        <v>6655.2000000000007</v>
-      </c>
-      <c r="G19" s="13">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="20"/>
-      <c r="B20" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" s="15">
-        <v>5391.2</v>
-      </c>
-      <c r="G20" s="16">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A21" s="17">
-        <v>13</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" s="6">
-        <v>7875</v>
-      </c>
-      <c r="G21" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="18"/>
-      <c r="B22" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" s="9">
-        <v>5542.4</v>
-      </c>
-      <c r="G22" s="10">
-        <v>0.45833333333333331</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A9:A12"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="A6:A7"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CB29911-BB44-4FDD-A64F-3326B20C32C3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF84429-6F7F-4D3F-822B-11709CC1436E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="24,08,26" sheetId="101" r:id="rId1"/>
+    <sheet name="25,08,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="4">
   <si>
     <t>КИ</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Сочи</t>
   </si>
   <si>
-    <t>26,08,26</t>
+    <t>27,08,26</t>
   </si>
 </sst>
 </file>
@@ -83,7 +83,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -136,112 +136,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -254,10 +154,16 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -642,83 +548,105 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="11">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="2">
-        <v>14211.409999999998</v>
-      </c>
-      <c r="G1" s="3">
-        <v>0.5</v>
+      <c r="F1" s="7">
+        <v>18353.179999999997</v>
+      </c>
+      <c r="G1" s="8">
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12"/>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="1">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="5">
-        <v>3487.7999999999997</v>
-      </c>
-      <c r="G2" s="6">
-        <v>0.5</v>
+      <c r="F2" s="3">
+        <v>18163.59</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0.45833333333333331</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7">
+      <c r="A3" s="5">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="C3" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="7">
+        <v>17810.400000000001</v>
+      </c>
+      <c r="G3" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="9">
-        <v>17503.2</v>
-      </c>
-      <c r="G3" s="10">
+      <c r="F4" s="3">
+        <v>18212.04</v>
+      </c>
+      <c r="G4" s="4">
         <v>0.54166666666666663</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:A2"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF84429-6F7F-4D3F-822B-11709CC1436E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3D4E67D-577A-4916-BF87-815AC1D4F779}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="25,08,26" sheetId="101" r:id="rId1"/>
+    <sheet name="26,08,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="12">
   <si>
     <t>КИ</t>
   </si>
@@ -42,7 +42,31 @@
     <t>Сочи</t>
   </si>
   <si>
-    <t>27,08,26</t>
+    <t>Симферополь</t>
+  </si>
+  <si>
+    <t>28,08,26</t>
+  </si>
+  <si>
+    <t>КСК</t>
+  </si>
+  <si>
+    <t>ЗПФ</t>
+  </si>
+  <si>
+    <t>29,08,26</t>
+  </si>
+  <si>
+    <t>Мелитополь</t>
+  </si>
+  <si>
+    <t>НВ</t>
+  </si>
+  <si>
+    <t>Бердянск</t>
+  </si>
+  <si>
+    <t>Донецк</t>
   </si>
 </sst>
 </file>
@@ -83,7 +107,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -136,11 +160,130 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -164,6 +307,66 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -548,10 +751,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="13.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -559,22 +763,22 @@
         <v>1</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F1" s="7">
-        <v>18353.179999999997</v>
+        <v>17539.759999999998</v>
       </c>
       <c r="G1" s="8">
-        <v>0.41666666666666669</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -582,71 +786,270 @@
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="3">
+        <v>17506.2</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="9">
+        <v>3</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="C3" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="11">
+        <v>1707.42</v>
+      </c>
+      <c r="G3" s="12">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="13"/>
+      <c r="B4" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="15">
+        <v>2503.7999999999997</v>
+      </c>
+      <c r="G4" s="16">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="13"/>
+      <c r="B5" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="15">
+        <v>4727.74</v>
+      </c>
+      <c r="G5" s="16">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="13"/>
+      <c r="B6" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="15">
+        <v>1497.6</v>
+      </c>
+      <c r="G6" s="16">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="13"/>
+      <c r="B7" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="15">
+        <v>6734.3000000000011</v>
+      </c>
+      <c r="G7" s="16">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="17"/>
+      <c r="B8" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="19">
+        <v>2496</v>
+      </c>
+      <c r="G8" s="20">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>4</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="3">
-        <v>18163.59</v>
-      </c>
-      <c r="G2" s="4">
+      <c r="C9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="3">
+        <v>17018.919999999998</v>
+      </c>
+      <c r="G9" s="4">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <v>5</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="7">
+        <v>17937.810000000001</v>
+      </c>
+      <c r="G10" s="8">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="21">
+        <v>6</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="23">
+        <v>11245.769999999999</v>
+      </c>
+      <c r="G11" s="24">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="25"/>
+      <c r="B12" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="27">
+        <v>6731.05</v>
+      </c>
+      <c r="G12" s="28">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5">
+        <v>7</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="7">
+        <v>18046.53</v>
+      </c>
+      <c r="G13" s="8">
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
-        <v>3</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="7">
-        <v>17810.400000000001</v>
-      </c>
-      <c r="G3" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>4</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="3">
-        <v>18212.04</v>
-      </c>
-      <c r="G4" s="4">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="A11:A12"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3D4E67D-577A-4916-BF87-815AC1D4F779}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD3ACBC2-D48E-4473-B551-483236517B36}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="26,08,26" sheetId="101" r:id="rId1"/>
+    <sheet name="27,08,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="10">
   <si>
     <t>КИ</t>
   </si>
@@ -45,28 +45,22 @@
     <t>Симферополь</t>
   </si>
   <si>
-    <t>28,08,26</t>
-  </si>
-  <si>
     <t>КСК</t>
-  </si>
-  <si>
-    <t>ЗПФ</t>
-  </si>
-  <si>
-    <t>29,08,26</t>
-  </si>
-  <si>
-    <t>Мелитополь</t>
   </si>
   <si>
     <t>НВ</t>
   </si>
   <si>
-    <t>Бердянск</t>
+    <t>Донецк</t>
   </si>
   <si>
-    <t>Донецк</t>
+    <t>30,08,26</t>
+  </si>
+  <si>
+    <t>Николаенко</t>
+  </si>
+  <si>
+    <t>Луганск</t>
   </si>
 </sst>
 </file>
@@ -283,7 +277,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -297,21 +291,6 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -321,9 +300,6 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -333,9 +309,6 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -345,9 +318,6 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -357,9 +327,6 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -367,6 +334,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -751,304 +733,215 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="19.5703125" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5">
+    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="20">
         <v>1</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="7">
-        <v>17539.759999999998</v>
-      </c>
-      <c r="G1" s="8">
+      <c r="F1" s="15">
+        <v>17216.78</v>
+      </c>
+      <c r="G1" s="16">
         <v>0.375</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>2</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="A2" s="21"/>
+      <c r="B2" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="3">
-        <v>17506.2</v>
-      </c>
-      <c r="G2" s="4">
-        <v>0.41666666666666669</v>
+      <c r="F2" s="18">
+        <v>1880.24</v>
+      </c>
+      <c r="G2" s="19">
+        <v>0.375</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="9">
-        <v>3</v>
-      </c>
-      <c r="B3" s="10" t="s">
+      <c r="A3" s="22">
         <v>2</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="11">
-        <v>1707.42</v>
-      </c>
-      <c r="G3" s="12">
-        <v>0.45833333333333331</v>
+      <c r="D3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="6">
+        <v>3253.0800000000004</v>
+      </c>
+      <c r="G3" s="7">
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="13"/>
-      <c r="B4" s="14" t="s">
+      <c r="A4" s="23"/>
+      <c r="B4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="9">
+        <v>1537.5</v>
+      </c>
+      <c r="G4" s="10">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="24"/>
+      <c r="B5" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C5" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="15" t="s">
+      <c r="D5" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="15">
-        <v>2503.7999999999997</v>
-      </c>
-      <c r="G4" s="16">
-        <v>0.45833333333333331</v>
+      <c r="F5" s="12">
+        <v>10081.98</v>
+      </c>
+      <c r="G5" s="13">
+        <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="13"/>
-      <c r="B5" s="14" t="s">
+    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>3</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="15" t="s">
+      <c r="D6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="15">
-        <v>4727.74</v>
-      </c>
-      <c r="G5" s="16">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="13"/>
-      <c r="B6" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="15">
-        <v>1497.6</v>
-      </c>
-      <c r="G6" s="16">
-        <v>0.45833333333333331</v>
+      <c r="F6" s="3">
+        <v>5004</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="15" t="s">
+      <c r="A7" s="22">
+        <v>4</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D7" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="15">
-        <v>6734.3000000000011</v>
-      </c>
-      <c r="G7" s="16">
+      <c r="D7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="6">
+        <v>936.96</v>
+      </c>
+      <c r="G7" s="7">
         <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="17"/>
-      <c r="B8" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="C8" s="19" t="s">
+    <row r="8" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="23"/>
+      <c r="B8" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="19">
-        <v>2496</v>
-      </c>
-      <c r="G8" s="20">
+      <c r="D8" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="9">
+        <v>6315.9200000000019</v>
+      </c>
+      <c r="G8" s="10">
         <v>0.45833333333333331</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>4</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="3" t="s">
+      <c r="A9" s="24"/>
+      <c r="B9" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="3">
-        <v>17018.919999999998</v>
-      </c>
-      <c r="G9" s="4">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5">
-        <v>5</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="7">
-        <v>17937.810000000001</v>
-      </c>
-      <c r="G10" s="8">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="21">
-        <v>6</v>
-      </c>
-      <c r="B11" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="23">
-        <v>11245.769999999999</v>
-      </c>
-      <c r="G11" s="24">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="25"/>
-      <c r="B12" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="27">
-        <v>6731.05</v>
-      </c>
-      <c r="G12" s="28">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5">
-        <v>7</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="7">
-        <v>18046.53</v>
-      </c>
-      <c r="G13" s="8">
+      <c r="F9" s="12">
+        <v>10510.679999999997</v>
+      </c>
+      <c r="G9" s="13">
         <v>0.45833333333333331</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="A11:A12"/>
+  <mergeCells count="3">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A7:A9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -1,28 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD3ACBC2-D48E-4473-B551-483236517B36}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C76DD2-459E-49C3-97EE-E222EBC17255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="27,08,26" sheetId="101" r:id="rId1"/>
+    <sheet name="28,08,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
@@ -31,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="18">
   <si>
     <t>КИ</t>
   </si>
@@ -57,10 +51,34 @@
     <t>30,08,26</t>
   </si>
   <si>
-    <t>Николаенко</t>
-  </si>
-  <si>
     <t>Луганск</t>
+  </si>
+  <si>
+    <t>ЗПФ</t>
+  </si>
+  <si>
+    <t>31,08,26</t>
+  </si>
+  <si>
+    <t>Бердянск</t>
+  </si>
+  <si>
+    <t>Мелитополь</t>
+  </si>
+  <si>
+    <t>01,09,26</t>
+  </si>
+  <si>
+    <t>Павленко</t>
+  </si>
+  <si>
+    <t>ОПТ</t>
+  </si>
+  <si>
+    <t>31 паллет</t>
+  </si>
+  <si>
+    <t>30 паллет</t>
   </si>
 </sst>
 </file>
@@ -101,7 +119,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -273,82 +291,352 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -733,215 +1021,630 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="19.42578125" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" customWidth="1"/>
+    <col min="8" max="8" width="0" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="20">
+    <row r="1" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1">
         <v>1</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="15" t="s">
+      <c r="C1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="15">
-        <v>17216.78</v>
-      </c>
-      <c r="G1" s="16">
+      <c r="F1" s="2">
+        <v>17015.000000000004</v>
+      </c>
+      <c r="G1" s="3">
         <v>0.375</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="21"/>
-      <c r="B2" s="17" t="s">
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+    </row>
+    <row r="2" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="14">
+        <v>2</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="15">
+        <v>17578.12</v>
+      </c>
+      <c r="G2" s="16">
+        <v>0.375</v>
+      </c>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+    </row>
+    <row r="3" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>3</v>
+      </c>
+      <c r="B3" s="38" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="24">
+        <v>17583.800000000003</v>
+      </c>
+      <c r="G3" s="39">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+    </row>
+    <row r="4" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="14">
+        <v>4</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="15">
+        <v>17377.23</v>
+      </c>
+      <c r="G4" s="16">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="H4" s="28"/>
+      <c r="I4" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>5</v>
+      </c>
+      <c r="B5" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="18" t="s">
+      <c r="C5" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2">
+        <v>17213.829999999998</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="H5" s="28"/>
+      <c r="I5" s="31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="45">
+        <v>6</v>
+      </c>
+      <c r="B6" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="6">
+        <v>8707.6400000000012</v>
+      </c>
+      <c r="G6" s="7">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+    </row>
+    <row r="7" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="46"/>
+      <c r="B7" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="8">
+        <v>9237.6900000000023</v>
+      </c>
+      <c r="G7" s="9">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+    </row>
+    <row r="8" spans="1:9" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="51">
         <v>7</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="B8" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="18">
-        <v>1880.24</v>
-      </c>
-      <c r="G2" s="19">
+      <c r="F8" s="10">
+        <v>2653.8800000000006</v>
+      </c>
+      <c r="G8" s="11">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="20"/>
+    </row>
+    <row r="9" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="53"/>
+      <c r="B9" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="12">
+        <v>8545.6</v>
+      </c>
+      <c r="G9" s="13">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="20"/>
+    </row>
+    <row r="10" spans="1:9" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="45">
+        <v>8</v>
+      </c>
+      <c r="B10" s="42" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="4">
+        <v>8122.92</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="H10" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="20"/>
+    </row>
+    <row r="11" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="46"/>
+      <c r="B11" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="8">
+        <v>4922.3999999999996</v>
+      </c>
+      <c r="G11" s="9">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+    </row>
+    <row r="12" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>9</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F12" s="2">
+        <v>13062.08</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+    </row>
+    <row r="13" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="14">
+        <v>10</v>
+      </c>
+      <c r="B13" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13" s="15">
+        <v>15789.479999999998</v>
+      </c>
+      <c r="G13" s="16">
         <v>0.375</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="22">
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+    </row>
+    <row r="14" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>11</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="2">
+        <v>19337.64</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0.375</v>
+      </c>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+    </row>
+    <row r="15" spans="1:9" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A15" s="45">
+        <v>12</v>
+      </c>
+      <c r="B15" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="C15" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="4">
+        <v>8170.920000000001</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="H15" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="20"/>
+    </row>
+    <row r="16" spans="1:9" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A16" s="50"/>
+      <c r="B16" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="6">
+        <v>1564.1</v>
+      </c>
+      <c r="G16" s="7">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="H16" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="20"/>
+    </row>
+    <row r="17" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="46"/>
+      <c r="B17" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="6" t="s">
+      <c r="C17" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="D17" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="6">
-        <v>3253.0800000000004</v>
-      </c>
-      <c r="G3" s="7">
+      <c r="F17" s="32">
+        <v>7791.96</v>
+      </c>
+      <c r="G17" s="44">
         <v>0.41666666666666669</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="23"/>
-      <c r="B4" s="8" t="s">
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+    </row>
+    <row r="18" spans="1:9" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A18" s="51">
+        <v>13</v>
+      </c>
+      <c r="B18" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="10">
+        <v>3623.4400000000005</v>
+      </c>
+      <c r="G18" s="11">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="H18" s="19"/>
+      <c r="I18" s="47" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A19" s="52"/>
+      <c r="B19" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" s="17">
+        <v>4839.5399999999981</v>
+      </c>
+      <c r="G19" s="18">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="H19" s="20"/>
+      <c r="I19" s="48"/>
+    </row>
+    <row r="20" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="53"/>
+      <c r="B20" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="12">
+        <v>8110.2</v>
+      </c>
+      <c r="G20" s="13">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="H20" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="49"/>
+    </row>
+    <row r="21" spans="1:9" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A21" s="45">
+        <v>14</v>
+      </c>
+      <c r="B21" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F21" s="6">
+        <v>8835.18</v>
+      </c>
+      <c r="G21" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="H21" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="I21" s="26"/>
+    </row>
+    <row r="22" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="46"/>
+      <c r="B22" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="9" t="s">
+      <c r="C22" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="9">
-        <v>1537.5</v>
-      </c>
-      <c r="G4" s="10">
+      <c r="F22" s="8">
+        <v>8805.5400000000009</v>
+      </c>
+      <c r="G22" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+    </row>
+    <row r="23" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>15</v>
+      </c>
+      <c r="B23" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>8001</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="H23" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="I23" s="20"/>
+    </row>
+    <row r="24" spans="1:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="14">
+        <v>16</v>
+      </c>
+      <c r="B24" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="15">
+        <v>11665.92</v>
+      </c>
+      <c r="G24" s="16">
         <v>0.41666666666666669</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="24"/>
-      <c r="B5" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="12">
-        <v>10081.98</v>
-      </c>
-      <c r="G5" s="13">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>3</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3">
-        <v>5004</v>
-      </c>
-      <c r="G6" s="4">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="22">
-        <v>4</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" s="6">
-        <v>936.96</v>
-      </c>
-      <c r="G7" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="23"/>
-      <c r="B8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" s="9">
-        <v>6315.9200000000019</v>
-      </c>
-      <c r="G8" s="10">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="24"/>
-      <c r="B9" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="12">
-        <v>10510.679999999997</v>
-      </c>
-      <c r="G9" s="13">
-        <v>0.45833333333333331</v>
-      </c>
+      <c r="H24" s="23"/>
+      <c r="I24" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A7:A9"/>
+  <mergeCells count="7">
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A21:A22"/>
+    <mergeCell ref="I18:I20"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A18:A20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{651D0853-621F-4743-8984-81A107B02AF1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C832263-BDD1-4F5A-860B-C50CAD4033AB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="31,08,26" sheetId="101" r:id="rId1"/>
+    <sheet name="01,09,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="4">
   <si>
     <t>КИ</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Сочи</t>
   </si>
   <si>
-    <t>02,09,26</t>
+    <t>03,09,26</t>
   </si>
 </sst>
 </file>
@@ -63,7 +63,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -73,6 +73,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -134,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -147,6 +153,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -530,33 +548,103 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="14.28515625" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1">
+      <c r="A1" s="5">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="2">
-        <v>9803.18</v>
-      </c>
-      <c r="G1" s="3">
+      <c r="F1" s="7">
+        <v>18112.099999999995</v>
+      </c>
+      <c r="G1" s="8">
         <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>2</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2">
+        <v>18033.18</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="7">
+        <v>17604.599999999999</v>
+      </c>
+      <c r="G3" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>18121.16</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0.54166666666666663</v>
       </c>
     </row>
   </sheetData>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -1,28 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C832263-BDD1-4F5A-860B-C50CAD4033AB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67548F22-83E3-4B70-9386-05AB512F446B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="01,09,26" sheetId="101" r:id="rId1"/>
+    <sheet name="02,09,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
@@ -31,18 +25,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="10">
   <si>
     <t>КИ</t>
   </si>
   <si>
-    <t>ЛП</t>
-  </si>
-  <si>
-    <t>Сочи</t>
-  </si>
-  <si>
-    <t>03,09,26</t>
+    <t>Симферополь</t>
+  </si>
+  <si>
+    <t>04,09,26</t>
+  </si>
+  <si>
+    <t>КСК</t>
+  </si>
+  <si>
+    <t>Бердянск</t>
+  </si>
+  <si>
+    <t>ЗПФ</t>
+  </si>
+  <si>
+    <t>НВ</t>
+  </si>
+  <si>
+    <t>Мелитополь</t>
+  </si>
+  <si>
+    <t>05,09,26</t>
+  </si>
+  <si>
+    <t>Луганск</t>
   </si>
 </sst>
 </file>
@@ -83,7 +95,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -136,11 +148,93 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -164,6 +258,30 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -548,11 +666,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="9.140625" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.5703125" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -560,22 +678,22 @@
         <v>1</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>1</v>
-      </c>
       <c r="F1" s="7">
-        <v>18112.099999999995</v>
+        <v>17770.98</v>
       </c>
       <c r="G1" s="8">
-        <v>0.41666666666666669</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -583,71 +701,140 @@
         <v>2</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>1</v>
-      </c>
       <c r="F2" s="2">
-        <v>18033.18</v>
+        <v>17390.300000000003</v>
       </c>
       <c r="G2" s="3">
-        <v>0.45833333333333331</v>
+        <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
+    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="9">
         <v>3</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="7">
-        <v>17604.599999999999</v>
-      </c>
-      <c r="G3" s="8">
-        <v>0.5</v>
+      <c r="E3" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="11">
+        <v>8620.1999999999989</v>
+      </c>
+      <c r="G3" s="12">
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
+      <c r="A4" s="13"/>
+      <c r="B4" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="15">
+        <v>5671.5599999999995</v>
+      </c>
+      <c r="G4" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="B5" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="2">
-        <v>18121.16</v>
-      </c>
-      <c r="G4" s="3">
-        <v>0.54166666666666663</v>
+      <c r="F5" s="2">
+        <v>20167.020000000004</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="9">
+        <v>5</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="11">
+        <v>8943.9599999999991</v>
+      </c>
+      <c r="G6" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13"/>
+      <c r="B7" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="15">
+        <v>8766.5399999999991</v>
+      </c>
+      <c r="G7" s="16">
+        <v>0.41666666666666669</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A6:A7"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -1,22 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\графики\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67548F22-83E3-4B70-9386-05AB512F446B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F469F0EF-60E6-45CC-8F5A-CC396AF7939B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="02,09,26" sheetId="101" r:id="rId1"/>
+    <sheet name="03,09,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="181029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
@@ -25,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="10">
   <si>
     <t>КИ</t>
   </si>
@@ -33,13 +39,7 @@
     <t>Симферополь</t>
   </si>
   <si>
-    <t>04,09,26</t>
-  </si>
-  <si>
     <t>КСК</t>
-  </si>
-  <si>
-    <t>Бердянск</t>
   </si>
   <si>
     <t>ЗПФ</t>
@@ -48,13 +48,19 @@
     <t>НВ</t>
   </si>
   <si>
-    <t>Мелитополь</t>
-  </si>
-  <si>
     <t>05,09,26</t>
   </si>
   <si>
-    <t>Луганск</t>
+    <t>ЛП</t>
+  </si>
+  <si>
+    <t>06,09,26</t>
+  </si>
+  <si>
+    <t>Донецк</t>
+  </si>
+  <si>
+    <t>Сочи</t>
   </si>
 </sst>
 </file>
@@ -95,7 +101,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -230,11 +236,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -248,21 +291,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -272,9 +300,6 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -282,6 +307,48 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -666,174 +733,216 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="22.5703125" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" customWidth="1"/>
+    <col min="1" max="1" width="6.42578125" customWidth="1"/>
+    <col min="2" max="2" width="20.28515625" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5">
+      <c r="A1" s="1">
         <v>1</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2">
+        <v>16049.4</v>
+      </c>
+      <c r="G1" s="3">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="22">
+        <v>2</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="7">
-        <v>17770.98</v>
-      </c>
-      <c r="G1" s="8">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>2</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="2">
-        <v>17390.300000000003</v>
-      </c>
-      <c r="G2" s="3">
-        <v>0.41666666666666669</v>
+      <c r="D2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="6">
+        <v>8637.08</v>
+      </c>
+      <c r="G2" s="7">
+        <v>0.45833333333333331</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="9">
-        <v>3</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="A3" s="23"/>
+      <c r="B3" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="11">
-        <v>8620.1999999999989</v>
-      </c>
-      <c r="G3" s="12">
-        <v>0.41666666666666669</v>
+      <c r="F3" s="12">
+        <v>312</v>
+      </c>
+      <c r="G3" s="13">
+        <v>0.45833333333333331</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13"/>
-      <c r="B4" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="15" t="s">
+    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="23"/>
+      <c r="B4" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="15">
-        <v>5671.5599999999995</v>
-      </c>
-      <c r="G4" s="16">
-        <v>0.41666666666666669</v>
+      <c r="F4" s="12">
+        <v>4296.3200000000006</v>
+      </c>
+      <c r="G4" s="13">
+        <v>0.45833333333333331</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="A5" s="24"/>
+      <c r="B5" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F5" s="2">
-        <v>20167.020000000004</v>
-      </c>
-      <c r="G5" s="3">
-        <v>0.375</v>
+      <c r="D5" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="9">
+        <v>5329.0000000000009</v>
+      </c>
+      <c r="G5" s="10">
+        <v>0.45833333333333331</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="9">
-        <v>5</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="11" t="s">
+      <c r="A6" s="20">
+        <v>3</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D6" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" s="11">
-        <v>8943.9599999999991</v>
-      </c>
-      <c r="G6" s="12">
-        <v>0.41666666666666669</v>
+      <c r="D6" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" s="15">
+        <v>17674.04</v>
+      </c>
+      <c r="G6" s="16">
+        <v>0.375</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="15" t="s">
+      <c r="A7" s="21"/>
+      <c r="B7" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="18">
+        <v>2533.3200000000002</v>
+      </c>
+      <c r="G7" s="19">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="22">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" s="15">
-        <v>8766.5399999999991</v>
-      </c>
-      <c r="G7" s="16">
+      <c r="C8" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="6">
+        <v>772.8</v>
+      </c>
+      <c r="G8" s="7">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="24"/>
+      <c r="B9" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="9">
+        <v>16789.900000000001</v>
+      </c>
+      <c r="G9" s="10">
         <v>0.41666666666666669</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A3:A4"/>
+  <mergeCells count="3">
     <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A8:A9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -1,28 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F469F0EF-60E6-45CC-8F5A-CC396AF7939B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5CC0F97-D7CE-4D58-9FC1-F2FAFF84D9FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="03,09,26" sheetId="101" r:id="rId1"/>
+    <sheet name="04,09,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
@@ -31,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="13">
   <si>
     <t>КИ</t>
   </si>
@@ -48,19 +42,28 @@
     <t>НВ</t>
   </si>
   <si>
-    <t>05,09,26</t>
-  </si>
-  <si>
     <t>ЛП</t>
   </si>
   <si>
-    <t>06,09,26</t>
-  </si>
-  <si>
     <t>Донецк</t>
   </si>
   <si>
     <t>Сочи</t>
+  </si>
+  <si>
+    <t>07,09,26</t>
+  </si>
+  <si>
+    <t>Бердянск</t>
+  </si>
+  <si>
+    <t>Мелитополь</t>
+  </si>
+  <si>
+    <t>Луганск</t>
+  </si>
+  <si>
+    <t>08,09,26</t>
   </si>
 </sst>
 </file>
@@ -277,7 +280,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -291,33 +294,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -342,13 +318,28 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -733,12 +724,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="6.42578125" customWidth="1"/>
-    <col min="2" max="2" width="20.28515625" customWidth="1"/>
-    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="1" max="1" width="7" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -752,197 +743,338 @@
         <v>3</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="2">
-        <v>16049.4</v>
+        <v>16669.04</v>
       </c>
       <c r="G1" s="3">
         <v>0.375</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="22">
+    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="13">
         <v>2</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="15">
+        <v>10739.76</v>
+      </c>
+      <c r="G2" s="16">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>3</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2">
+        <v>17597.66</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="13">
+        <v>4</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="15">
+        <v>17908.080000000002</v>
+      </c>
+      <c r="G4" s="16">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="11">
+        <v>5</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C5" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="6">
+        <v>8730.48</v>
+      </c>
+      <c r="G5" s="7">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="12"/>
+      <c r="B6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="9">
+        <v>7135.9200000000019</v>
+      </c>
+      <c r="G6" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13">
+        <v>6</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="15">
+        <v>8689.0400000000009</v>
+      </c>
+      <c r="G7" s="16">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A8" s="11">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="6">
-        <v>8637.08</v>
-      </c>
-      <c r="G2" s="7">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="23"/>
-      <c r="B3" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="12">
-        <v>312</v>
-      </c>
-      <c r="G3" s="13">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="23"/>
-      <c r="B4" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4" s="12">
-        <v>4296.3200000000006</v>
-      </c>
-      <c r="G4" s="13">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="24"/>
-      <c r="B5" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="9">
-        <v>5329.0000000000009</v>
-      </c>
-      <c r="G5" s="10">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="20">
-        <v>3</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F6" s="15">
-        <v>17674.04</v>
-      </c>
-      <c r="G6" s="16">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="21"/>
-      <c r="B7" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="F7" s="18">
-        <v>2533.3200000000002</v>
-      </c>
-      <c r="G7" s="19">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="22">
-        <v>4</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>4</v>
-      </c>
       <c r="F8" s="6">
-        <v>772.8</v>
+        <v>2026.08</v>
       </c>
       <c r="G8" s="7">
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="24"/>
-      <c r="B9" s="8" t="s">
+    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="17"/>
+      <c r="B9" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="E9" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9" s="19">
+        <v>9787.68</v>
+      </c>
+      <c r="G9" s="20">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12"/>
+      <c r="B10" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="9">
+        <v>1257.5999999999999</v>
+      </c>
+      <c r="G10" s="10">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13">
+        <v>8</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D9" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="9" t="s">
+      <c r="D11" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F11" s="15">
+        <v>17575.240000000002</v>
+      </c>
+      <c r="G11" s="16">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>9</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F12" s="2">
+        <v>17884.45</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="13">
+        <v>10</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="9">
-        <v>16789.900000000001</v>
-      </c>
-      <c r="G9" s="10">
+      <c r="F13" s="15">
+        <v>17311.98</v>
+      </c>
+      <c r="G13" s="16">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>11</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="2">
+        <v>17304.93</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="13">
+        <v>12</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15" s="15">
+        <v>12076.199999999999</v>
+      </c>
+      <c r="G15" s="16">
         <v>0.41666666666666669</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A8:A9"/>
+  <mergeCells count="2">
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A8:A10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -1,22 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\графики\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5CC0F97-D7CE-4D58-9FC1-F2FAFF84D9FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F6191EF-B39B-456C-BD40-0F19AC2EB616}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="04,09,26" sheetId="101" r:id="rId1"/>
+    <sheet name="07,09,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
@@ -25,51 +31,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="4">
   <si>
     <t>КИ</t>
-  </si>
-  <si>
-    <t>Симферополь</t>
-  </si>
-  <si>
-    <t>КСК</t>
-  </si>
-  <si>
-    <t>ЗПФ</t>
-  </si>
-  <si>
-    <t>НВ</t>
   </si>
   <si>
     <t>ЛП</t>
   </si>
   <si>
-    <t>Донецк</t>
-  </si>
-  <si>
     <t>Сочи</t>
   </si>
   <si>
-    <t>07,09,26</t>
-  </si>
-  <si>
-    <t>Бердянск</t>
-  </si>
-  <si>
-    <t>Мелитополь</t>
-  </si>
-  <si>
-    <t>Луганск</t>
-  </si>
-  <si>
-    <t>08,09,26</t>
+    <t>10,09,26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -84,7 +66,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -97,64 +79,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="13">
+  <borders count="7">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -239,61 +170,21 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -303,43 +194,16 @@
     <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -724,357 +588,65 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1">
+    <row r="1" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A1" s="9">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="7">
+        <v>2.87</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="G1" s="2">
+        <v>2937.4599999999996</v>
+      </c>
+      <c r="H1" s="3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="10"/>
+      <c r="B2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="8">
+        <v>14.9</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="2">
-        <v>16669.04</v>
-      </c>
-      <c r="G1" s="3">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13">
-        <v>2</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="15">
-        <v>10739.76</v>
-      </c>
-      <c r="G2" s="16">
+      <c r="F2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="5">
+        <v>15070.84</v>
+      </c>
+      <c r="H2" s="6">
         <v>0.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>3</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="2">
-        <v>17597.66</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
-        <v>4</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="15">
-        <v>17908.080000000002</v>
-      </c>
-      <c r="G4" s="16">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="11">
-        <v>5</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="6">
-        <v>8730.48</v>
-      </c>
-      <c r="G5" s="7">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="B6" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F6" s="9">
-        <v>7135.9200000000019</v>
-      </c>
-      <c r="G6" s="10">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="13">
-        <v>6</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="F7" s="15">
-        <v>8689.0400000000009</v>
-      </c>
-      <c r="G7" s="16">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="11">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" s="6">
-        <v>2026.08</v>
-      </c>
-      <c r="G8" s="7">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="17"/>
-      <c r="B9" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="19">
-        <v>9787.68</v>
-      </c>
-      <c r="G9" s="20">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="12"/>
-      <c r="B10" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="9">
-        <v>1257.5999999999999</v>
-      </c>
-      <c r="G10" s="10">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="13">
-        <v>8</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F11" s="15">
-        <v>17575.240000000002</v>
-      </c>
-      <c r="G11" s="16">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>9</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F12" s="2">
-        <v>17884.45</v>
-      </c>
-      <c r="G12" s="3">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="13">
-        <v>10</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="F13" s="15">
-        <v>17311.98</v>
-      </c>
-      <c r="G13" s="16">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>11</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="2">
-        <v>17304.93</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="13">
-        <v>12</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="F15" s="15">
-        <v>12076.199999999999</v>
-      </c>
-      <c r="G15" s="16">
-        <v>0.41666666666666669</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A8:A10"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F6191EF-B39B-456C-BD40-0F19AC2EB616}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60612D07-8205-43D3-82EB-02EECB850656}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="07,09,26" sheetId="101" r:id="rId1"/>
+    <sheet name="08,09,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="4">
   <si>
     <t>КИ</t>
   </si>
@@ -49,9 +49,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -66,7 +63,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -79,8 +76,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -98,20 +101,7 @@
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -120,27 +110,14 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color auto="1"/>
       </right>
       <top style="medium">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -148,25 +125,14 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color auto="1"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
       <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -174,8 +140,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -183,27 +164,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -588,66 +548,129 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="5" width="13.5703125" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="9">
+    <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="7">
-        <v>2.87</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="2">
-        <v>2937.4599999999996</v>
-      </c>
-      <c r="H1" s="3">
+      <c r="F1" s="3">
+        <v>18206.340000000004</v>
+      </c>
+      <c r="G1" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5">
+        <v>2</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="7">
+        <v>18073.95</v>
+      </c>
+      <c r="G2" s="8">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>3</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3">
+        <v>18103.2</v>
+      </c>
+      <c r="G3" s="4">
         <v>0.5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="10"/>
-      <c r="B2" s="4" t="s">
+    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>4</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="8">
-        <v>14.9</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="D4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="E4" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="5">
-        <v>15070.84</v>
-      </c>
-      <c r="H2" s="6">
-        <v>0.5</v>
+      <c r="F4" s="7">
+        <v>17604.599999999999</v>
+      </c>
+      <c r="G4" s="8">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3">
+        <v>18066.18</v>
+      </c>
+      <c r="G5" s="4">
+        <v>0.58333333333333337</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:A2"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60612D07-8205-43D3-82EB-02EECB850656}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8285FCE-4EC9-4B14-AF83-FAC34B539D50}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="08,09,26" sheetId="101" r:id="rId1"/>
+    <sheet name="09,09,26" sheetId="101" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,18 +31,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="10">
   <si>
     <t>КИ</t>
   </si>
   <si>
-    <t>ЛП</t>
-  </si>
-  <si>
-    <t>Сочи</t>
-  </si>
-  <si>
-    <t>10,09,26</t>
+    <t>Симферополь</t>
+  </si>
+  <si>
+    <t>11,09,26</t>
+  </si>
+  <si>
+    <t>КСК</t>
+  </si>
+  <si>
+    <t>Луганск</t>
+  </si>
+  <si>
+    <t>ЗПФ</t>
+  </si>
+  <si>
+    <t>НВ</t>
+  </si>
+  <si>
+    <t>12,09,26</t>
+  </si>
+  <si>
+    <t>Мелитополь</t>
+  </si>
+  <si>
+    <t>Донецк</t>
   </si>
 </sst>
 </file>
@@ -548,126 +566,172 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1">
+      <c r="A1" s="5">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="3">
-        <v>18206.340000000004</v>
-      </c>
-      <c r="G1" s="4">
-        <v>0.41666666666666669</v>
+      <c r="F1" s="7">
+        <v>18021.300000000003</v>
+      </c>
+      <c r="G1" s="8">
+        <v>0.375</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
+      <c r="A2" s="1">
         <v>2</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="7">
-        <v>18073.95</v>
-      </c>
-      <c r="G2" s="8">
-        <v>0.45833333333333331</v>
+      <c r="F2" s="3">
+        <v>19042.120000000003</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
+      <c r="A3" s="5">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="3">
-        <v>18103.2</v>
-      </c>
-      <c r="G3" s="4">
-        <v>0.5</v>
+      <c r="E3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="7">
+        <v>13638.64</v>
+      </c>
+      <c r="G3" s="8">
+        <v>0.41666666666666669</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
+      <c r="A4" s="1">
         <v>4</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="7" t="s">
+      <c r="B4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="7">
-        <v>17604.599999999999</v>
-      </c>
-      <c r="G4" s="8">
-        <v>0.54166666666666663</v>
+      <c r="F4" s="3">
+        <v>21025.500000000004</v>
+      </c>
+      <c r="G4" s="4">
+        <v>0.375</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
+      <c r="A5" s="5">
         <v>5</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="B5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="3">
-        <v>18066.18</v>
-      </c>
-      <c r="G5" s="4">
-        <v>0.58333333333333337</v>
+      <c r="D5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F5" s="7">
+        <v>17783.120000000003</v>
+      </c>
+      <c r="G5" s="8">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" s="3">
+        <v>17540.11</v>
+      </c>
+      <c r="G6" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>7</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="7">
+        <v>17846.140000000003</v>
+      </c>
+      <c r="G7" s="8">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8285FCE-4EC9-4B14-AF83-FAC34B539D50}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB62898F-C192-4F57-9DE2-D69B16E5E67F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="09,09,26" sheetId="101" r:id="rId1"/>
+    <sheet name="10,09,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,15 +31,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="12">
   <si>
     <t>КИ</t>
   </si>
   <si>
     <t>Симферополь</t>
-  </si>
-  <si>
-    <t>11,09,26</t>
   </si>
   <si>
     <t>КСК</t>
@@ -57,10 +54,19 @@
     <t>12,09,26</t>
   </si>
   <si>
-    <t>Мелитополь</t>
+    <t>Донецк</t>
   </si>
   <si>
-    <t>Донецк</t>
+    <t>ЛП</t>
+  </si>
+  <si>
+    <t>13,09,26</t>
+  </si>
+  <si>
+    <t>Бердянск</t>
+  </si>
+  <si>
+    <t>Сочи</t>
   </si>
 </sst>
 </file>
@@ -101,7 +107,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -154,11 +160,130 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -182,6 +307,78 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="20" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -566,175 +763,505 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="21.28515625" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5">
+      <c r="A1" s="1">
         <v>1</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="C1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="3">
+        <v>15326.64</v>
+      </c>
+      <c r="G1" s="4">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A2" s="29">
+        <v>2</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="10">
+        <v>12825.84</v>
+      </c>
+      <c r="G2" s="11">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="30"/>
+      <c r="B3" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="13">
+        <v>4217.8600000000006</v>
+      </c>
+      <c r="G3" s="14">
+        <v>0.54166666666666663</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="27">
         <v>3</v>
       </c>
-      <c r="F1" s="7">
-        <v>18021.300000000003</v>
-      </c>
-      <c r="G1" s="8">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+      <c r="B4" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="16">
+        <v>3859.44</v>
+      </c>
+      <c r="G4" s="17">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="31"/>
+      <c r="B5" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="19">
+        <v>9427.0800000000017</v>
+      </c>
+      <c r="G5" s="20">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="28"/>
+      <c r="B6" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="22">
+        <v>1657</v>
+      </c>
+      <c r="G6" s="23">
+        <v>0.58333333333333337</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="29">
+        <v>4</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="10">
+        <v>15748.080000000004</v>
+      </c>
+      <c r="G7" s="11">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="30"/>
+      <c r="B8" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="13">
+        <v>4500</v>
+      </c>
+      <c r="G8" s="14">
+        <v>0.625</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A9" s="27">
+        <v>5</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="16">
+        <v>2004.6</v>
+      </c>
+      <c r="G9" s="17">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="31"/>
+      <c r="B10" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="19">
+        <v>4005</v>
+      </c>
+      <c r="G10" s="20">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A11" s="31"/>
+      <c r="B11" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="19">
+        <v>1008</v>
+      </c>
+      <c r="G11" s="20">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A12" s="31"/>
+      <c r="B12" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="19">
+        <v>998.4</v>
+      </c>
+      <c r="G12" s="20">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="28"/>
+      <c r="B13" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="22">
+        <v>2496</v>
+      </c>
+      <c r="G13" s="23">
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5">
+        <v>6</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="F14" s="7">
+        <v>17582.64</v>
+      </c>
+      <c r="G14" s="8">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A15" s="27">
+        <v>7</v>
+      </c>
+      <c r="B15" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="C15" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F15" s="16">
+        <v>15567.38</v>
+      </c>
+      <c r="G15" s="17">
+        <v>8.3333333333333329E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="28"/>
+      <c r="B16" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="F16" s="22">
+        <v>2315.7800000000007</v>
+      </c>
+      <c r="G16" s="23">
+        <v>8.3333333333333329E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A17" s="29">
+        <v>8</v>
+      </c>
+      <c r="B17" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="3">
-        <v>19042.120000000003</v>
-      </c>
-      <c r="G2" s="4">
+      <c r="C17" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="10">
+        <v>964.8</v>
+      </c>
+      <c r="G17" s="11">
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
+    <row r="18" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A18" s="32"/>
+      <c r="B18" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="7" t="s">
+      <c r="C18" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="7">
-        <v>13638.64</v>
-      </c>
-      <c r="G3" s="8">
+      <c r="F18" s="25">
+        <v>7275.92</v>
+      </c>
+      <c r="G18" s="26">
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>4</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3" t="s">
+    <row r="19" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="30"/>
+      <c r="B19" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" s="13">
+        <v>9418.86</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A20" s="27">
+        <v>9</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="16">
+        <v>1556.3</v>
+      </c>
+      <c r="G20" s="17">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="28"/>
+      <c r="B21" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="3">
-        <v>21025.500000000004</v>
-      </c>
-      <c r="G4" s="4">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
+      <c r="C21" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E21" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="7">
-        <v>17783.120000000003</v>
-      </c>
-      <c r="G5" s="8">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="F21" s="22">
+        <v>16165.960000000001</v>
+      </c>
+      <c r="G21" s="23">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="5">
+        <v>10</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" s="3">
-        <v>17540.11</v>
-      </c>
-      <c r="G6" s="4">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
-        <v>7</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" s="7">
-        <v>17846.140000000003</v>
-      </c>
-      <c r="G7" s="8">
+      <c r="E22" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="7">
+        <v>17727.21</v>
+      </c>
+      <c r="G22" s="8">
         <v>0.5</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A13"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="A17:A19"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/графики/Для Паши.xlsx
+++ b/графики/Для Паши.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\графики\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB62898F-C192-4F57-9DE2-D69B16E5E67F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE28746A-87E2-43B7-9225-208D84923900}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="10,09,26" sheetId="101" r:id="rId1"/>
+    <sheet name="11,09,26" sheetId="101" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="12">
   <si>
     <t>КИ</t>
   </si>
@@ -51,13 +51,7 @@
     <t>НВ</t>
   </si>
   <si>
-    <t>12,09,26</t>
-  </si>
-  <si>
     <t>Донецк</t>
-  </si>
-  <si>
-    <t>ЛП</t>
   </si>
   <si>
     <t>13,09,26</t>
@@ -66,7 +60,13 @@
     <t>Бердянск</t>
   </si>
   <si>
-    <t>Сочи</t>
+    <t>14,09,26</t>
+  </si>
+  <si>
+    <t>Мелитополь</t>
+  </si>
+  <si>
+    <t>15,09,26</t>
   </si>
 </sst>
 </file>
@@ -283,7 +283,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -354,18 +354,12 @@
     <xf numFmtId="20" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -373,12 +367,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -763,11 +751,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94168203-2274-4554-96B1-274DAAA6E777}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="18.28515625" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -781,486 +769,382 @@
         <v>4</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="3">
-        <v>15326.64</v>
+        <v>15423.2</v>
       </c>
       <c r="G1" s="4">
-        <v>0.375</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="29">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5">
         <v>2</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="7">
+        <v>17751.039999999997</v>
+      </c>
+      <c r="G2" s="8">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A3" s="24">
+        <v>3</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="16">
+        <v>10686.22</v>
+      </c>
+      <c r="G3" s="17">
+        <v>8.3333333333333329E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="25"/>
+      <c r="B4" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="19">
+        <v>2259.3000000000002</v>
+      </c>
+      <c r="G4" s="20">
+        <v>8.3333333333333329E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="26"/>
+      <c r="B5" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="22">
+        <v>4914</v>
+      </c>
+      <c r="G5" s="23">
+        <v>8.3333333333333329E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A6" s="27">
+        <v>4</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="10">
+        <v>9525.1799999999985</v>
+      </c>
+      <c r="G6" s="11">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="28"/>
+      <c r="B7" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F7" s="13">
+        <v>8393.86</v>
+      </c>
+      <c r="G7" s="14">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>5</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="3">
+        <v>17593.480000000003</v>
+      </c>
+      <c r="G8" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>6</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="7">
+        <v>17815.55</v>
+      </c>
+      <c r="G9" s="8">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A10" s="24">
+        <v>7</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" s="16">
+        <v>6440.84</v>
+      </c>
+      <c r="G10" s="17">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="26"/>
+      <c r="B11" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" s="22">
+        <v>6430.28</v>
+      </c>
+      <c r="G11" s="23">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5">
+        <v>8</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="E12" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F12" s="7">
+        <v>15627.560000000001</v>
+      </c>
+      <c r="G12" s="8">
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>9</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="10">
-        <v>12825.84</v>
-      </c>
-      <c r="G2" s="11">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="30"/>
-      <c r="B3" s="12" t="s">
+      <c r="D13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="13">
-        <v>4217.8600000000006</v>
-      </c>
-      <c r="G3" s="14">
-        <v>0.54166666666666663</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="27">
-        <v>3</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="16">
-        <v>3859.44</v>
-      </c>
-      <c r="G4" s="17">
-        <v>0.58333333333333337</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="31"/>
-      <c r="B5" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="19">
-        <v>9427.0800000000017</v>
-      </c>
-      <c r="G5" s="20">
-        <v>0.58333333333333337</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="28"/>
-      <c r="B6" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="22">
-        <v>1657</v>
-      </c>
-      <c r="G6" s="23">
-        <v>0.58333333333333337</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="29">
-        <v>4</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="10">
-        <v>15748.080000000004</v>
-      </c>
-      <c r="G7" s="11">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="30"/>
-      <c r="B8" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="13">
-        <v>4500</v>
-      </c>
-      <c r="G8" s="14">
-        <v>0.625</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A9" s="27">
-        <v>5</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="16">
-        <v>2004.6</v>
-      </c>
-      <c r="G9" s="17">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A10" s="31"/>
-      <c r="B10" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="19">
-        <v>4005</v>
-      </c>
-      <c r="G10" s="20">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A11" s="31"/>
-      <c r="B11" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="19">
-        <v>1008</v>
-      </c>
-      <c r="G11" s="20">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A12" s="31"/>
-      <c r="B12" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="19">
-        <v>998.4</v>
-      </c>
-      <c r="G12" s="20">
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="28"/>
-      <c r="B13" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" s="22">
-        <v>2496</v>
-      </c>
-      <c r="G13" s="23">
-        <v>0.66666666666666663</v>
+      <c r="E13" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F13" s="3">
+        <v>18819.259999999998</v>
+      </c>
+      <c r="G13" s="4">
+        <v>4.1666666666666664E-2</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>0</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F14" s="7">
-        <v>17582.64</v>
+        <v>5549.28</v>
       </c>
       <c r="G14" s="8">
-        <v>4.1666666666666664E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A15" s="27">
-        <v>7</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="16" t="s">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D15" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="F15" s="16">
-        <v>15567.38</v>
-      </c>
-      <c r="G15" s="17">
-        <v>8.3333333333333329E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="28"/>
-      <c r="B16" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="D16" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="F16" s="22">
-        <v>2315.7800000000007</v>
-      </c>
-      <c r="G16" s="23">
-        <v>8.3333333333333329E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A17" s="29">
+      <c r="D15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="3">
+        <v>17410.560000000001</v>
+      </c>
+      <c r="G15" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
+      <c r="A16" s="27">
+        <v>12</v>
+      </c>
+      <c r="B16" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="10" t="s">
+      <c r="C16" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F17" s="10">
-        <v>964.8</v>
-      </c>
-      <c r="G17" s="11">
+      <c r="F16" s="10">
+        <v>10851.199999999999</v>
+      </c>
+      <c r="G16" s="11">
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A18" s="32"/>
-      <c r="B18" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="D18" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" s="25" t="s">
+    <row r="17" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="28"/>
+      <c r="B17" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F18" s="25">
-        <v>7275.92</v>
-      </c>
-      <c r="G18" s="26">
+      <c r="F17" s="13">
+        <v>3746.52</v>
+      </c>
+      <c r="G17" s="14">
         <v>0.41666666666666669</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="30"/>
-      <c r="B19" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" s="13">
-        <v>9418.86</v>
-      </c>
-      <c r="G19" s="14">
-        <v>0.41666666666666669</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="18.75" x14ac:dyDescent="0.2">
-      <c r="A20" s="27">
-        <v>9</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="16">
-        <v>1556.3</v>
-      </c>
-      <c r="G20" s="17">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="28"/>
-      <c r="B21" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="D21" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="E21" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" s="22">
-        <v>16165.960000000001</v>
-      </c>
-      <c r="G21" s="23">
-        <v>0.45833333333333331</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="5">
-        <v>10</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" s="7">
-        <v>17727.21</v>
-      </c>
-      <c r="G22" s="8">
-        <v>0.5</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A17:A19"/>
+  <mergeCells count="4">
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A16:A17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
